--- a/MappingGuides/mapping/guides/MappingGuide_MMS200MI_ItemToolbox.xlsx
+++ b/MappingGuides/mapping/guides/MappingGuide_MMS200MI_ItemToolbox.xlsx
@@ -30738,12 +30738,7 @@
       <c r="X387" s="2" t="inlineStr"/>
       <c r="Y387" s="2" t="inlineStr"/>
       <c r="Z387" s="2" t="inlineStr"/>
-      <c r="AA387" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates company number, which is the primary identity in all files in the M3 system. The purpose of this is to be able to handle, in the same database, several companies completely or partially separated.
-A maximum of 999 companies may be handled in the same database.</t>
-        </is>
-      </c>
+      <c r="AA387" s="2" t="inlineStr"/>
       <c r="AB387" s="2" t="inlineStr"/>
       <c r="AC387" s="2" t="inlineStr">
         <is>
@@ -30997,12 +30992,7 @@
       </c>
       <c r="Y389" s="2" t="inlineStr"/>
       <c r="Z389" s="2" t="inlineStr"/>
-      <c r="AA389" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the item number (for Maintenance, the item number or equipment number), which is a unique ID for an individual item.
-Items are entered and maintained in (MMS001). Item number can consist up to 15 alphanumeric characters.</t>
-        </is>
-      </c>
+      <c r="AA389" s="2" t="inlineStr"/>
       <c r="AB389" s="2" t="inlineStr"/>
       <c r="AC389" s="2" t="inlineStr">
         <is>
@@ -31113,11 +31103,7 @@
       </c>
       <c r="Y390" s="2" t="inlineStr"/>
       <c r="Z390" s="2" t="inlineStr"/>
-      <c r="AA390" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the name for each item. The max allowed length of the item name can be controlled via (CRS735).</t>
-        </is>
-      </c>
+      <c r="AA390" s="2" t="inlineStr"/>
       <c r="AB390" s="2" t="inlineStr"/>
       <c r="AC390" s="2" t="inlineStr"/>
       <c r="AD390" s="2" t="inlineStr"/>
@@ -31208,14 +31194,7 @@
       <c r="X391" s="2" t="inlineStr"/>
       <c r="Y391" s="2" t="inlineStr"/>
       <c r="Z391" s="2" t="inlineStr"/>
-      <c r="AA391" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a supplementary description of the item. The maximum length of the item description can be controlled via (CRS735).
-The description information can be configured when 'Dynamic description' parameter is deactivated in (CRS760). The configurable description is set up in (MWS050) with number type 6 ('Item description'), and in (MWS051).
-The item numbering rule is linked to the item type and language via (MWS045). If it is activated, the item description will be built via item numbering rules. If no record is activated, the first 32 positions can be maintained in a separate field in the Work-with function for items (the I panel), displayed in a 3*10 format.
-The description can be used as a search key.</t>
-        </is>
-      </c>
+      <c r="AA391" s="2" t="inlineStr"/>
       <c r="AB391" s="2" t="inlineStr"/>
       <c r="AC391" s="2" t="inlineStr"/>
       <c r="AD391" s="2" t="inlineStr"/>
@@ -31306,12 +31285,7 @@
       <c r="X392" s="2" t="inlineStr"/>
       <c r="Y392" s="2" t="inlineStr"/>
       <c r="Z392" s="2" t="inlineStr"/>
-      <c r="AA392" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a unique ID for the drawing used in designing the item.
-The drawing number is set per item and can also be used as a search key in both the item file and product structures.</t>
-        </is>
-      </c>
+      <c r="AA392" s="2" t="inlineStr"/>
       <c r="AB392" s="2" t="inlineStr"/>
       <c r="AC392" s="2" t="inlineStr"/>
       <c r="AD392" s="2" t="inlineStr"/>
@@ -31521,12 +31495,7 @@
       <c r="X394" s="2" t="inlineStr"/>
       <c r="Y394" s="2" t="inlineStr"/>
       <c r="Z394" s="2" t="inlineStr"/>
-      <c r="AA394" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many decimal places are to be used in connection with processing quantities.
-Zero to six decimal places may be used.</t>
-        </is>
-      </c>
+      <c r="AA394" s="2" t="inlineStr"/>
       <c r="AB394" s="2" t="inlineStr"/>
       <c r="AC394" s="2" t="inlineStr"/>
       <c r="AD394" s="2" t="inlineStr"/>
@@ -31633,11 +31602,7 @@
       </c>
       <c r="Y395" s="2" t="inlineStr"/>
       <c r="Z395" s="2" t="inlineStr"/>
-      <c r="AA395" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the unit in which each item is recorded in inventory, even if alternate inventory units of measure are used. All balance information for the current item is always stored in this unit.</t>
-        </is>
-      </c>
+      <c r="AA395" s="2" t="inlineStr"/>
       <c r="AB395" s="2" t="inlineStr"/>
       <c r="AC395" s="2" t="inlineStr"/>
       <c r="AD395" s="2" t="inlineStr"/>
@@ -31744,12 +31709,7 @@
         </is>
       </c>
       <c r="Z396" s="2" t="inlineStr"/>
-      <c r="AA396" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the item group from which items should be included in the forecast adjustment.
-The information is used as selection and sorting criteria in different contexts.</t>
-        </is>
-      </c>
+      <c r="AA396" s="2" t="inlineStr"/>
       <c r="AB396" s="2" t="inlineStr"/>
       <c r="AC396" s="2" t="inlineStr">
         <is>
@@ -31864,12 +31824,7 @@
         </is>
       </c>
       <c r="Z397" s="2" t="inlineStr"/>
-      <c r="AA397" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the product group from which items should be included in the forecast adjustment.
-The information is used as selection and sorting criteria in different contexts.</t>
-        </is>
-      </c>
+      <c r="AA397" s="2" t="inlineStr"/>
       <c r="AB397" s="2" t="inlineStr"/>
       <c r="AC397" s="2" t="inlineStr">
         <is>
@@ -31964,11 +31919,7 @@
       <c r="X398" s="2" t="inlineStr"/>
       <c r="Y398" s="2" t="inlineStr"/>
       <c r="Z398" s="2" t="inlineStr"/>
-      <c r="AA398" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the business area for this shop. This business area is a tool used to group information for budgeting and statistical purposes and is created in (CRS036).</t>
-        </is>
-      </c>
+      <c r="AA398" s="2" t="inlineStr"/>
       <c r="AB398" s="2" t="inlineStr"/>
       <c r="AC398" s="2" t="inlineStr">
         <is>
@@ -32059,11 +32010,7 @@
       <c r="X399" s="2" t="inlineStr"/>
       <c r="Y399" s="2" t="inlineStr"/>
       <c r="Z399" s="2" t="inlineStr"/>
-      <c r="AA399" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the environment group. Each item can be connected to a group that is defined in (CRS038).</t>
-        </is>
-      </c>
+      <c r="AA399" s="2" t="inlineStr"/>
       <c r="AB399" s="2" t="inlineStr"/>
       <c r="AC399" s="2" t="inlineStr">
         <is>
@@ -32178,18 +32125,7 @@
         </is>
       </c>
       <c r="Z400" s="2" t="inlineStr"/>
-      <c r="AA400" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the item type, which determines an item's life cycle. The item type is mandatory and cannot be changed after the item is created. The only time an item type can be changed is when you copy template items.
-The functions connected to the item type include:
--A template item that contains default values for creating items.
--A numbering rule for assigning the correct item number based on settings in (MWS050).
--Field control in (MWS041) that sets the fields displayed for the item in (MMS001), the item/warehouse in (MMS002), and the item/facility in (MMS003).
--A warehouse/item type in (MWS042) to set the item/warehouse records generated when you create an item.
--An alias/item type in (MWS043) that is used to set the alias numbers generated when you create an item. Alias numbers are EAN13, UPC, popular numbers, and so on.
-The item type can also be used as selection criteria to find any type of item, such as raw material, purchased components, semi-finished products, and finished products. Item types are defined in (CRS040), where they can also be linked to an item category.</t>
-        </is>
-      </c>
+      <c r="AA400" s="2" t="inlineStr"/>
       <c r="AB400" s="2" t="inlineStr"/>
       <c r="AC400" s="2" t="inlineStr">
         <is>
@@ -32288,25 +32224,8 @@
       <c r="X401" s="2" t="inlineStr"/>
       <c r="Y401" s="2" t="inlineStr"/>
       <c r="Z401" s="2" t="inlineStr"/>
-      <c r="AA401" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the item category that best represents the characteristics of each item.</t>
-        </is>
-      </c>
-      <c r="AB401" s="2" t="inlineStr">
-        <is>
-          <t>00: Normal item
-02: Phantom item
-03: Subcontracted item
-04: Tool
-05: Fixed machine
-07: Repairable item
-08: Recyclable item
-11: Extended Catalog Item (ECI)
-12: Non-coded Extended Catalog Item
-13: Non-material item</t>
-        </is>
-      </c>
+      <c r="AA401" s="2" t="inlineStr"/>
+      <c r="AB401" s="2" t="inlineStr"/>
       <c r="AC401" s="2" t="inlineStr"/>
       <c r="AD401" s="2" t="inlineStr"/>
       <c r="AE401" s="2" t="inlineStr">
@@ -32416,17 +32335,8 @@
         </is>
       </c>
       <c r="Z402" s="2" t="inlineStr"/>
-      <c r="AA402" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the item is manufactured in-house or purchased.</t>
-        </is>
-      </c>
-      <c r="AB402" s="2" t="inlineStr">
-        <is>
-          <t>1: Manufactured
-2: Purchased.</t>
-        </is>
-      </c>
+      <c r="AA402" s="2" t="inlineStr"/>
+      <c r="AB402" s="2" t="inlineStr"/>
       <c r="AC402" s="2" t="inlineStr"/>
       <c r="AD402" s="2" t="inlineStr"/>
       <c r="AE402" s="2" t="inlineStr"/>
@@ -32516,21 +32426,8 @@
       <c r="X403" s="2" t="inlineStr"/>
       <c r="Y403" s="2" t="inlineStr"/>
       <c r="Z403" s="2" t="inlineStr"/>
-      <c r="AA403" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if the item is configured when ordered or configured as a maintenance item.</t>
-        </is>
-      </c>
-      <c r="AB403" s="2" t="inlineStr">
-        <is>
-          <t>0: No.
-1: Yes.
-2: Yes, as a family item from which product variants with item numbers are created.
-3: No. The item is a product variant with the item number of the family item.
-4: The item is a maintenance item. Regulates the item costing.
-5: The item is a maintenance item. Possibility to answer inquiries to get a better planned work order.</t>
-        </is>
-      </c>
+      <c r="AA403" s="2" t="inlineStr"/>
+      <c r="AB403" s="2" t="inlineStr"/>
       <c r="AC403" s="2" t="inlineStr"/>
       <c r="AD403" s="2" t="inlineStr"/>
       <c r="AE403" s="2" t="inlineStr">
@@ -32628,19 +32525,8 @@
         </is>
       </c>
       <c r="Z404" s="2" t="inlineStr"/>
-      <c r="AA404" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the stock kept for the item is accounted in inventory.</t>
-        </is>
-      </c>
-      <c r="AB404" s="2" t="inlineStr">
-        <is>
-          <t>0: No.
-1: Yes, the item is inventory accounted.
-2: No, the item is not inventory accounted, but it is planned as demand in the material planning process in (MMS080).
-3: No, the item is not inventory accounted, but it is planned as a function number. A function number is a dummy number for items that can replace each other. So material planning for the item is done on the function number level instead of the item level.</t>
-        </is>
-      </c>
+      <c r="AA404" s="2" t="inlineStr"/>
+      <c r="AB404" s="2" t="inlineStr"/>
       <c r="AC404" s="2" t="inlineStr"/>
       <c r="AD404" s="2" t="inlineStr"/>
       <c r="AE404" s="2" t="inlineStr">
@@ -32730,25 +32616,8 @@
       <c r="X405" s="2" t="inlineStr"/>
       <c r="Y405" s="2" t="inlineStr"/>
       <c r="Z405" s="2" t="inlineStr"/>
-      <c r="AA405" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the serial number is created.</t>
-        </is>
-      </c>
-      <c r="AB405" s="2" t="inlineStr">
-        <is>
-          <t>0: Manually
-1: Automatically, using YYMM plus a sequence number
-2: Automatically, using YY plus a sequence number
-3: Automatically, using a sequence number
-4: Goods receiving number generated during goods receipt, but this must be entered manually
-5: Order number - only used with manufacturing orders
-6: Automatically, using YYMMDD plus a sequence number
-7: Automatically, using the numbering rules defined in (CRS040)
-8: Simple lot tracing for outbound deliveries, mandatory to fill in a lot reference when reporting picking lines
-9: Simple lot tracing for outbound deliveries, optional to fill in a lot reference when reporting picking list lines.</t>
-        </is>
-      </c>
+      <c r="AA405" s="2" t="inlineStr"/>
+      <c r="AB405" s="2" t="inlineStr"/>
       <c r="AC405" s="2" t="inlineStr"/>
       <c r="AD405" s="2" t="inlineStr"/>
       <c r="AE405" s="2" t="inlineStr">
@@ -33136,19 +33005,8 @@
       <c r="X409" s="2" t="inlineStr"/>
       <c r="Y409" s="2" t="inlineStr"/>
       <c r="Z409" s="2" t="inlineStr"/>
-      <c r="AA409" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the product type of the item.</t>
-        </is>
-      </c>
-      <c r="AB409" s="2" t="inlineStr">
-        <is>
-          <t>0: Normal item.
-1: By-product that is usable material resulting from the manufacture of another product. This is considered a standard value and is defaulted during material line entry.
-2: Co-product that results in a usable item.
-3: Main product that orders production and costing for co-products.</t>
-        </is>
-      </c>
+      <c r="AA409" s="2" t="inlineStr"/>
+      <c r="AB409" s="2" t="inlineStr"/>
       <c r="AC409" s="2" t="inlineStr"/>
       <c r="AD409" s="2" t="inlineStr"/>
       <c r="AE409" s="2" t="inlineStr">
@@ -33242,13 +33100,7 @@
       <c r="X410" s="2" t="inlineStr"/>
       <c r="Y410" s="2" t="inlineStr"/>
       <c r="Z410" s="2" t="inlineStr"/>
-      <c r="AA410" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the normal waste percentage per item, and is expressed as a percentage to two decimal places.
-The normal waste percentage is suggested as waste percentage at new entry of materials where it may be overruled for each material line.
-The information is used at estimate, requirements calculation and material reservations.</t>
-        </is>
-      </c>
+      <c r="AA410" s="2" t="inlineStr"/>
       <c r="AB410" s="2" t="inlineStr"/>
       <c r="AC410" s="2" t="inlineStr"/>
       <c r="AD410" s="2" t="inlineStr"/>
@@ -33343,19 +33195,8 @@
       <c r="X411" s="2" t="inlineStr"/>
       <c r="Y411" s="2" t="inlineStr"/>
       <c r="Z411" s="2" t="inlineStr"/>
-      <c r="AA411" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if and how the item should be quality inspected.</t>
-        </is>
-      </c>
-      <c r="AB411" s="2" t="inlineStr">
-        <is>
-          <t>0: The item should not be quality inspected.
-1: The item should be quality inspected but without a quality request.
-2: The item should be quality inspected together with a quality request.
-3: The item should be quality inspected together with a quality request and automatically create inspection records in (PPS300) and lots in (MMS235).</t>
-        </is>
-      </c>
+      <c r="AA411" s="2" t="inlineStr"/>
+      <c r="AB411" s="2" t="inlineStr"/>
       <c r="AC411" s="2" t="inlineStr"/>
       <c r="AD411" s="2" t="inlineStr"/>
       <c r="AE411" s="2" t="inlineStr">
@@ -33445,13 +33286,7 @@
       <c r="X412" s="2" t="inlineStr"/>
       <c r="Y412" s="2" t="inlineStr"/>
       <c r="Z412" s="2" t="inlineStr"/>
-      <c r="AA412" s="2" t="inlineStr">
-        <is>
-          <t>This field indicates if yield for an item should be calculated when it is prepared as a product.
-Select the check box to calculate when it is prepared as a product.
-If the product is to be prepared through the indication of the bill of material and routing per production batch, then yield calculation must have been activated for the product.</t>
-        </is>
-      </c>
+      <c r="AA412" s="2" t="inlineStr"/>
       <c r="AB412" s="2" t="inlineStr"/>
       <c r="AC412" s="2" t="inlineStr"/>
       <c r="AD412" s="2" t="inlineStr"/>
@@ -33546,11 +33381,7 @@
       <c r="X413" s="2" t="inlineStr"/>
       <c r="Y413" s="2" t="inlineStr"/>
       <c r="Z413" s="2" t="inlineStr"/>
-      <c r="AA413" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the normal potency, which is used for inventory accounting and planning. The potency is expressed as a percentage to two decimal places.</t>
-        </is>
-      </c>
+      <c r="AA413" s="2" t="inlineStr"/>
       <c r="AB413" s="2" t="inlineStr"/>
       <c r="AC413" s="2" t="inlineStr"/>
       <c r="AD413" s="2" t="inlineStr"/>
@@ -33645,20 +33476,8 @@
       <c r="X414" s="2" t="inlineStr"/>
       <c r="Y414" s="2" t="inlineStr"/>
       <c r="Z414" s="2" t="inlineStr"/>
-      <c r="AA414" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether this is an active or a catch weight item.</t>
-        </is>
-      </c>
-      <c r="AB414" s="2" t="inlineStr">
-        <is>
-          <t>0: Neither
-1: Active item
-2: Catch weight item inspected for both receipt and delivery
-3: Catch weight item inspected for receipt
-4: Catch weight item inspected for delivery without requiring lot control.</t>
-        </is>
-      </c>
+      <c r="AA414" s="2" t="inlineStr"/>
+      <c r="AB414" s="2" t="inlineStr"/>
       <c r="AC414" s="2" t="inlineStr"/>
       <c r="AD414" s="2" t="inlineStr"/>
       <c r="AE414" s="2" t="inlineStr">
@@ -33748,13 +33567,7 @@
       <c r="X415" s="2" t="inlineStr"/>
       <c r="Y415" s="2" t="inlineStr"/>
       <c r="Z415" s="2" t="inlineStr"/>
-      <c r="AA415" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates item hierarchy, which groups items vertically in a way that describes a company''s business. Item hierarchy provides a flexible and logical way to search for items and to group items for statistics and control purposes.
-Acceptable item hierarchies are defined in (MMS021) and are connected to an item via (MMS001/M).
-The number of item hierarchies (max 5) and the length on each hierarchical level are defined in (CRS704). The total length of all item hierarchies is 15 positions.</t>
-        </is>
-      </c>
+      <c r="AA415" s="2" t="inlineStr"/>
       <c r="AB415" s="2" t="inlineStr"/>
       <c r="AC415" s="2" t="inlineStr"/>
       <c r="AD415" s="2" t="inlineStr"/>
@@ -33841,13 +33654,7 @@
       <c r="X416" s="2" t="inlineStr"/>
       <c r="Y416" s="2" t="inlineStr"/>
       <c r="Z416" s="2" t="inlineStr"/>
-      <c r="AA416" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates item hierarchy, which groups items vertically in a way that describes a company''s business. Item hierarchy provides a flexible and logical way to search for items and to group items for statistics and control purposes.
-Acceptable item hierarchies are defined in (MMS021) and are connected to an item via (MMS001/M).
-The number of item hierarchies (max 5) and the length on each hierarchical level are defined in (CRS704). The total length of all item hierarchies is 15 positions.</t>
-        </is>
-      </c>
+      <c r="AA416" s="2" t="inlineStr"/>
       <c r="AB416" s="2" t="inlineStr"/>
       <c r="AC416" s="2" t="inlineStr"/>
       <c r="AD416" s="2" t="inlineStr"/>
@@ -33934,13 +33741,7 @@
       <c r="X417" s="2" t="inlineStr"/>
       <c r="Y417" s="2" t="inlineStr"/>
       <c r="Z417" s="2" t="inlineStr"/>
-      <c r="AA417" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates item hierarchy, which groups items vertically in a way that describes a company''s business. Item hierarchy provides a flexible and logical way to search for items and to group items for statistics and control purposes.
-Acceptable item hierarchies are defined in (MMS021) and are connected to an item via (MMS001/M).
-The number of item hierarchies (max 5) and the length on each hierarchical level are defined in (CRS704). The total length of all item hierarchies is 15 positions.</t>
-        </is>
-      </c>
+      <c r="AA417" s="2" t="inlineStr"/>
       <c r="AB417" s="2" t="inlineStr"/>
       <c r="AC417" s="2" t="inlineStr"/>
       <c r="AD417" s="2" t="inlineStr"/>
@@ -34027,13 +33828,7 @@
       <c r="X418" s="2" t="inlineStr"/>
       <c r="Y418" s="2" t="inlineStr"/>
       <c r="Z418" s="2" t="inlineStr"/>
-      <c r="AA418" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates item hierarchy, which groups items vertically in a way that describes a company''s business. Item hierarchy provides a flexible and logical way to search for items and to group items for statistics and control purposes.
-Acceptable item hierarchies are defined in (MMS021) and are connected to an item via (MMS001/M).
-The number of item hierarchies (max 5) and the length on each hierarchical level are defined in (CRS704). The total length of all item hierarchies is 15 positions.</t>
-        </is>
-      </c>
+      <c r="AA418" s="2" t="inlineStr"/>
       <c r="AB418" s="2" t="inlineStr"/>
       <c r="AC418" s="2" t="inlineStr"/>
       <c r="AD418" s="2" t="inlineStr"/>
@@ -34120,13 +33915,7 @@
       <c r="X419" s="2" t="inlineStr"/>
       <c r="Y419" s="2" t="inlineStr"/>
       <c r="Z419" s="2" t="inlineStr"/>
-      <c r="AA419" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates item hierarchy, which groups items vertically in a way that describes a company''s business. Item hierarchy provides a flexible and logical way to search for items and to group items for statistics and control purposes.
-Acceptable item hierarchies are defined in (MMS021) and are connected to an item via (MMS001/M).
-The number of item hierarchies (max 5) and the length on each hierarchical level are defined in (CRS704). The total length of all item hierarchies is 15 positions.</t>
-        </is>
-      </c>
+      <c r="AA419" s="2" t="inlineStr"/>
       <c r="AB419" s="2" t="inlineStr"/>
       <c r="AC419" s="2" t="inlineStr"/>
       <c r="AD419" s="2" t="inlineStr"/>
@@ -34213,12 +34002,7 @@
       <c r="X420" s="2" t="inlineStr"/>
       <c r="Y420" s="2" t="inlineStr"/>
       <c r="Z420" s="2" t="inlineStr"/>
-      <c r="AA420" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the search group, which is a user-defined field with no table behind it and which can be used as a complement to the item hierarchies. The purpose of the search group is to allow a horizontal search.
-The use of item search groups is controlled by (CRS704). A search group can be linked to an item hierarchy in (MMS021).</t>
-        </is>
-      </c>
+      <c r="AA420" s="2" t="inlineStr"/>
       <c r="AB420" s="2" t="inlineStr"/>
       <c r="AC420" s="2" t="inlineStr"/>
       <c r="AD420" s="2" t="inlineStr"/>
@@ -34305,12 +34089,7 @@
       <c r="X421" s="2" t="inlineStr"/>
       <c r="Y421" s="2" t="inlineStr"/>
       <c r="Z421" s="2" t="inlineStr"/>
-      <c r="AA421" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the search group, which is a user-defined field with no table behind it and which can be used as a complement to the item hierarchies. The purpose of the search group is to allow a horizontal search.
-The use of item search groups is controlled by (CRS704). A search group can be linked to an item hierarchy in (MMS021).</t>
-        </is>
-      </c>
+      <c r="AA421" s="2" t="inlineStr"/>
       <c r="AB421" s="2" t="inlineStr"/>
       <c r="AC421" s="2" t="inlineStr"/>
       <c r="AD421" s="2" t="inlineStr"/>
@@ -34397,12 +34176,7 @@
       <c r="X422" s="2" t="inlineStr"/>
       <c r="Y422" s="2" t="inlineStr"/>
       <c r="Z422" s="2" t="inlineStr"/>
-      <c r="AA422" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the search group, which is a user-defined field with no table behind it and which can be used as a complement to the item hierarchies. The purpose of the search group is to allow a horizontal search.
-The use of item search groups is controlled by (CRS704). A search group can be linked to an item hierarchy in (MMS021).</t>
-        </is>
-      </c>
+      <c r="AA422" s="2" t="inlineStr"/>
       <c r="AB422" s="2" t="inlineStr"/>
       <c r="AC422" s="2" t="inlineStr"/>
       <c r="AD422" s="2" t="inlineStr"/>
@@ -34489,12 +34263,7 @@
       <c r="X423" s="2" t="inlineStr"/>
       <c r="Y423" s="2" t="inlineStr"/>
       <c r="Z423" s="2" t="inlineStr"/>
-      <c r="AA423" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the search group, which is a user-defined field with no table behind it and which can be used as a complement to the item hierarchies. The purpose of the search group is to allow a horizontal search.
-The use of item search groups is controlled by (CRS704). A search group can be linked to an item hierarchy in (MMS021).</t>
-        </is>
-      </c>
+      <c r="AA423" s="2" t="inlineStr"/>
       <c r="AB423" s="2" t="inlineStr"/>
       <c r="AC423" s="2" t="inlineStr"/>
       <c r="AD423" s="2" t="inlineStr"/>
@@ -34581,12 +34350,7 @@
       <c r="X424" s="2" t="inlineStr"/>
       <c r="Y424" s="2" t="inlineStr"/>
       <c r="Z424" s="2" t="inlineStr"/>
-      <c r="AA424" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the search group, which is a user-defined field with no table behind it and which can be used as a complement to the item hierarchies. The purpose of the search group is to allow a horizontal search.
-The use of item search groups is controlled by (CRS704). A search group can be linked to an item hierarchy in (MMS021).</t>
-        </is>
-      </c>
+      <c r="AA424" s="2" t="inlineStr"/>
       <c r="AB424" s="2" t="inlineStr"/>
       <c r="AC424" s="2" t="inlineStr"/>
       <c r="AD424" s="2" t="inlineStr"/>
@@ -35149,11 +34913,7 @@
       <c r="X430" s="2" t="inlineStr"/>
       <c r="Y430" s="2" t="inlineStr"/>
       <c r="Z430" s="2" t="inlineStr"/>
-      <c r="AA430" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the text ID, which identifies comments made. It is updated automatically when entering comments.</t>
-        </is>
-      </c>
+      <c r="AA430" s="2" t="inlineStr"/>
       <c r="AB430" s="2" t="inlineStr"/>
       <c r="AC430" s="2" t="inlineStr"/>
       <c r="AD430" s="2" t="inlineStr"/>
@@ -35248,11 +35008,7 @@
       <c r="X431" s="2" t="inlineStr"/>
       <c r="Y431" s="2" t="inlineStr"/>
       <c r="Z431" s="2" t="inlineStr"/>
-      <c r="AA431" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the revision number (edition) for an item or document.</t>
-        </is>
-      </c>
+      <c r="AA431" s="2" t="inlineStr"/>
       <c r="AB431" s="2" t="inlineStr"/>
       <c r="AC431" s="2" t="inlineStr"/>
       <c r="AD431" s="2" t="inlineStr"/>
@@ -35339,11 +35095,7 @@
       <c r="X432" s="2" t="inlineStr"/>
       <c r="Y432" s="2" t="inlineStr"/>
       <c r="Z432" s="2" t="inlineStr"/>
-      <c r="AA432" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if an item or document is managed using an engineering change order (ECO). ECOs are used for complex products. You must have the Engineering Change Order Management module installed to use this function.</t>
-        </is>
-      </c>
+      <c r="AA432" s="2" t="inlineStr"/>
       <c r="AB432" s="2" t="inlineStr"/>
       <c r="AC432" s="2" t="inlineStr"/>
       <c r="AD432" s="2" t="inlineStr"/>
@@ -35438,12 +35190,7 @@
       <c r="X433" s="2" t="inlineStr"/>
       <c r="Y433" s="2" t="inlineStr"/>
       <c r="Z433" s="2" t="inlineStr"/>
-      <c r="AA433" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the procurement group for an item, which is used to facilitate selections by grouping similar items together.
-Procurement groups are defined in (CRS037), and are entered for each item in the item file. Classifications are defined by the user.</t>
-        </is>
-      </c>
+      <c r="AA433" s="2" t="inlineStr"/>
       <c r="AB433" s="2" t="inlineStr"/>
       <c r="AC433" s="2" t="inlineStr">
         <is>
@@ -35534,14 +35281,7 @@
       <c r="X434" s="2" t="inlineStr"/>
       <c r="Y434" s="2" t="inlineStr"/>
       <c r="Z434" s="2" t="inlineStr"/>
-      <c r="AA434" s="2" t="inlineStr">
-        <is>
-          <t>This field represents a reference code for standard text which is to be printed on external PO and quotation request documents.
-Standard texts are entered in (MMS135).
-The specified code is entered in (MMS001) and proposed by default. However, it may be changed on the purchase order lines.
-The standard text printed is not saved on the purchase order.</t>
-        </is>
-      </c>
+      <c r="AA434" s="2" t="inlineStr"/>
       <c r="AB434" s="2" t="inlineStr"/>
       <c r="AC434" s="2" t="inlineStr"/>
       <c r="AD434" s="2" t="inlineStr"/>
@@ -35632,11 +35372,7 @@
       <c r="X435" s="2" t="inlineStr"/>
       <c r="Y435" s="2" t="inlineStr"/>
       <c r="Z435" s="2" t="inlineStr"/>
-      <c r="AA435" s="2" t="inlineStr">
-        <is>
-          <t>The field is user-defined, but is most often used to control account entries. It is therefore an accounting object that can be verified and changed in (CRS335).</t>
-        </is>
-      </c>
+      <c r="AA435" s="2" t="inlineStr"/>
       <c r="AB435" s="2" t="inlineStr"/>
       <c r="AC435" s="2" t="inlineStr">
         <is>
@@ -35830,12 +35566,7 @@
       <c r="X437" s="2" t="inlineStr"/>
       <c r="Y437" s="2" t="inlineStr"/>
       <c r="Z437" s="2" t="inlineStr"/>
-      <c r="AA437" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the unit of measure (U/M) in which the quantity on the purchase order is expressed.
-The purchase order U/M can be the alternate U/M or the item's standard purchase U/M, if an alternate does not exist. If there is no standard purchase U/M, the item's basic U/M is used.</t>
-        </is>
-      </c>
+      <c r="AA437" s="2" t="inlineStr"/>
       <c r="AB437" s="2" t="inlineStr"/>
       <c r="AC437" s="2" t="inlineStr">
         <is>
@@ -36027,18 +35758,8 @@
       <c r="X439" s="2" t="inlineStr"/>
       <c r="Y439" s="2" t="inlineStr"/>
       <c r="Z439" s="2" t="inlineStr"/>
-      <c r="AA439" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if and how alternate units of measure can be used for an item.</t>
-        </is>
-      </c>
-      <c r="AB439" s="2" t="inlineStr">
-        <is>
-          <t>0: No alternate units of measurement can be used.
-1: Alternate units of measurement exist but must never differ from the standard U/M - purchase order, defined in(MMS015/E). This alternative applies to purchase orders only.
-2: Alternate units of measurement exist and are permitted, under the condition that the unit is entered for the item.</t>
-        </is>
-      </c>
+      <c r="AA439" s="2" t="inlineStr"/>
+      <c r="AB439" s="2" t="inlineStr"/>
       <c r="AC439" s="2" t="inlineStr"/>
       <c r="AD439" s="2" t="inlineStr"/>
       <c r="AE439" s="2" t="inlineStr">
@@ -36128,20 +35849,8 @@
       <c r="X440" s="2" t="inlineStr"/>
       <c r="Y440" s="2" t="inlineStr"/>
       <c r="Z440" s="2" t="inlineStr"/>
-      <c r="AA440" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many decimal places that should be used when displaying or entering prices.</t>
-        </is>
-      </c>
-      <c r="AB440" s="2" t="inlineStr">
-        <is>
-          <t>0: No decimals
-1: One
-2: Two
-3: Three
-4: Four</t>
-        </is>
-      </c>
+      <c r="AA440" s="2" t="inlineStr"/>
+      <c r="AB440" s="2" t="inlineStr"/>
       <c r="AC440" s="2" t="inlineStr"/>
       <c r="AD440" s="2" t="inlineStr"/>
       <c r="AE440" s="2" t="inlineStr">
@@ -36314,11 +36023,7 @@
       <c r="X442" s="2" t="inlineStr"/>
       <c r="Y442" s="2" t="inlineStr"/>
       <c r="Z442" s="2" t="inlineStr"/>
-      <c r="AA442" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates either a customer number, project number or optional text, depending on the reference ID code.</t>
-        </is>
-      </c>
+      <c r="AA442" s="2" t="inlineStr"/>
       <c r="AB442" s="2" t="inlineStr"/>
       <c r="AC442" s="2" t="inlineStr"/>
       <c r="AD442" s="2" t="inlineStr"/>
@@ -36405,18 +36110,8 @@
       <c r="X443" s="2" t="inlineStr"/>
       <c r="Y443" s="2" t="inlineStr"/>
       <c r="Z443" s="2" t="inlineStr"/>
-      <c r="AA443" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates what is displayed in the reference ID field.</t>
-        </is>
-      </c>
-      <c r="AB443" s="2" t="inlineStr">
-        <is>
-          <t>0: Missing
-1: Customer number
-2: Project number.</t>
-        </is>
-      </c>
+      <c r="AA443" s="2" t="inlineStr"/>
+      <c r="AB443" s="2" t="inlineStr"/>
       <c r="AC443" s="2" t="inlineStr"/>
       <c r="AD443" s="2" t="inlineStr"/>
       <c r="AE443" s="2" t="inlineStr">
@@ -36506,11 +36201,7 @@
       <c r="X444" s="2" t="inlineStr"/>
       <c r="Y444" s="2" t="inlineStr"/>
       <c r="Z444" s="2" t="inlineStr"/>
-      <c r="AA444" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a technical relationship used to group items. The value entered must therefore follow the classification rules defined in (MMS042).</t>
-        </is>
-      </c>
+      <c r="AA444" s="2" t="inlineStr"/>
       <c r="AB444" s="2" t="inlineStr"/>
       <c r="AC444" s="2" t="inlineStr">
         <is>
@@ -36601,11 +36292,7 @@
       <c r="X445" s="2" t="inlineStr"/>
       <c r="Y445" s="2" t="inlineStr"/>
       <c r="Z445" s="2" t="inlineStr"/>
-      <c r="AA445" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates grouping of items according to their technical relations.</t>
-        </is>
-      </c>
+      <c r="AA445" s="2" t="inlineStr"/>
       <c r="AB445" s="2" t="inlineStr"/>
       <c r="AC445" s="2" t="inlineStr">
         <is>
@@ -36696,20 +36383,8 @@
       <c r="X446" s="2" t="inlineStr"/>
       <c r="Y446" s="2" t="inlineStr"/>
       <c r="Z446" s="2" t="inlineStr"/>
-      <c r="AA446" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the expiration date is calculated. This is used to set the expiration date, which is primarily used to obtain a correct priority date for lots in (MMS060). This, in turn, is used for automatic allocation when following FIFO principles.</t>
-        </is>
-      </c>
-      <c r="AB446" s="2" t="inlineStr">
-        <is>
-          <t>0: Expiration date missing. The receipt date is used as the priority date for allocation if lot control is used.
-1: The expiration date is calculated from the goods receiving/receipt date using the item's shelf life. This date can be overridden in goods receiving for purchasing and in receipt for manufacturing orders.
-2: The expiration date is calculated from the production date specified (either in goods receiving for purchasing or in receipt for manufacturing orders). This date can be overridden.
-3: The same as alternative 1, except that if the number of days is changed according to shelf life, re-inspection time or sales time it will update all warehouses for the item.
-4: The same as alternative 2, except that if the number of days is changed according to shelf life, re-inspection time or sales time it will update all warehouses for the item.</t>
-        </is>
-      </c>
+      <c r="AA446" s="2" t="inlineStr"/>
+      <c r="AB446" s="2" t="inlineStr"/>
       <c r="AC446" s="2" t="inlineStr"/>
       <c r="AD446" s="2" t="inlineStr"/>
       <c r="AE446" s="2" t="inlineStr">
@@ -36799,12 +36474,7 @@
       <c r="X447" s="2" t="inlineStr"/>
       <c r="Y447" s="2" t="inlineStr"/>
       <c r="Z447" s="2" t="inlineStr"/>
-      <c r="AA447" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the method that controls the processing of the goods receiving flow. Depending on the method, quality inspection may be performed, certain documents may be printed, etc.
-On the purchase order line, a default goods receiving method is proposed. This method may be overridden. The proposal is retrieved from one of three sources according to the following priority ranking:</t>
-        </is>
-      </c>
+      <c r="AA447" s="2" t="inlineStr"/>
       <c r="AB447" s="2" t="inlineStr"/>
       <c r="AC447" s="2" t="inlineStr">
         <is>
@@ -36991,18 +36661,8 @@
       <c r="X449" s="2" t="inlineStr"/>
       <c r="Y449" s="2" t="inlineStr"/>
       <c r="Z449" s="2" t="inlineStr"/>
-      <c r="AA449" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if the item is a sales item.</t>
-        </is>
-      </c>
-      <c r="AB449" s="2" t="inlineStr">
-        <is>
-          <t>0: No, customer orders/service orders may not be entered.
-1: Yes, customer orders/service orders may be entered.
-2: Yes, but customer orders/service orders may only be entered if the item is a component in a KIT.</t>
-        </is>
-      </c>
+      <c r="AA449" s="2" t="inlineStr"/>
+      <c r="AB449" s="2" t="inlineStr"/>
       <c r="AC449" s="2" t="inlineStr"/>
       <c r="AD449" s="2" t="inlineStr"/>
       <c r="AE449" s="2" t="inlineStr">
@@ -37092,12 +36752,7 @@
       <c r="X450" s="2" t="inlineStr"/>
       <c r="Y450" s="2" t="inlineStr"/>
       <c r="Z450" s="2" t="inlineStr"/>
-      <c r="AA450" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the fragility of the item. The fragility is used to sort items in a picking list.
-The order type usually determines how items are sorted. Items with the higher fragility value are printed last on the picking list, so they are placed highest in the package.</t>
-        </is>
-      </c>
+      <c r="AA450" s="2" t="inlineStr"/>
       <c r="AB450" s="2" t="inlineStr"/>
       <c r="AC450" s="2" t="inlineStr"/>
       <c r="AD450" s="2" t="inlineStr"/>
@@ -37188,12 +36843,7 @@
       <c r="X451" s="2" t="inlineStr"/>
       <c r="Y451" s="2" t="inlineStr"/>
       <c r="Z451" s="2" t="inlineStr"/>
-      <c r="AA451" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if an item, charge, customer or ship-to location is taxable or not.
-The tax code is used to calculate US sales tax.</t>
-        </is>
-      </c>
+      <c r="AA451" s="2" t="inlineStr"/>
       <c r="AB451" s="2" t="inlineStr"/>
       <c r="AC451" s="2" t="inlineStr">
         <is>
@@ -37288,12 +36938,7 @@
       <c r="X452" s="2" t="inlineStr"/>
       <c r="Y452" s="2" t="inlineStr"/>
       <c r="Z452" s="2" t="inlineStr"/>
-      <c r="AA452" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of an attribute model.
-Attribute models are connected to items and used to set the attributes that can be connected to the item.</t>
-        </is>
-      </c>
+      <c r="AA452" s="2" t="inlineStr"/>
       <c r="AB452" s="2" t="inlineStr"/>
       <c r="AC452" s="2" t="inlineStr">
         <is>
@@ -37384,19 +37029,8 @@
       <c r="X453" s="2" t="inlineStr"/>
       <c r="Y453" s="2" t="inlineStr"/>
       <c r="Z453" s="2" t="inlineStr"/>
-      <c r="AA453" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the item is processed using attribute management.</t>
-        </is>
-      </c>
-      <c r="AB453" s="2" t="inlineStr">
-        <is>
-          <t>0: No.
-1: Yes, the attribute panel is displayed automatically.
-2: Yes, the attribute panel is always displayed for receipt to stock. The panel is displayed for order entry only when an attribute value is incorrect.
-3: Yes, the attribute panel is only displayed when an attribute value is incorrect. This applies both to order entry and receipt to stock.</t>
-        </is>
-      </c>
+      <c r="AA453" s="2" t="inlineStr"/>
+      <c r="AB453" s="2" t="inlineStr"/>
       <c r="AC453" s="2" t="inlineStr"/>
       <c r="AD453" s="2" t="inlineStr"/>
       <c r="AE453" s="2" t="inlineStr">
@@ -37486,11 +37120,7 @@
       <c r="X454" s="2" t="inlineStr"/>
       <c r="Y454" s="2" t="inlineStr"/>
       <c r="Z454" s="2" t="inlineStr"/>
-      <c r="AA454" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the template item used to automatically create a new item. This item contains the same settings as the template.</t>
-        </is>
-      </c>
+      <c r="AA454" s="2" t="inlineStr"/>
       <c r="AB454" s="2" t="inlineStr"/>
       <c r="AC454" s="2" t="inlineStr">
         <is>
@@ -37800,18 +37430,8 @@
       <c r="X457" s="2" t="inlineStr"/>
       <c r="Y457" s="2" t="inlineStr"/>
       <c r="Z457" s="2" t="inlineStr"/>
-      <c r="AA457" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if the sales price U/M is fixed or dynamic.</t>
-        </is>
-      </c>
-      <c r="AB457" s="2" t="inlineStr">
-        <is>
-          <t>0: Item is not a sales item
-1: Fixed
-2: Dynamic</t>
-        </is>
-      </c>
+      <c r="AA457" s="2" t="inlineStr"/>
+      <c r="AB457" s="2" t="inlineStr"/>
       <c r="AC457" s="2" t="inlineStr"/>
       <c r="AD457" s="2" t="inlineStr"/>
       <c r="AE457" s="2" t="inlineStr">
@@ -37901,13 +37521,7 @@
       <c r="X458" s="2" t="inlineStr"/>
       <c r="Y458" s="2" t="inlineStr"/>
       <c r="Z458" s="2" t="inlineStr"/>
-      <c r="AA458" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates an alternate unit of measure (U/M) for the basic U/M for an item. An unlimited number of alternate U/Ms may be defined for each item.
-Alternative U/Ms for an item are entered in (MMS015) along with an alternate U/M type, that controls how the U/M is used. In this program, also the alternative U/Ms that are to be used as default values in different situations are entered.
-When transactions are entered, the default U/M is suggested. If no U/M has been registered, the item's basic U/M is retrieved. It is, however, always possible to enter any alternate U/M manually.</t>
-        </is>
-      </c>
+      <c r="AA458" s="2" t="inlineStr"/>
       <c r="AB458" s="2" t="inlineStr"/>
       <c r="AC458" s="2" t="inlineStr">
         <is>
@@ -38085,13 +37699,7 @@
       <c r="X460" s="2" t="inlineStr"/>
       <c r="Y460" s="2" t="inlineStr"/>
       <c r="Z460" s="2" t="inlineStr"/>
-      <c r="AA460" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a general item that describes a family of items. Each stored variant within the family is automatically created as a copy of the main product in (PDS060).
-Each stored variant, i e with characteristics code 3, of the main product is given a main product number in the item file.
-The product structure of the main product is a common structure for all products in the family, i e common for all products with characteristics code 3 and the same main product.</t>
-        </is>
-      </c>
+      <c r="AA460" s="2" t="inlineStr"/>
       <c r="AB460" s="2" t="inlineStr"/>
       <c r="AC460" s="2" t="inlineStr"/>
       <c r="AD460" s="2" t="inlineStr"/>
@@ -38336,18 +37944,8 @@
       <c r="X463" s="2" t="inlineStr"/>
       <c r="Y463" s="2" t="inlineStr"/>
       <c r="Z463" s="2" t="inlineStr"/>
-      <c r="AA463" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if and how charges will be calculated.</t>
-        </is>
-      </c>
-      <c r="AB463" s="2" t="inlineStr">
-        <is>
-          <t>0: No charges are calculated
-1: Charges are calculated separately, in other words as regular order line charges.
-2: Charges are calculated but included in the item's gross price.</t>
-        </is>
-      </c>
+      <c r="AA463" s="2" t="inlineStr"/>
+      <c r="AB463" s="2" t="inlineStr"/>
       <c r="AC463" s="2" t="inlineStr"/>
       <c r="AD463" s="2" t="inlineStr"/>
       <c r="AE463" s="2" t="inlineStr">
@@ -38520,17 +38118,8 @@
       <c r="X465" s="2" t="inlineStr"/>
       <c r="Y465" s="2" t="inlineStr"/>
       <c r="Z465" s="2" t="inlineStr"/>
-      <c r="AA465" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the VAT code to be used for purchased items.</t>
-        </is>
-      </c>
-      <c r="AB465" s="2" t="inlineStr">
-        <is>
-          <t>0: VAT not used
-1-99: User-defined VAT codes</t>
-        </is>
-      </c>
+      <c r="AA465" s="2" t="inlineStr"/>
+      <c r="AB465" s="2" t="inlineStr"/>
       <c r="AC465" s="2" t="inlineStr"/>
       <c r="AD465" s="2" t="inlineStr"/>
       <c r="AE465" s="2" t="inlineStr">
@@ -38620,17 +38209,8 @@
       <c r="X466" s="2" t="inlineStr"/>
       <c r="Y466" s="2" t="inlineStr"/>
       <c r="Z466" s="2" t="inlineStr"/>
-      <c r="AA466" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the VAT code to be used for sold items.</t>
-        </is>
-      </c>
-      <c r="AB466" s="2" t="inlineStr">
-        <is>
-          <t>0: VAT not used
-1-99: User-defined VAT codes</t>
-        </is>
-      </c>
+      <c r="AA466" s="2" t="inlineStr"/>
+      <c r="AB466" s="2" t="inlineStr"/>
       <c r="AC466" s="2" t="inlineStr"/>
       <c r="AD466" s="2" t="inlineStr"/>
       <c r="AE466" s="2" t="inlineStr">
@@ -38720,11 +38300,7 @@
       <c r="X467" s="2" t="inlineStr"/>
       <c r="Y467" s="2" t="inlineStr"/>
       <c r="Z467" s="2" t="inlineStr"/>
-      <c r="AA467" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of the terms for the core return. The terms include information such as description, aging, and return date.</t>
-        </is>
-      </c>
+      <c r="AA467" s="2" t="inlineStr"/>
       <c r="AB467" s="2" t="inlineStr"/>
       <c r="AC467" s="2" t="inlineStr"/>
       <c r="AD467" s="2" t="inlineStr"/>
@@ -38811,19 +38387,8 @@
       <c r="X468" s="2" t="inlineStr"/>
       <c r="Y468" s="2" t="inlineStr"/>
       <c r="Z468" s="2" t="inlineStr"/>
-      <c r="AA468" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if the item is available as part of a core exchange program. The use of this field is essential for all items that exist in the core process.
-All remanufactured parts come with an associated core charge or core deposit. The core is a worn part (usually a larger component or subassembly such as an engine, gearbox or fuel pump) that can be rebuilt or remanufactured and brought back to specifications. When customers buy a remanufactured part, they are expected to send the current part to us as a rebuildable core. When the core is received, it will be inspected by the remanufacturing (reman) department to make sure that the core is rebuildable. The core charge is refunded once the core passes inspection.</t>
-        </is>
-      </c>
-      <c r="AB468" s="2" t="inlineStr">
-        <is>
-          <t>0: No.
-1: Supplier remanufacturing. A core entitlement is created on a purchase order, customer order, and a maintenance customer order (MCO).
-2: Internal remanufacturing. A core entitlement is created on a customer order and an MCO.</t>
-        </is>
-      </c>
+      <c r="AA468" s="2" t="inlineStr"/>
+      <c r="AB468" s="2" t="inlineStr"/>
       <c r="AC468" s="2" t="inlineStr"/>
       <c r="AD468" s="2" t="inlineStr"/>
       <c r="AE468" s="2" t="inlineStr">
@@ -38913,12 +38478,7 @@
       <c r="X469" s="2" t="inlineStr"/>
       <c r="Y469" s="2" t="inlineStr"/>
       <c r="Z469" s="2" t="inlineStr"/>
-      <c r="AA469" s="2" t="inlineStr">
-        <is>
-          <t>This setting determines the level on which catch weight will be stored. Select the check box to store catch weight on the location level. If you do not select the check box, catch weight is stored on the lot level.
-In order to store catch weight on the location level, the alternative 'Food &amp; Beverage' must be selected in the Industry field in MNS095.</t>
-        </is>
-      </c>
+      <c r="AA469" s="2" t="inlineStr"/>
       <c r="AB469" s="2" t="inlineStr"/>
       <c r="AC469" s="2" t="inlineStr"/>
       <c r="AD469" s="2" t="inlineStr"/>
@@ -39009,12 +38569,7 @@
       <c r="X470" s="2" t="inlineStr"/>
       <c r="Y470" s="2" t="inlineStr"/>
       <c r="Z470" s="2" t="inlineStr"/>
-      <c r="AA470" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the catch weight U/M.
-This is the U/M in which the catch weight of the item is saved. For Food &amp; Beverage customers who use location based catch weight, a alternative U/M for catch weight can be created.</t>
-        </is>
-      </c>
+      <c r="AA470" s="2" t="inlineStr"/>
       <c r="AB470" s="2" t="inlineStr"/>
       <c r="AC470" s="2" t="inlineStr"/>
       <c r="AD470" s="2" t="inlineStr"/>
@@ -39109,13 +38664,7 @@
       <c r="X471" s="2" t="inlineStr"/>
       <c r="Y471" s="2" t="inlineStr"/>
       <c r="Z471" s="2" t="inlineStr"/>
-      <c r="AA471" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the cost U/M.
-This is the U/M in which the cost of the item is calculated and saved. In addition to the cost the inventory accounting price, acquisition cost, average cost, and internal transfer price are defined in the cost U/M. Every item has a cost U/M specified.
-For companies not in the Food and Beverage industry, the basic U/M is always used as the cost U/M and it cannot be changed. For companies in the Food and Beverage industry, an alternate U/M in (MMS015) can be defined to be the standard U/M for cost.</t>
-        </is>
-      </c>
+      <c r="AA471" s="2" t="inlineStr"/>
       <c r="AB471" s="2" t="inlineStr"/>
       <c r="AC471" s="2" t="inlineStr"/>
       <c r="AD471" s="2" t="inlineStr"/>
@@ -39202,20 +38751,8 @@
       <c r="X472" s="2" t="inlineStr"/>
       <c r="Y472" s="2" t="inlineStr"/>
       <c r="Z472" s="2" t="inlineStr"/>
-      <c r="AA472" s="2" t="inlineStr">
-        <is>
-          <t>The field is a value that indicates whether an item is considered returnable.
-This field is mainly used for purchased items. However, since the indicator is also contained in the item master it can influence different acquisition types.</t>
-        </is>
-      </c>
-      <c r="AB472" s="2" t="inlineStr">
-        <is>
-          <t>0: The item is fully returnable.
-1: The item is returnable with restrictions. Only for information; no warnings are issued.
-2: The item is not returnable to the supplier. You can receive warning messages at customer order entry and customer order return when manually adding a material line on a work order, when entering a planned purchase order, and when entering a purchase order line. You can also receive warning message 65 on the planned purchase order to avoid an auto release.
-3: The item is not returnable to us and/or the supplier. Same as alternative 2, except that the customer order return and work order return can be blocked for this item.</t>
-        </is>
-      </c>
+      <c r="AA472" s="2" t="inlineStr"/>
+      <c r="AB472" s="2" t="inlineStr"/>
       <c r="AC472" s="2" t="inlineStr"/>
       <c r="AD472" s="2" t="inlineStr"/>
       <c r="AE472" s="2" t="inlineStr">
@@ -39297,11 +38834,7 @@
       <c r="X473" s="2" t="inlineStr"/>
       <c r="Y473" s="2" t="inlineStr"/>
       <c r="Z473" s="2" t="inlineStr"/>
-      <c r="AA473" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the supplier's ABC classification of the item.</t>
-        </is>
-      </c>
+      <c r="AA473" s="2" t="inlineStr"/>
       <c r="AB473" s="2" t="inlineStr"/>
       <c r="AC473" s="2" t="inlineStr">
         <is>
@@ -39384,20 +38917,8 @@
       <c r="X474" s="2" t="inlineStr"/>
       <c r="Y474" s="2" t="inlineStr"/>
       <c r="Z474" s="2" t="inlineStr"/>
-      <c r="AA474" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the types of returnable messages that can appear.</t>
-        </is>
-      </c>
-      <c r="AB474" s="2" t="inlineStr">
-        <is>
-          <t>0: No messages.
-1: Warning message in WO/CO entry and warning message in WO/CO return.
-2: Warning message in WO/CO entry and error message in WO/CO return.
-3: No message in WO/CO entry. Warning message in WO/CO return.
-4: No message in WO/CO entry. Error message in WO/CO return.</t>
-        </is>
-      </c>
+      <c r="AA474" s="2" t="inlineStr"/>
+      <c r="AB474" s="2" t="inlineStr"/>
       <c r="AC474" s="2" t="inlineStr"/>
       <c r="AD474" s="2" t="inlineStr"/>
       <c r="AE474" s="2" t="inlineStr">
@@ -39479,11 +39000,7 @@
       <c r="X475" s="2" t="inlineStr"/>
       <c r="Y475" s="2" t="inlineStr"/>
       <c r="Z475" s="2" t="inlineStr"/>
-      <c r="AA475" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the model or the site (for Plant Maintenance).</t>
-        </is>
-      </c>
+      <c r="AA475" s="2" t="inlineStr"/>
       <c r="AB475" s="2" t="inlineStr"/>
       <c r="AC475" s="2" t="inlineStr">
         <is>
@@ -39566,11 +39083,7 @@
       <c r="X476" s="2" t="inlineStr"/>
       <c r="Y476" s="2" t="inlineStr"/>
       <c r="Z476" s="2" t="inlineStr"/>
-      <c r="AA476" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the compatibility code, which can be used to describe similar pieces of equipment from different manufacturers or of different brands. The code can be used in statistical reports, for example, to describe market share among manufacturers for the same kind of equipment.</t>
-        </is>
-      </c>
+      <c r="AA476" s="2" t="inlineStr"/>
       <c r="AB476" s="2" t="inlineStr"/>
       <c r="AC476" s="2" t="inlineStr">
         <is>
@@ -39653,11 +39166,7 @@
       <c r="X477" s="2" t="inlineStr"/>
       <c r="Y477" s="2" t="inlineStr"/>
       <c r="Z477" s="2" t="inlineStr"/>
-      <c r="AA477" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the acceptance group, whose items have interchangeable entitlements. A core return can be created against an entitlement for any item number within the same acceptance group. The core refund will be calculated for the returned part number. Hence the core refund may be lower if the returned core is replaced from the assortment.</t>
-        </is>
-      </c>
+      <c r="AA477" s="2" t="inlineStr"/>
       <c r="AB477" s="2" t="inlineStr"/>
       <c r="AC477" s="2" t="inlineStr"/>
       <c r="AD477" s="2" t="inlineStr"/>
@@ -39736,11 +39245,7 @@
       <c r="X478" s="2" t="inlineStr"/>
       <c r="Y478" s="2" t="inlineStr"/>
       <c r="Z478" s="2" t="inlineStr"/>
-      <c r="AA478" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the item used on the core charge line when entering customer orders. It is also used on the invoice specification when entering maintenance customer orders</t>
-        </is>
-      </c>
+      <c r="AA478" s="2" t="inlineStr"/>
       <c r="AB478" s="2" t="inlineStr"/>
       <c r="AC478" s="2" t="inlineStr"/>
       <c r="AD478" s="2" t="inlineStr"/>
@@ -39819,11 +39324,7 @@
       <c r="X479" s="2" t="inlineStr"/>
       <c r="Y479" s="2" t="inlineStr"/>
       <c r="Z479" s="2" t="inlineStr"/>
-      <c r="AA479" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of a costing model for core charges. The core charge costing model is used to calculate the core charge and the core refund.</t>
-        </is>
-      </c>
+      <c r="AA479" s="2" t="inlineStr"/>
       <c r="AB479" s="2" t="inlineStr"/>
       <c r="AC479" s="2" t="inlineStr"/>
       <c r="AD479" s="2" t="inlineStr"/>
@@ -39902,11 +39403,7 @@
       <c r="X480" s="2" t="inlineStr"/>
       <c r="Y480" s="2" t="inlineStr"/>
       <c r="Z480" s="2" t="inlineStr"/>
-      <c r="AA480" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the item used by default for a core return on (OIS390/A). This is used in the internal remanufacturing process when the core return is used as a raw material in the finished product. The item number used preferably has a prefix indicating its similarity to the other item in the same acceptance group.</t>
-        </is>
-      </c>
+      <c r="AA480" s="2" t="inlineStr"/>
       <c r="AB480" s="2" t="inlineStr"/>
       <c r="AC480" s="2" t="inlineStr"/>
       <c r="AD480" s="2" t="inlineStr"/>
@@ -39985,12 +39482,7 @@
       <c r="X481" s="2" t="inlineStr"/>
       <c r="Y481" s="2" t="inlineStr"/>
       <c r="Z481" s="2" t="inlineStr"/>
-      <c r="AA481" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the item should be part of the statistical rollup. Select the check box to roll up demand from the customer order, manufacturing order, and work order according to the predefined warehouse relations in (MWS008) and (MWS009).
-The rolled up demand will be used instead of the distribution order demand when calculating annual demand, for example.</t>
-        </is>
-      </c>
+      <c r="AA481" s="2" t="inlineStr"/>
       <c r="AB481" s="2" t="inlineStr"/>
       <c r="AC481" s="2" t="inlineStr"/>
       <c r="AD481" s="2" t="inlineStr"/>
@@ -40073,18 +39565,8 @@
       <c r="X482" s="2" t="inlineStr"/>
       <c r="Y482" s="2" t="inlineStr"/>
       <c r="Z482" s="2" t="inlineStr"/>
-      <c r="AA482" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the system determines the harvested date of an item.</t>
-        </is>
-      </c>
-      <c r="AB482" s="2" t="inlineStr">
-        <is>
-          <t>0: Not used
-1: Harvested date on record
-2: Harvested date inherited</t>
-        </is>
-      </c>
+      <c r="AA482" s="2" t="inlineStr"/>
+      <c r="AB482" s="2" t="inlineStr"/>
       <c r="AC482" s="2" t="inlineStr"/>
       <c r="AD482" s="2" t="inlineStr"/>
       <c r="AE482" s="2" t="inlineStr">
@@ -40178,11 +39660,7 @@
       </c>
       <c r="Y483" s="2" t="inlineStr"/>
       <c r="Z483" s="2" t="inlineStr"/>
-      <c r="AA483" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the extended item number, which is a prolonged item number used in lists, sorting, viewing information, etc. If an extended item number is not entered, the item number is defaulted to this field. The extended item number must contain a unique value.</t>
-        </is>
-      </c>
+      <c r="AA483" s="2" t="inlineStr"/>
       <c r="AB483" s="2" t="inlineStr"/>
       <c r="AC483" s="2" t="inlineStr"/>
       <c r="AD483" s="2" t="inlineStr"/>
@@ -40265,11 +39743,7 @@
       <c r="X484" s="2" t="inlineStr"/>
       <c r="Y484" s="2" t="inlineStr"/>
       <c r="Z484" s="2" t="inlineStr"/>
-      <c r="AA484" s="2" t="inlineStr">
-        <is>
-          <t>The field provides a way to classify items that have similar quality specifications.</t>
-        </is>
-      </c>
+      <c r="AA484" s="2" t="inlineStr"/>
       <c r="AB484" s="2" t="inlineStr"/>
       <c r="AC484" s="2" t="inlineStr">
         <is>
@@ -40356,11 +39830,7 @@
       <c r="X485" s="2" t="inlineStr"/>
       <c r="Y485" s="2" t="inlineStr"/>
       <c r="Z485" s="2" t="inlineStr"/>
-      <c r="AA485" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the specific gravity (theoretical) of an item. An item's specific gravity is the ratio of its density (mass divided by volume) to the density of water. This field is not currently used in M3.</t>
-        </is>
-      </c>
+      <c r="AA485" s="2" t="inlineStr"/>
       <c r="AB485" s="2" t="inlineStr"/>
       <c r="AC485" s="2" t="inlineStr"/>
       <c r="AD485" s="2" t="inlineStr"/>
@@ -40443,11 +39913,7 @@
       <c r="X486" s="2" t="inlineStr"/>
       <c r="Y486" s="2" t="inlineStr"/>
       <c r="Z486" s="2" t="inlineStr"/>
-      <c r="AA486" s="2" t="inlineStr">
-        <is>
-          <t>This setting applies to packaged items and indicates whether quality specifications can be inherited from the related bulk item.</t>
-        </is>
-      </c>
+      <c r="AA486" s="2" t="inlineStr"/>
       <c r="AB486" s="2" t="inlineStr"/>
       <c r="AC486" s="2" t="inlineStr"/>
       <c r="AD486" s="2" t="inlineStr"/>
@@ -40530,12 +39996,7 @@
       <c r="X487" s="2" t="inlineStr"/>
       <c r="Y487" s="2" t="inlineStr"/>
       <c r="Z487" s="2" t="inlineStr"/>
-      <c r="AA487" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if the item requires quality inspection for non-lot controlled items. When selected, a quality request will be created.
-For manufacturing orders, this field is also applicable for lot controlled items with inspection code set to 0 in (MMS001). A quality request will be created but the balance ID may already be set to status '2-Approved' upon receipt. Putaway for quality-inspected item in (PMS130) is not needed.ã</t>
-        </is>
-      </c>
+      <c r="AA487" s="2" t="inlineStr"/>
       <c r="AB487" s="2" t="inlineStr"/>
       <c r="AC487" s="2" t="inlineStr"/>
       <c r="AD487" s="2" t="inlineStr"/>
@@ -40626,12 +40087,7 @@
       <c r="X488" s="2" t="inlineStr"/>
       <c r="Y488" s="2" t="inlineStr"/>
       <c r="Z488" s="2" t="inlineStr"/>
-      <c r="AA488" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the product line for an item which is used to facilitate purchase planning by grouping similar types of items from a supplier.
-Product lines are defined in (CRS099) and can be entered either for each item record on (MMS001/E) or for each item-warehouse record on (MMS002/F), depending on the value of the product line level on (CRS780/H).</t>
-        </is>
-      </c>
+      <c r="AA488" s="2" t="inlineStr"/>
       <c r="AB488" s="2" t="inlineStr"/>
       <c r="AC488" s="2" t="inlineStr">
         <is>
@@ -40714,12 +40170,7 @@
       <c r="X489" s="2" t="inlineStr"/>
       <c r="Y489" s="2" t="inlineStr"/>
       <c r="Z489" s="2" t="inlineStr"/>
-      <c r="AA489" s="2" t="inlineStr">
-        <is>
-          <t>This field indicates the ID of the composition group.
-The composition group is used as the highest entity in a structure of custom field groups and custom fields. It is used for composition information input in (CMS474).</t>
-        </is>
-      </c>
+      <c r="AA489" s="2" t="inlineStr"/>
       <c r="AB489" s="2" t="inlineStr"/>
       <c r="AC489" s="2" t="inlineStr">
         <is>
@@ -40802,13 +40253,7 @@
       <c r="X490" s="2" t="inlineStr"/>
       <c r="Y490" s="2" t="inlineStr"/>
       <c r="Z490" s="2" t="inlineStr"/>
-      <c r="AA490" s="2" t="inlineStr">
-        <is>
-          <t>Select this check box if an item is sublot controlled.
-The prerequisites for the item include: being defined as an Inventory accounting item and having a Lot control method.
-Sublots are unique identities used to capture the catch weight of an individual packaged item.</t>
-        </is>
-      </c>
+      <c r="AA490" s="2" t="inlineStr"/>
       <c r="AB490" s="2" t="inlineStr"/>
       <c r="AC490" s="2" t="inlineStr"/>
       <c r="AD490" s="2" t="inlineStr"/>
@@ -40891,12 +40336,7 @@
       <c r="X491" s="2" t="inlineStr"/>
       <c r="Y491" s="2" t="inlineStr"/>
       <c r="Z491" s="2" t="inlineStr"/>
-      <c r="AA491" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the identifier for the sublot policy where parameters are defined for the Reference sublot ID field. A sublot policy is assigned to an item in (MMS001) when that item is sublot controlled.
-When defining a sublot policy, you may indicate that the Reference sublot ID is auto-populated upon creation. Also, you may indicate that the value in the Reference sublot ID field is protected, i.e. cannot be changed after being established.</t>
-        </is>
-      </c>
+      <c r="AA491" s="2" t="inlineStr"/>
       <c r="AB491" s="2" t="inlineStr"/>
       <c r="AC491" s="2" t="inlineStr">
         <is>
@@ -40979,18 +40419,8 @@
       <c r="X492" s="2" t="inlineStr"/>
       <c r="Y492" s="2" t="inlineStr"/>
       <c r="Z492" s="2" t="inlineStr"/>
-      <c r="AA492" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if the item, based on its price source, contributes or not to the supplier rebate generating and/or paying total.</t>
-        </is>
-      </c>
-      <c r="AB492" s="2" t="inlineStr">
-        <is>
-          <t>0: Does not affect
-1: Generating
-2: Paying</t>
-        </is>
-      </c>
+      <c r="AA492" s="2" t="inlineStr"/>
+      <c r="AB492" s="2" t="inlineStr"/>
       <c r="AC492" s="2" t="inlineStr"/>
       <c r="AD492" s="2" t="inlineStr"/>
       <c r="AE492" s="2" t="inlineStr">
@@ -41076,12 +40506,7 @@
       <c r="X493" s="2" t="inlineStr"/>
       <c r="Y493" s="2" t="inlineStr"/>
       <c r="Z493" s="2" t="inlineStr"/>
-      <c r="AA493" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates company number, which is the primary identity in all files in the M3 system. The purpose of this is to be able to handle, in the same database, several companies completely or partially separated.
-A maximum of 999 companies may be handled in the same database.</t>
-        </is>
-      </c>
+      <c r="AA493" s="2" t="inlineStr"/>
       <c r="AB493" s="2" t="inlineStr"/>
       <c r="AC493" s="2" t="inlineStr">
         <is>
@@ -41204,13 +40629,7 @@
         </is>
       </c>
       <c r="Z494" s="2" t="inlineStr"/>
-      <c r="AA494" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the warehouse ID.
-Warehouse is a stock zone which is used to distinguish different geographical locations within a company. The warehouse is used as a planning level for material and production. Stock zones, stock locations and items are connected to the warehouse.
-Warehouses are created in (MMS005).</t>
-        </is>
-      </c>
+      <c r="AA494" s="2" t="inlineStr"/>
       <c r="AB494" s="2" t="inlineStr"/>
       <c r="AC494" s="2" t="inlineStr">
         <is>
@@ -41329,12 +40748,7 @@
       </c>
       <c r="Y495" s="2" t="inlineStr"/>
       <c r="Z495" s="2" t="inlineStr"/>
-      <c r="AA495" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the item number (for Maintenance, the item number or equipment number), which is a unique ID for an individual item.
-Items are entered and maintained in (MMS001). Item number can consist up to 15 alphanumeric characters.</t>
-        </is>
-      </c>
+      <c r="AA495" s="2" t="inlineStr"/>
       <c r="AB495" s="2" t="inlineStr"/>
       <c r="AC495" s="2" t="inlineStr">
         <is>
@@ -41429,12 +40843,7 @@
       <c r="X496" s="2" t="inlineStr"/>
       <c r="Y496" s="2" t="inlineStr"/>
       <c r="Z496" s="2" t="inlineStr"/>
-      <c r="AA496" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the approved on-hand balance quantity. The quantity is the total of all balance identities with status 2 for each warehouse.
-The quantity is expressed in the in the basic unit of measure of the item.</t>
-        </is>
-      </c>
+      <c r="AA496" s="2" t="inlineStr"/>
       <c r="AB496" s="2" t="inlineStr"/>
       <c r="AC496" s="2" t="inlineStr"/>
       <c r="AD496" s="2" t="inlineStr"/>
@@ -41529,12 +40938,7 @@
       <c r="X497" s="2" t="inlineStr"/>
       <c r="Y497" s="2" t="inlineStr"/>
       <c r="Z497" s="2" t="inlineStr"/>
-      <c r="AA497" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the on-hand balance under inspection per warehouse/item.
-This balance is always shown in the basic unit of the item and it cannot be allocated automatically. It is the total of all on-hand balance identities that have status 1.</t>
-        </is>
-      </c>
+      <c r="AA497" s="2" t="inlineStr"/>
       <c r="AB497" s="2" t="inlineStr"/>
       <c r="AC497" s="2" t="inlineStr"/>
       <c r="AD497" s="2" t="inlineStr"/>
@@ -41629,12 +41033,7 @@
       <c r="X498" s="2" t="inlineStr"/>
       <c r="Y498" s="2" t="inlineStr"/>
       <c r="Z498" s="2" t="inlineStr"/>
-      <c r="AA498" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the rejected on-hand balance for each warehouse and item.
-The on-hand balance is always expressed in the item's basic U/M, and the quantity may never be allocated. The rejected on-hand balance is the total of all the identities with status 3.</t>
-        </is>
-      </c>
+      <c r="AA498" s="2" t="inlineStr"/>
       <c r="AB498" s="2" t="inlineStr"/>
       <c r="AC498" s="2" t="inlineStr"/>
       <c r="AD498" s="2" t="inlineStr"/>
@@ -41729,12 +41128,7 @@
       <c r="X499" s="2" t="inlineStr"/>
       <c r="Y499" s="2" t="inlineStr"/>
       <c r="Z499" s="2" t="inlineStr"/>
-      <c r="AA499" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the part of the physical stock that is marked, manually or automatically, to be used in issues to requisitions, manufacturing and/or customer orders.
-The information is stored for each balance identity and for each item.</t>
-        </is>
-      </c>
+      <c r="AA499" s="2" t="inlineStr"/>
       <c r="AB499" s="2" t="inlineStr"/>
       <c r="AC499" s="2" t="inlineStr"/>
       <c r="AD499" s="2" t="inlineStr"/>
@@ -41829,11 +41223,7 @@
       <c r="X500" s="2" t="inlineStr"/>
       <c r="Y500" s="2" t="inlineStr"/>
       <c r="Z500" s="2" t="inlineStr"/>
-      <c r="AA500" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the quantity of the on-hand balance that is available for allocation.</t>
-        </is>
-      </c>
+      <c r="AA500" s="2" t="inlineStr"/>
       <c r="AB500" s="2" t="inlineStr"/>
       <c r="AC500" s="2" t="inlineStr"/>
       <c r="AD500" s="2" t="inlineStr"/>
@@ -41920,12 +41310,7 @@
       <c r="X501" s="2" t="inlineStr"/>
       <c r="Y501" s="2" t="inlineStr"/>
       <c r="Z501" s="2" t="inlineStr"/>
-      <c r="AA501" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the part of the allocated quantity that is printed on a picking list, but not yet reported as picked.
-The quantity is expressed in the basic unit of measure of the item.</t>
-        </is>
-      </c>
+      <c r="AA501" s="2" t="inlineStr"/>
       <c r="AB501" s="2" t="inlineStr"/>
       <c r="AC501" s="2" t="inlineStr"/>
       <c r="AD501" s="2" t="inlineStr"/>
@@ -42016,23 +41401,8 @@
       <c r="X502" s="2" t="inlineStr"/>
       <c r="Y502" s="2" t="inlineStr"/>
       <c r="Z502" s="2" t="inlineStr"/>
-      <c r="AA502" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how containers are managed. Container management is used to account for items in inventory using a container ID, such as a pallet number.</t>
-        </is>
-      </c>
-      <c r="AB502" s="2" t="inlineStr">
-        <is>
-          <t>0: Containers are not used.
-1: Containers are used. No verification that the container exists in the container master.
-2: Containers are used. Verification that the container exists in the container master.
-3: Containers are used. These must be defined as lot numbers. An existence check is performed against the lot master file.
-4: Same as method 1, but the container can only be stored in one location at a time.
-5: Same as method 2, but the container can only be stored in one location at a time.
-6: Same as method 3, but the container can only be stored in one location at a time.
-7: The container number indicates a package in stock (MMS470) and can only be stored in one location at a time.</t>
-        </is>
-      </c>
+      <c r="AA502" s="2" t="inlineStr"/>
+      <c r="AB502" s="2" t="inlineStr"/>
       <c r="AC502" s="2" t="inlineStr"/>
       <c r="AD502" s="2" t="inlineStr"/>
       <c r="AE502" s="2" t="inlineStr">
@@ -42142,22 +41512,8 @@
         </is>
       </c>
       <c r="Z503" s="2" t="inlineStr"/>
-      <c r="AA503" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how allocation is carried out for each item/warehouse combination.</t>
-        </is>
-      </c>
-      <c r="AB503" s="2" t="inlineStr">
-        <is>
-          <t>1: Manual allocation.
-2: Automatic allocation using the allocation table if one is created for the item. If there is no table, allocation is done using FIFO without considering the location type.
-3: Automatic allocation for the location entered for each item/warehouse or the location specified for the order line (if one is specified). This allows the user to force allocation from a particular location. Overallocation is allowed for each location but not for each warehouse. This method cannot be used if the item is lot controlled.
-4: Automatic allocation for the location entered for each item/warehouse or the location specified for the order line (if one is specified). This allows the user to force allocation from a particular location. Allocation is done without a balance check. This method cannot be used if the item is lot controlled.
-5: Automatic allocation using the allocation table, and total required quantity must be allocatable on the same lot. This method can only be used in combination with lot control.
-6: Soft automatic allocation with a check against allocatable balance on warehouse level. See Note 1.
-7: Soft automatic allocation without balance check. See Note 1.</t>
-        </is>
-      </c>
+      <c r="AA503" s="2" t="inlineStr"/>
+      <c r="AB503" s="2" t="inlineStr"/>
       <c r="AC503" s="2" t="inlineStr"/>
       <c r="AD503" s="2" t="inlineStr"/>
       <c r="AE503" s="2" t="inlineStr">
@@ -42271,18 +41627,8 @@
         </is>
       </c>
       <c r="Z504" s="2" t="inlineStr"/>
-      <c r="AA504" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the storage method for each item/warehouse, and determines how the item is distributed at different locations.</t>
-        </is>
-      </c>
-      <c r="AB504" s="2" t="inlineStr">
-        <is>
-          <t>1: Single location
-2: Multiple location
-3: Multiple location where reorder points are used.</t>
-        </is>
-      </c>
+      <c r="AA504" s="2" t="inlineStr"/>
+      <c r="AB504" s="2" t="inlineStr"/>
       <c r="AC504" s="2" t="inlineStr"/>
       <c r="AD504" s="2" t="inlineStr"/>
       <c r="AE504" s="2" t="inlineStr">
@@ -42392,25 +41738,8 @@
         </is>
       </c>
       <c r="Z505" s="2" t="inlineStr"/>
-      <c r="AA505" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates when and how material issues to work orders and manufacturing orders are reported.</t>
-        </is>
-      </c>
-      <c r="AB505" s="2" t="inlineStr">
-        <is>
-          <t>1: Material is issued against a picking list according to the allocation method used. Note that this method should be used if the item is order-initiated.
-2: Material is issued against a requisition and reported manually.
-3: Material is issued automatically based on the quantity reported as put away. The issue is always made from the location entered per item/warehouse.
-4: Material is issued automatically based on the quantity reported as produced in the operation where it is used. The issue is always made from the location entered per item/warehouse.
-5: Material is issued automatically based on the quantity reported as put away. The issue is made from the location entered in the work center for the operation to which the material is connected.
-6: Material is issued automatically based on the quantity that is reported as produced in the operation where it is used. The issue is made from the location specified in the work center for the operation to which the material is connected.
-7: The system sets this option to exclude the issue of the bulk item for child process orders or pack orders in (PMS060).
-8: Material is reported on one manufacturing order and issued to the next order by an external manufacturing execution system.
-9: Material is issued automatically by an external manufacturing execution system.
-0: Material issue method 0 may be used for non-stocked items for work orders in (MOS101). The material transaction status is set to 90 as soon as the transaction is finished.</t>
-        </is>
-      </c>
+      <c r="AA505" s="2" t="inlineStr"/>
+      <c r="AB505" s="2" t="inlineStr"/>
       <c r="AC505" s="2" t="inlineStr"/>
       <c r="AD505" s="2" t="inlineStr"/>
       <c r="AE505" s="2" t="inlineStr">
@@ -42500,11 +41829,7 @@
       <c r="X506" s="2" t="inlineStr"/>
       <c r="Y506" s="2" t="inlineStr"/>
       <c r="Z506" s="2" t="inlineStr"/>
-      <c r="AA506" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates an optional text for the warehouse/item.</t>
-        </is>
-      </c>
+      <c r="AA506" s="2" t="inlineStr"/>
       <c r="AB506" s="2" t="inlineStr"/>
       <c r="AC506" s="2" t="inlineStr"/>
       <c r="AD506" s="2" t="inlineStr"/>
@@ -42694,13 +42019,7 @@
       <c r="X508" s="2" t="inlineStr"/>
       <c r="Y508" s="2" t="inlineStr"/>
       <c r="Z508" s="2" t="inlineStr"/>
-      <c r="AA508" s="2" t="inlineStr">
-        <is>
-          <t>The field contains all reservations from the current date and forward.
-Reservations that belong to planned orders are not included. Reservations prior to the current date are accumulated in another field.
-Note that the field 'Upd on-ord/res in (CRS701) defines if firm planned orders are included.</t>
-        </is>
-      </c>
+      <c r="AA508" s="2" t="inlineStr"/>
       <c r="AB508" s="2" t="inlineStr"/>
       <c r="AC508" s="2" t="inlineStr"/>
       <c r="AD508" s="2" t="inlineStr"/>
@@ -42795,11 +42114,7 @@
       <c r="X509" s="2" t="inlineStr"/>
       <c r="Y509" s="2" t="inlineStr"/>
       <c r="Z509" s="2" t="inlineStr"/>
-      <c r="AA509" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the portion of the total reserved quantity which is delayed. Probable reservations from planned orders are not included.</t>
-        </is>
-      </c>
+      <c r="AA509" s="2" t="inlineStr"/>
       <c r="AB509" s="2" t="inlineStr"/>
       <c r="AC509" s="2" t="inlineStr"/>
       <c r="AD509" s="2" t="inlineStr"/>
@@ -42977,14 +42292,7 @@
       <c r="X511" s="2" t="inlineStr"/>
       <c r="Y511" s="2" t="inlineStr"/>
       <c r="Z511" s="2" t="inlineStr"/>
-      <c r="AA511" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the latest stock receipt date for the current ID. It is updated according to the rules for each ID.
-For example, the following is true for items and warehouses: The latest stock receipt date is only updated in connection with put-away in reference to purchasing, manufacturing or distribution.
-For a balance identity (warehouse/item/location/lot/container/receiving number), the field is updated whenever stock is added for a transaction date later than the existing last received date, except for transaction type 90 (stock count).
-This is different than updates for the item/warehouse level because, for example, a move order does not change the stock in the warehouse, only where it is in the warehouse, but it may change the stock in a particular location.</t>
-        </is>
-      </c>
+      <c r="AA511" s="2" t="inlineStr"/>
       <c r="AB511" s="2" t="inlineStr"/>
       <c r="AC511" s="2" t="inlineStr"/>
       <c r="AD511" s="2" t="inlineStr"/>
@@ -43075,11 +42383,7 @@
       <c r="X512" s="2" t="inlineStr"/>
       <c r="Y512" s="2" t="inlineStr"/>
       <c r="Z512" s="2" t="inlineStr"/>
-      <c r="AA512" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the date of the most recent issue of this record. Physical inventory does not affect this date.</t>
-        </is>
-      </c>
+      <c r="AA512" s="2" t="inlineStr"/>
       <c r="AB512" s="2" t="inlineStr"/>
       <c r="AC512" s="2" t="inlineStr"/>
       <c r="AD512" s="2" t="inlineStr"/>
@@ -43170,11 +42474,7 @@
       <c r="X513" s="2" t="inlineStr"/>
       <c r="Y513" s="2" t="inlineStr"/>
       <c r="Z513" s="2" t="inlineStr"/>
-      <c r="AA513" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the date an inventory of the item was last performed.</t>
-        </is>
-      </c>
+      <c r="AA513" s="2" t="inlineStr"/>
       <c r="AB513" s="2" t="inlineStr"/>
       <c r="AC513" s="2" t="inlineStr"/>
       <c r="AD513" s="2" t="inlineStr"/>
@@ -43348,12 +42648,7 @@
       <c r="X515" s="2" t="inlineStr"/>
       <c r="Y515" s="2" t="inlineStr"/>
       <c r="Z515" s="2" t="inlineStr"/>
-      <c r="AA515" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the applicable physical inventory cycle.
-The inventory cycle contains information as to how many days are to elapse before inventory for the item is once again taken.</t>
-        </is>
-      </c>
+      <c r="AA515" s="2" t="inlineStr"/>
       <c r="AB515" s="2" t="inlineStr"/>
       <c r="AC515" s="2" t="inlineStr"/>
       <c r="AD515" s="2" t="inlineStr"/>
@@ -43440,11 +42735,7 @@
       <c r="X516" s="2" t="inlineStr"/>
       <c r="Y516" s="2" t="inlineStr"/>
       <c r="Z516" s="2" t="inlineStr"/>
-      <c r="AA516" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many records have been counted in inventory or are part of the current inventory.</t>
-        </is>
-      </c>
+      <c r="AA516" s="2" t="inlineStr"/>
       <c r="AB516" s="2" t="inlineStr"/>
       <c r="AC516" s="2" t="inlineStr"/>
       <c r="AD516" s="2" t="inlineStr"/>
@@ -43539,12 +42830,7 @@
       <c r="X517" s="2" t="inlineStr"/>
       <c r="Y517" s="2" t="inlineStr"/>
       <c r="Z517" s="2" t="inlineStr"/>
-      <c r="AA517" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the running year's usage and is based on historical item statistics.
-The historical item statistics are calculated based on a running year, rather than a calendar year.</t>
-        </is>
-      </c>
+      <c r="AA517" s="2" t="inlineStr"/>
       <c r="AB517" s="2" t="inlineStr"/>
       <c r="AC517" s="2" t="inlineStr"/>
       <c r="AD517" s="2" t="inlineStr"/>
@@ -43639,11 +42925,7 @@
       <c r="X518" s="2" t="inlineStr"/>
       <c r="Y518" s="2" t="inlineStr"/>
       <c r="Z518" s="2" t="inlineStr"/>
-      <c r="AA518" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the simulated average on-hand balance based on the input data for the calculation. The value is calculated by (MMS220).</t>
-        </is>
-      </c>
+      <c r="AA518" s="2" t="inlineStr"/>
       <c r="AB518" s="2" t="inlineStr"/>
       <c r="AC518" s="2" t="inlineStr"/>
       <c r="AD518" s="2" t="inlineStr"/>
@@ -43738,11 +43020,7 @@
       <c r="X519" s="2" t="inlineStr"/>
       <c r="Y519" s="2" t="inlineStr"/>
       <c r="Z519" s="2" t="inlineStr"/>
-      <c r="AA519" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the calculated on-hand balance at the end of the lead time based on all transactions which exist in the material plan. Note that forecast is not included. The field is used in the MRP for re-orderpoint items.</t>
-        </is>
-      </c>
+      <c r="AA519" s="2" t="inlineStr"/>
       <c r="AB519" s="2" t="inlineStr"/>
       <c r="AC519" s="2" t="inlineStr"/>
       <c r="AD519" s="2" t="inlineStr"/>
@@ -43957,13 +43235,7 @@
       <c r="X521" s="2" t="inlineStr"/>
       <c r="Y521" s="2" t="inlineStr"/>
       <c r="Z521" s="2" t="inlineStr"/>
-      <c r="AA521" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the buyer normally responsible for purchasing.
-The buyer can, for example, be responsible for purchase orders, agreements, item/supplier combinations or item/warehouse combinations.
-The specified buyer for each item/warehouse is copied to the planned orders generated by M3.</t>
-        </is>
-      </c>
+      <c r="AA521" s="2" t="inlineStr"/>
       <c r="AB521" s="2" t="inlineStr"/>
       <c r="AC521" s="2" t="inlineStr"/>
       <c r="AD521" s="2" t="inlineStr"/>
@@ -44181,12 +43453,7 @@
         </is>
       </c>
       <c r="Z523" s="2" t="inlineStr"/>
-      <c r="AA523" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates group warehouses of the same type.
-In addition to being used as classification, the term also determines whether the warehouse balance should be accumulated by facility level.</t>
-        </is>
-      </c>
+      <c r="AA523" s="2" t="inlineStr"/>
       <c r="AB523" s="2" t="inlineStr"/>
       <c r="AC523" s="2" t="inlineStr">
         <is>
@@ -44297,12 +43564,7 @@
         </is>
       </c>
       <c r="Z524" s="2" t="inlineStr"/>
-      <c r="AA524" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the warehouse subtype, and is used to differentiate warehouses within each type.
-The field is defined in a separate table and is used for informational purposes only.</t>
-        </is>
-      </c>
+      <c r="AA524" s="2" t="inlineStr"/>
       <c r="AB524" s="2" t="inlineStr"/>
       <c r="AC524" s="2" t="inlineStr">
         <is>
@@ -44397,12 +43659,7 @@
       <c r="X525" s="2" t="inlineStr"/>
       <c r="Y525" s="2" t="inlineStr"/>
       <c r="Z525" s="2" t="inlineStr"/>
-      <c r="AA525" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the inventory statistics are to be saved.
-The code is defined in a separate table and can be specified for each item/warehouse.</t>
-        </is>
-      </c>
+      <c r="AA525" s="2" t="inlineStr"/>
       <c r="AB525" s="2" t="inlineStr"/>
       <c r="AC525" s="2" t="inlineStr"/>
       <c r="AD525" s="2" t="inlineStr"/>
@@ -44493,11 +43750,7 @@
       <c r="X526" s="2" t="inlineStr"/>
       <c r="Y526" s="2" t="inlineStr"/>
       <c r="Z526" s="2" t="inlineStr"/>
-      <c r="AA526" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how to group similar items distributed to the same warehouse.</t>
-        </is>
-      </c>
+      <c r="AA526" s="2" t="inlineStr"/>
       <c r="AB526" s="2" t="inlineStr"/>
       <c r="AC526" s="2" t="inlineStr">
         <is>
@@ -44709,16 +43962,7 @@
       <c r="X528" s="2" t="inlineStr"/>
       <c r="Y528" s="2" t="inlineStr"/>
       <c r="Z528" s="2" t="inlineStr"/>
-      <c r="AA528" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of a stock zone which is used to divide a warehouse into different areas.
-The stock zone is specified in three different programs, depending on the desired purpose:
-1. Stock zone per location (MMS010) is a central search key for making inquiries regarding locations, for example when searching for available locations (using (MMS010), system directed put-away or (MMS160)). Entering a stock zone in (MMS010) is mandatory.
-2. Stock zone per balance ID (MWS060) is automatically retrieved from the location when the balance ID is created and is used to split an order into several picking lists (one picking list per stock zone). The printers used to print the picking lists are defined per stock zone in (MMS040).
-3. Stock zone per item/warehouse (MMS002) is used to suggest locations when performing stock receipt. The stock zone entered here is also suggested as the From stock zone on proposed replenishment orders (MMS170).
-The stock zone in (MMS002) is entered manually and is not mandatory.</t>
-        </is>
-      </c>
+      <c r="AA528" s="2" t="inlineStr"/>
       <c r="AB528" s="2" t="inlineStr"/>
       <c r="AC528" s="2" t="inlineStr">
         <is>
@@ -44809,12 +44053,7 @@
       <c r="X529" s="2" t="inlineStr"/>
       <c r="Y529" s="2" t="inlineStr"/>
       <c r="Z529" s="2" t="inlineStr"/>
-      <c r="AA529" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of balance IDs.
-This an accumulator which contains information on the number of balance identities that exists per warehouse.</t>
-        </is>
-      </c>
+      <c r="AA529" s="2" t="inlineStr"/>
       <c r="AB529" s="2" t="inlineStr"/>
       <c r="AC529" s="2" t="inlineStr"/>
       <c r="AD529" s="2" t="inlineStr"/>
@@ -44909,12 +44148,7 @@
       <c r="X530" s="2" t="inlineStr"/>
       <c r="Y530" s="2" t="inlineStr"/>
       <c r="Z530" s="2" t="inlineStr"/>
-      <c r="AA530" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the minimum issue multiple.
-The value is checked in connection with order entry of the item and warehouse combination.</t>
-        </is>
-      </c>
+      <c r="AA530" s="2" t="inlineStr"/>
       <c r="AB530" s="2" t="inlineStr"/>
       <c r="AC530" s="2" t="inlineStr"/>
       <c r="AD530" s="2" t="inlineStr"/>
@@ -45009,12 +44243,7 @@
       <c r="X531" s="2" t="inlineStr"/>
       <c r="Y531" s="2" t="inlineStr"/>
       <c r="Z531" s="2" t="inlineStr"/>
-      <c r="AA531" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a group of locations based on the characteristics (size etc.).
-The information can be used to locate unoccupied locations of the right size in connection with receipt of goods, for example.</t>
-        </is>
-      </c>
+      <c r="AA531" s="2" t="inlineStr"/>
       <c r="AB531" s="2" t="inlineStr"/>
       <c r="AC531" s="2" t="inlineStr">
         <is>
@@ -45105,14 +44334,7 @@
       <c r="X532" s="2" t="inlineStr"/>
       <c r="Y532" s="2" t="inlineStr"/>
       <c r="Z532" s="2" t="inlineStr"/>
-      <c r="AA532" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a specific piece of warehouse equipment used in a warehouse.
-This is used when special equipment is required for inhouse movements of certain items, or to/from certain locations.
-Warehouse equipment can be set for each item/warehouse in (MMS002/G) and location in (MMS010/F). Out of these two, the item/warehouse has the highest priority.
-When the special equipment is required for an issue, separate picking lists are created in M3 for different pieces of warehouse equipment.</t>
-        </is>
-      </c>
+      <c r="AA532" s="2" t="inlineStr"/>
       <c r="AB532" s="2" t="inlineStr"/>
       <c r="AC532" s="2" t="inlineStr"/>
       <c r="AD532" s="2" t="inlineStr"/>
@@ -45223,11 +44445,7 @@
         </is>
       </c>
       <c r="Z533" s="2" t="inlineStr"/>
-      <c r="AA533" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the planning policy which contains a number of rules that determine how generation of planned orders, action messages and warning messages are to be applied.</t>
-        </is>
-      </c>
+      <c r="AA533" s="2" t="inlineStr"/>
       <c r="AB533" s="2" t="inlineStr"/>
       <c r="AC533" s="2" t="inlineStr"/>
       <c r="AD533" s="2" t="inlineStr"/>
@@ -45318,11 +44536,7 @@
       <c r="X534" s="2" t="inlineStr"/>
       <c r="Y534" s="2" t="inlineStr"/>
       <c r="Z534" s="2" t="inlineStr"/>
-      <c r="AA534" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates an optional ABC class that is to be used to group item numbers per warehouse according to the definition per installation.</t>
-        </is>
-      </c>
+      <c r="AA534" s="2" t="inlineStr"/>
       <c r="AB534" s="2" t="inlineStr"/>
       <c r="AC534" s="2" t="inlineStr">
         <is>
@@ -45441,14 +44655,7 @@
         </is>
       </c>
       <c r="Z535" s="2" t="inlineStr"/>
-      <c r="AA535" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a code, usually A, B or C, used to group items according to how they affect the total sales volume (the sales volume is the product of an item's annual usage multiplied by a particular price).
-The ABC class is defined in the parameter file.
-ABC class sales volume can also be used as selection criteria when printing reports, taking inventory or determining stock control values.
-The sales volume is updated per warehouse/item, either automatically or manually depending upon the method you have chosen.</t>
-        </is>
-      </c>
+      <c r="AA535" s="2" t="inlineStr"/>
       <c r="AB535" s="2" t="inlineStr"/>
       <c r="AC535" s="2" t="inlineStr">
         <is>
@@ -45547,11 +44754,7 @@
       <c r="X536" s="2" t="inlineStr"/>
       <c r="Y536" s="2" t="inlineStr"/>
       <c r="Z536" s="2" t="inlineStr"/>
-      <c r="AA536" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to automatically update the ABC class for the item/warehouse combination. If you do not select the check box, the ABC class must be manually updated.</t>
-        </is>
-      </c>
+      <c r="AA536" s="2" t="inlineStr"/>
       <c r="AB536" s="2" t="inlineStr"/>
       <c r="AC536" s="2" t="inlineStr"/>
       <c r="AD536" s="2" t="inlineStr"/>
@@ -45666,16 +44869,7 @@
         </is>
       </c>
       <c r="Z537" s="2" t="inlineStr"/>
-      <c r="AA537" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ABC class frequency code, which is a code from A to J.
-This code is used for two main purposes:
-The code can also be used as selection criteria.
-The code is based on one of the following (applies to 1 and 2 above):
-When the ABC class frequency is calculated automatically as in (MMS675), enter the division basis to be used.
-The ABC class frequency is updated for each item/warehouse. Depending on the ABC frequency method, this is done manually or automatically.</t>
-        </is>
-      </c>
+      <c r="AA537" s="2" t="inlineStr"/>
       <c r="AB537" s="2" t="inlineStr"/>
       <c r="AC537" s="2" t="inlineStr">
         <is>
@@ -45774,11 +44968,7 @@
       <c r="X538" s="2" t="inlineStr"/>
       <c r="Y538" s="2" t="inlineStr"/>
       <c r="Z538" s="2" t="inlineStr"/>
-      <c r="AA538" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to automatically update the ABC class for the item/warehouse combination. If you do not select the check box, the ABC class must be manually updated.</t>
-        </is>
-      </c>
+      <c r="AA538" s="2" t="inlineStr"/>
       <c r="AB538" s="2" t="inlineStr"/>
       <c r="AC538" s="2" t="inlineStr"/>
       <c r="AD538" s="2" t="inlineStr"/>
@@ -45893,13 +45083,7 @@
         </is>
       </c>
       <c r="Z539" s="2" t="inlineStr"/>
-      <c r="AA539" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates group items based on their contribution margin for each item/warehouse.
-The value can be set manually or automatically. The valid values are A to J.
-When grouping is performed automatically, the contribution is calculated by multiplying the sales quantity by the contribution margin for each unit. The contribution margin is calculated by subtracting the item file's sales price or a price list price with the specified costing price.</t>
-        </is>
-      </c>
+      <c r="AA539" s="2" t="inlineStr"/>
       <c r="AB539" s="2" t="inlineStr"/>
       <c r="AC539" s="2" t="inlineStr">
         <is>
@@ -45998,11 +45182,7 @@
       <c r="X540" s="2" t="inlineStr"/>
       <c r="Y540" s="2" t="inlineStr"/>
       <c r="Z540" s="2" t="inlineStr"/>
-      <c r="AA540" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to automatically update the ABC class for the item/warehouse combination. If you do not select the check box, the ABC class must be manually updated.</t>
-        </is>
-      </c>
+      <c r="AA540" s="2" t="inlineStr"/>
       <c r="AB540" s="2" t="inlineStr"/>
       <c r="AC540" s="2" t="inlineStr"/>
       <c r="AD540" s="2" t="inlineStr"/>
@@ -46093,18 +45273,7 @@
       <c r="X541" s="2" t="inlineStr"/>
       <c r="Y541" s="2" t="inlineStr"/>
       <c r="Z541" s="2" t="inlineStr"/>
-      <c r="AA541" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many days remain before a replenishment order must be performed.
-If the value is negative it indicates the number of days, theoretically, that has passed since the order should have been released/performed.
-The priority value is calculated automatically when a planned or actual transaction occurs for the warehouse/item according to the following formula:
-Priority value = run-out time - lead time
-Where:
-DU is the greatest of DU1 and DU2 according to the following:
-DU1:
-DU2:</t>
-        </is>
-      </c>
+      <c r="AA541" s="2" t="inlineStr"/>
       <c r="AB541" s="2" t="inlineStr"/>
       <c r="AC541" s="2" t="inlineStr"/>
       <c r="AD541" s="2" t="inlineStr"/>
@@ -46195,14 +45364,7 @@
       <c r="X542" s="2" t="inlineStr"/>
       <c r="Y542" s="2" t="inlineStr"/>
       <c r="Z542" s="2" t="inlineStr"/>
-      <c r="AA542" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many days usage the on-hand balance can be expected to cover if a replenishment does not take place.
-The formula used is:
-Run-out time = On-hand balance / Daily requirement
-The daily requirement is determined by selecting the larger of forecasted or reserved quantity up to the end of the lead time and dividing it by the lead time.</t>
-        </is>
-      </c>
+      <c r="AA542" s="2" t="inlineStr"/>
       <c r="AB542" s="2" t="inlineStr"/>
       <c r="AC542" s="2" t="inlineStr"/>
       <c r="AD542" s="2" t="inlineStr"/>
@@ -46301,12 +45463,7 @@
       <c r="X543" s="2" t="inlineStr"/>
       <c r="Y543" s="2" t="inlineStr"/>
       <c r="Z543" s="2" t="inlineStr"/>
-      <c r="AA543" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the reorder point. When the on-hand balance is equal to or below the level displayed in this field, a planned order is automatically created.
-The reorder point is calculated either manually or as the safety stock plus usage during the lead time.</t>
-        </is>
-      </c>
+      <c r="AA543" s="2" t="inlineStr"/>
       <c r="AB543" s="2" t="inlineStr"/>
       <c r="AC543" s="2" t="inlineStr"/>
       <c r="AD543" s="2" t="inlineStr"/>
@@ -46401,21 +45558,8 @@
       <c r="X544" s="2" t="inlineStr"/>
       <c r="Y544" s="2" t="inlineStr"/>
       <c r="Z544" s="2" t="inlineStr"/>
-      <c r="AA544" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the method used to determine the reorder point.</t>
-        </is>
-      </c>
-      <c r="AB544" s="2" t="inlineStr">
-        <is>
-          <t>0: Set manually. A reorder point value of 0 is not included in the reorder point calculation.
-1: Calculated automatically according to the formula: Reorder point = Safety stock + (daily usage * lead time).
-2: Reorder point is always 0 (zero).
-3: Defined by an external system.
-4: Automatically according to Poisson table.
-5: Average quantity per issue. The reorder point equals the demand during the last 12 months / Number of issues last 12 months.</t>
-        </is>
-      </c>
+      <c r="AA544" s="2" t="inlineStr"/>
+      <c r="AB544" s="2" t="inlineStr"/>
       <c r="AC544" s="2" t="inlineStr"/>
       <c r="AD544" s="2" t="inlineStr"/>
       <c r="AE544" s="2" t="inlineStr">
@@ -46509,12 +45653,7 @@
       <c r="X545" s="2" t="inlineStr"/>
       <c r="Y545" s="2" t="inlineStr"/>
       <c r="Z545" s="2" t="inlineStr"/>
-      <c r="AA545" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a buffer quantity which is only used during unexpected circumstances such as increased demand, difficulties in delivery, etc.
-The selected safety stock method determines how the safety stock is entered.</t>
-        </is>
-      </c>
+      <c r="AA545" s="2" t="inlineStr"/>
       <c r="AB545" s="2" t="inlineStr"/>
       <c r="AC545" s="2" t="inlineStr"/>
       <c r="AD545" s="2" t="inlineStr"/>
@@ -46605,24 +45744,8 @@
       <c r="X546" s="2" t="inlineStr"/>
       <c r="Y546" s="2" t="inlineStr"/>
       <c r="Z546" s="2" t="inlineStr"/>
-      <c r="AA546" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the safety stock is calculated and updated.</t>
-        </is>
-      </c>
-      <c r="AB546" s="2" t="inlineStr">
-        <is>
-          <t>0: Manually
-1: Automatically according to the formula: Number of safety stock days * Daily usage
-2: Automatically according to the formula: Safety stock percentage * Lead time * Daily usage
-3: Automatically according to the formula: Safety factor * 1.25 * Mean absolute deviation (MAD) * Square root of lead time in number of periods
-4: Number of safety stock days in accordance with (MMS093)
-5: Number of average issues in accordance with the safety stock control table
-6: By integration to MerciaLincs
-7: Automatically according to Poisson table
-8: Automatically, average quantity/issue. Optionally multiplied with safety stock factor.</t>
-        </is>
-      </c>
+      <c r="AA546" s="2" t="inlineStr"/>
+      <c r="AB546" s="2" t="inlineStr"/>
       <c r="AC546" s="2" t="inlineStr"/>
       <c r="AD546" s="2" t="inlineStr"/>
       <c r="AE546" s="2" t="inlineStr">
@@ -46708,12 +45831,7 @@
       <c r="X547" s="2" t="inlineStr"/>
       <c r="Y547" s="2" t="inlineStr"/>
       <c r="Z547" s="2" t="inlineStr"/>
-      <c r="AA547" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates manual safety stock (MSS), which may be entered per warehouse and item. This quantity is an extra security and it is added to the safety stock (SS) when the reorder point (RoP) is calculated according to calculation method 1, as follows.
-RoP = SS + MSS + Usage during lead time.</t>
-        </is>
-      </c>
+      <c r="AA547" s="2" t="inlineStr"/>
       <c r="AB547" s="2" t="inlineStr"/>
       <c r="AC547" s="2" t="inlineStr"/>
       <c r="AD547" s="2" t="inlineStr"/>
@@ -46804,12 +45922,7 @@
       <c r="X548" s="2" t="inlineStr"/>
       <c r="Y548" s="2" t="inlineStr"/>
       <c r="Z548" s="2" t="inlineStr"/>
-      <c r="AA548" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the safety stock unit.
-Depending on the safety stock method used, the value is entered as:</t>
-        </is>
-      </c>
+      <c r="AA548" s="2" t="inlineStr"/>
       <c r="AB548" s="2" t="inlineStr"/>
       <c r="AC548" s="2" t="inlineStr"/>
       <c r="AD548" s="2" t="inlineStr"/>
@@ -46904,12 +46017,7 @@
       <c r="X549" s="2" t="inlineStr"/>
       <c r="Y549" s="2" t="inlineStr"/>
       <c r="Z549" s="2" t="inlineStr"/>
-      <c r="AA549" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the service level. It is expressed in the form of a percentage and defines what level is planned, per item, with regards to the possibility of immediately meeting demands.
-The service level is connected to a table which converts the percentage values to security factors.</t>
-        </is>
-      </c>
+      <c r="AA549" s="2" t="inlineStr"/>
       <c r="AB549" s="2" t="inlineStr"/>
       <c r="AC549" s="2" t="inlineStr">
         <is>
@@ -47008,13 +46116,7 @@
       <c r="X550" s="2" t="inlineStr"/>
       <c r="Y550" s="2" t="inlineStr"/>
       <c r="Z550" s="2" t="inlineStr"/>
-      <c r="AA550" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the maximum quantity that is allowed for each combination of warehouse and item.
-If the planned on-hand balance exceeds the maximum stock level an action message is issued.
-If the on-hand balance exceeds the maximum stock level a planning message is issued to so called planning mail box.</t>
-        </is>
-      </c>
+      <c r="AA550" s="2" t="inlineStr"/>
       <c r="AB550" s="2" t="inlineStr"/>
       <c r="AC550" s="2" t="inlineStr"/>
       <c r="AD550" s="2" t="inlineStr"/>
@@ -47105,18 +46207,8 @@
       <c r="X551" s="2" t="inlineStr"/>
       <c r="Y551" s="2" t="inlineStr"/>
       <c r="Z551" s="2" t="inlineStr"/>
-      <c r="AA551" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the maximum stock is to be calculated automatically.</t>
-        </is>
-      </c>
-      <c r="AB551" s="2" t="inlineStr">
-        <is>
-          <t>0: No
-1: Yes
-2: Yes, with maximum stock 0 (zero)</t>
-        </is>
-      </c>
+      <c r="AA551" s="2" t="inlineStr"/>
+      <c r="AB551" s="2" t="inlineStr"/>
       <c r="AC551" s="2" t="inlineStr"/>
       <c r="AD551" s="2" t="inlineStr"/>
       <c r="AE551" s="2" t="inlineStr">
@@ -47206,12 +46298,7 @@
       <c r="X552" s="2" t="inlineStr"/>
       <c r="Y552" s="2" t="inlineStr"/>
       <c r="Z552" s="2" t="inlineStr"/>
-      <c r="AA552" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates calculation of the maximum inventory quantity according to maximum inventory method 1.
-The percentage entered in the field is multiplied by the sum of the reorder point and the order quantity.</t>
-        </is>
-      </c>
+      <c r="AA552" s="2" t="inlineStr"/>
       <c r="AB552" s="2" t="inlineStr"/>
       <c r="AC552" s="2" t="inlineStr"/>
       <c r="AD552" s="2" t="inlineStr"/>
@@ -47405,27 +46492,8 @@
       <c r="X554" s="2" t="inlineStr"/>
       <c r="Y554" s="2" t="inlineStr"/>
       <c r="Z554" s="2" t="inlineStr"/>
-      <c r="AA554" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the process for calculating the order quantity for each item/warehouse. The alternatives are described in more detail below.
-Fixed quantity/variable period:</t>
-        </is>
-      </c>
-      <c r="AB554" s="2" t="inlineStr">
-        <is>
-          <t>00: Manually entered quantity
-01: Fixed quantity calculated from run-out time
-02: Economic order quantity - Wilson's formula.
-11: Discrete order quantity
-12: Manually entered run-out time
-13: Economic run-out time
-15: Run-out time using a timetable (so-called point-of-time table).
-21: Least unit cost
-23: Period-based order quantity without balance check
-24: Period-based order quantity with balance check
-25: Up to maximum on-hand balance.</t>
-        </is>
-      </c>
+      <c r="AA554" s="2" t="inlineStr"/>
+      <c r="AB554" s="2" t="inlineStr"/>
       <c r="AC554" s="2" t="inlineStr"/>
       <c r="AD554" s="2" t="inlineStr"/>
       <c r="AE554" s="2" t="inlineStr">
@@ -47515,12 +46583,7 @@
       <c r="X555" s="2" t="inlineStr"/>
       <c r="Y555" s="2" t="inlineStr"/>
       <c r="Z555" s="2" t="inlineStr"/>
-      <c r="AA555" s="2" t="inlineStr">
-        <is>
-          <t>This field indicates the number of days demand that is to apply when calculating the order quantity in accordance with the rules which apply for each order quantity method.
-If nothing has been specified per item/warehouse combination, the number of days is obtained from the ABC sales volume class.</t>
-        </is>
-      </c>
+      <c r="AA555" s="2" t="inlineStr"/>
       <c r="AB555" s="2" t="inlineStr"/>
       <c r="AC555" s="2" t="inlineStr"/>
       <c r="AD555" s="2" t="inlineStr"/>
@@ -47615,12 +46678,7 @@
       <c r="X556" s="2" t="inlineStr"/>
       <c r="Y556" s="2" t="inlineStr"/>
       <c r="Z556" s="2" t="inlineStr"/>
-      <c r="AA556" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the annual demand per warehouse/item. This can be entered either manually or calculated automatically. The automatic calculation can either be performed as an integrated part of the forecast calculation or based on the demand calculation result.
-The annual demand is used on different occasions, such as calculation of sales value analysis, order quantity etc.</t>
-        </is>
-      </c>
+      <c r="AA556" s="2" t="inlineStr"/>
       <c r="AB556" s="2" t="inlineStr"/>
       <c r="AC556" s="2" t="inlineStr"/>
       <c r="AD556" s="2" t="inlineStr"/>
@@ -47715,17 +46773,8 @@
       <c r="X557" s="2" t="inlineStr"/>
       <c r="Y557" s="2" t="inlineStr"/>
       <c r="Z557" s="2" t="inlineStr"/>
-      <c r="AA557" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the annual demand is updated.</t>
-        </is>
-      </c>
-      <c r="AB557" s="2" t="inlineStr">
-        <is>
-          <t>0: Manually
-1: Automatically, either integrated with the forecasting or based on the demand calculation results.</t>
-        </is>
-      </c>
+      <c r="AA557" s="2" t="inlineStr"/>
+      <c r="AB557" s="2" t="inlineStr"/>
       <c r="AC557" s="2" t="inlineStr"/>
       <c r="AD557" s="2" t="inlineStr"/>
       <c r="AE557" s="2" t="inlineStr">
@@ -47819,16 +46868,7 @@
       <c r="X558" s="2" t="inlineStr"/>
       <c r="Y558" s="2" t="inlineStr"/>
       <c r="Z558" s="2" t="inlineStr"/>
-      <c r="AA558" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the minimum order quantity allowed.
-The information is used when batch size is calculated in connection with the requirements calculation, but only if it is greater than zero.
-The minimum order quantity can be specified in following locations and search hierarchy:
-1. Item/supplier (PPS040) in the PO unit of measure (U/M) in PPS040
-2. Item/warehouse (MMS002) in basic U/M
-Warning messages in PPS171, PPS201 and OIS145 display the minimum order quantity in the same U/M as entered on the order.</t>
-        </is>
-      </c>
+      <c r="AA558" s="2" t="inlineStr"/>
       <c r="AB558" s="2" t="inlineStr"/>
       <c r="AC558" s="2" t="inlineStr"/>
       <c r="AD558" s="2" t="inlineStr"/>
@@ -47919,12 +46959,7 @@
       <c r="X559" s="2" t="inlineStr"/>
       <c r="Y559" s="2" t="inlineStr"/>
       <c r="Z559" s="2" t="inlineStr"/>
-      <c r="AA559" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates maximum order quantity, which is the maximum allowed order quantity for each combination of item/warehouse.
-The information is used at calculation of batch size in connection with requirement calculation, only if the batch size is greater than zero.</t>
-        </is>
-      </c>
+      <c r="AA559" s="2" t="inlineStr"/>
       <c r="AB559" s="2" t="inlineStr"/>
       <c r="AC559" s="2" t="inlineStr"/>
       <c r="AD559" s="2" t="inlineStr"/>
@@ -48031,19 +47066,8 @@
         </is>
       </c>
       <c r="Z560" s="2" t="inlineStr"/>
-      <c r="AA560" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how acquisition is performed for requirements (immediate or planned) for each item/warehouse.</t>
-        </is>
-      </c>
-      <c r="AB560" s="2" t="inlineStr">
-        <is>
-          <t>1: Manufacturing
-2: Purchasing
-3: Distribution from another warehouse
-6: Maintenance.</t>
-        </is>
-      </c>
+      <c r="AA560" s="2" t="inlineStr"/>
+      <c r="AB560" s="2" t="inlineStr"/>
       <c r="AC560" s="2" t="inlineStr"/>
       <c r="AD560" s="2" t="inlineStr"/>
       <c r="AE560" s="2" t="inlineStr">
@@ -48133,13 +47157,7 @@
       <c r="X561" s="2" t="inlineStr"/>
       <c r="Y561" s="2" t="inlineStr"/>
       <c r="Z561" s="2" t="inlineStr"/>
-      <c r="AA561" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the supplying warehouse, which is the warehouse that is planned to supply the current warehouse when needed. This field is to be specified when the acquisition code is set to 2 or 3.
-When acquisition code 2 is used together with an internal supplier, a supplying warehouse will be used. If the supplying warehouse is left blank, it will be populated with the supplying warehouse of the supplier from (CRS624). When a purchase order is created with the internal supplier, a customer order is created in the supplying warehouse.
-When acquisition code 3 is used, a supplying warehouse must be entered. When a distribution order in the current warehouse is generated automatically, the supplying warehouse will supply this demand.</t>
-        </is>
-      </c>
+      <c r="AA561" s="2" t="inlineStr"/>
       <c r="AB561" s="2" t="inlineStr"/>
       <c r="AC561" s="2" t="inlineStr"/>
       <c r="AD561" s="2" t="inlineStr"/>
@@ -48226,12 +47244,7 @@
       <c r="X562" s="2" t="inlineStr"/>
       <c r="Y562" s="2" t="inlineStr"/>
       <c r="Z562" s="2" t="inlineStr"/>
-      <c r="AA562" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a period frame template which is used to group days in appropriate periods. Each template ID is user-defined and can include up to 50 periods/columns with varying lengths. The period frame template entered per planning unit is also used for forecast distribution, if appropriate. Each period frame template is defined by entering three pieces of information in four intervals: - Number of periods/columns - Unit multiplier, that is the number of units that will form the period/column - Unit, expressed in days, weeks or system periods.
-In addition, it is possible to determine the manner in which eventual changes from one unit to another should be processed by specifying whether overlapping should be used.</t>
-        </is>
-      </c>
+      <c r="AA562" s="2" t="inlineStr"/>
       <c r="AB562" s="2" t="inlineStr"/>
       <c r="AC562" s="2" t="inlineStr"/>
       <c r="AD562" s="2" t="inlineStr"/>
@@ -48322,11 +47335,7 @@
       <c r="X563" s="2" t="inlineStr"/>
       <c r="Y563" s="2" t="inlineStr"/>
       <c r="Z563" s="2" t="inlineStr"/>
-      <c r="AA563" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of a forecast method. Forecast methods define how the item is processed during forecasting and are created in (FCS300).</t>
-        </is>
-      </c>
+      <c r="AA563" s="2" t="inlineStr"/>
       <c r="AB563" s="2" t="inlineStr"/>
       <c r="AC563" s="2" t="inlineStr"/>
       <c r="AD563" s="2" t="inlineStr"/>
@@ -48413,12 +47422,7 @@
       <c r="X564" s="2" t="inlineStr"/>
       <c r="Y564" s="2" t="inlineStr"/>
       <c r="Z564" s="2" t="inlineStr"/>
-      <c r="AA564" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the forecast should be managed when transferred to material requirements planning. The parameters defined for each forecast logic mainly determine how reservations should be matched against forecasts.
-Forecast calculation methods are defined in (FCS305).</t>
-        </is>
-      </c>
+      <c r="AA564" s="2" t="inlineStr"/>
       <c r="AB564" s="2" t="inlineStr"/>
       <c r="AC564" s="2" t="inlineStr"/>
       <c r="AD564" s="2" t="inlineStr"/>
@@ -48509,11 +47513,7 @@
       <c r="X565" s="2" t="inlineStr"/>
       <c r="Y565" s="2" t="inlineStr"/>
       <c r="Z565" s="2" t="inlineStr"/>
-      <c r="AA565" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the fixed annual demand, which can only be updated by moving the current annual demand at the time of the run to this data element.</t>
-        </is>
-      </c>
+      <c r="AA565" s="2" t="inlineStr"/>
       <c r="AB565" s="2" t="inlineStr"/>
       <c r="AC565" s="2" t="inlineStr"/>
       <c r="AD565" s="2" t="inlineStr"/>
@@ -48691,11 +47691,7 @@
       <c r="X567" s="2" t="inlineStr"/>
       <c r="Y567" s="2" t="inlineStr"/>
       <c r="Z567" s="2" t="inlineStr"/>
-      <c r="AA567" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the planning time fence which is a time in the planning horizon of the master scheduling process that marks a limit. Inside the planning time fence changes to the material plan are reviewed by the responsible planner. Planned orders beyond the planning time fence can be changed using system planning logic.</t>
-        </is>
-      </c>
+      <c r="AA567" s="2" t="inlineStr"/>
       <c r="AB567" s="2" t="inlineStr"/>
       <c r="AC567" s="2" t="inlineStr"/>
       <c r="AD567" s="2" t="inlineStr"/>
@@ -48786,16 +47782,7 @@
       <c r="X568" s="2" t="inlineStr"/>
       <c r="Y568" s="2" t="inlineStr"/>
       <c r="Z568" s="2" t="inlineStr"/>
-      <c r="AA568" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the supply lead time in days.
-For manufactured items (acquisition method 1) and distribution items (acquisition method 3), the lead time is always expressed in workdays.
-For manufactured items, the supply lead time is updated automatically (from the product header). It always includes the directly ordered acquisition of included material, regardless of whether the material is manufactured or purchased.
-For purchased items (acquisition method 2), you can set the supply lead time to either five or seven days per week using setting 33 in (CRS780).
-For purchased items, this field is updated manually in (MMS002) or for the main supplier in (PPS044). (PPS044) is reached via option 14 in (PPS040). When one program is updated, the other is updated automatically if the main supplier is the same and single supply has been selected in the multiple supply field in (MMS002). This field is also updated when a new purchase agreement becomes valid (order date) during a separate user-initiated run (PPS950).
-For distributed items, this lead time reflects the supply chain lead time if the item is order initiated for the supplying warehouse or for the supplying and the receiving warehouse. Example: An item is order initiated at warehouse 100 (supplying warehouse) where the total lead time is 20 days. At warehouse 200 (receiving warehouse), the transport lead time is 2 days. The total lead time at warehouse 200 will then be 20 (supply lead time) + 2 (transport lead time) = 22 days. Note, no automatic update of the lead time value for the item on the receiving warehouse is performed if changing the item on the supplying warehouse from order initiated to MRP, this has to be done manually.</t>
-        </is>
-      </c>
+      <c r="AA568" s="2" t="inlineStr"/>
       <c r="AB568" s="2" t="inlineStr"/>
       <c r="AC568" s="2" t="inlineStr"/>
       <c r="AD568" s="2" t="inlineStr"/>
@@ -48890,15 +47877,7 @@
       <c r="X569" s="2" t="inlineStr"/>
       <c r="Y569" s="2" t="inlineStr"/>
       <c r="Z569" s="2" t="inlineStr"/>
-      <c r="AA569" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the time normally required for goods receipt, quality inspection, and put-away. Inspection lead time is not allowed for direct put-away where the inspection point is defined as 1 on (PPS345/E).
-The inspection lead time is mainly used for purchased items and is thus always entered via the current goods receiving method.
-In order for a changed inspection lead time to affect all appropriate items, (MMS987) should be run.
-When a manufactured product is quality-inspected, the inspection lead time is used; otherwise it is not used. In this case it is entered immediately for the item/warehouse combination.
-Items procured through distribution orders do not use inspection lead time.</t>
-        </is>
-      </c>
+      <c r="AA569" s="2" t="inlineStr"/>
       <c r="AB569" s="2" t="inlineStr"/>
       <c r="AC569" s="2" t="inlineStr"/>
       <c r="AD569" s="2" t="inlineStr"/>
@@ -48989,14 +47968,7 @@
       <c r="X570" s="2" t="inlineStr"/>
       <c r="Y570" s="2" t="inlineStr"/>
       <c r="Z570" s="2" t="inlineStr"/>
-      <c r="AA570" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates transportation lead time, which is always maintained through other associated files depending on the method of procurement.
-When a need is fulfilled via a distribution order, the transportation time is obtained from the respective warehouse relation (DPS001). If there are several supplying warehouses, the transportation time from the warehouse which comes first in alphabetical order is used.
-For purchased items, any transportation time is obtained from the file which is maintained in (PPS010). The elements making up this time for purchased items are clearly explained in the function.
-The transportation lead time is not used for manufactured items.</t>
-        </is>
-      </c>
+      <c r="AA570" s="2" t="inlineStr"/>
       <c r="AB570" s="2" t="inlineStr"/>
       <c r="AC570" s="2" t="inlineStr"/>
       <c r="AD570" s="2" t="inlineStr"/>
@@ -49087,20 +48059,7 @@
       <c r="X571" s="2" t="inlineStr"/>
       <c r="Y571" s="2" t="inlineStr"/>
       <c r="Z571" s="2" t="inlineStr"/>
-      <c r="AA571" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the lead time for each item. This is the time needed to meet a requirement, from the point in time when acquisition activities are started to the point in time when the requirement is fulfilled.
-Lead time includes administrative time, postal lead time, supply lead time, transportation time, and inspection time.
-Lead time is always expressed in the unit of five (5) days per week when referring to production or distribution supply. For purchased items, the lead time can be as above or expressed in calendar days (7 days per week).
-1. Administrative time:
-2. Postal lead time:
-3. Supply lead time:
-4. Transportation time:
-Specified and retrieved from:
-(If the acquisition code = 4 and no relation exists for the supplying warehouse, the relation is initially retrieved via the item number, else via the distribution group.)
-5. Inspection time:</t>
-        </is>
-      </c>
+      <c r="AA571" s="2" t="inlineStr"/>
       <c r="AB571" s="2" t="inlineStr"/>
       <c r="AC571" s="2" t="inlineStr"/>
       <c r="AD571" s="2" t="inlineStr"/>
@@ -49195,18 +48154,7 @@
       <c r="X572" s="2" t="inlineStr"/>
       <c r="Y572" s="2" t="inlineStr"/>
       <c r="Z572" s="2" t="inlineStr"/>
-      <c r="AA572" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the order multiple quantity. It is used in order to avoid the need to break up packages, for example.
-The order multiple can be specified in following locations and search hierarchy:
-1. Item/supplier (PPS040) in the PO U/M in PPS040
-2. Alternative U/M (MMS015) in the alternate U/M
-3. Item/warehouse (MMS002) in the basic U/M
-When an order is planned or created, a check is made to ensure that the order quantity is divisible by the order multiple.
-The order multiple is also used when the order quantity is calculated during the material requirements calculation (MRP).
-Warning messages in PPS171, PPS201 and OIS145 display the order multiple in the same U/M as entered on the order.</t>
-        </is>
-      </c>
+      <c r="AA572" s="2" t="inlineStr"/>
       <c r="AB572" s="2" t="inlineStr"/>
       <c r="AC572" s="2" t="inlineStr"/>
       <c r="AD572" s="2" t="inlineStr"/>
@@ -49293,19 +48241,8 @@
       <c r="X573" s="2" t="inlineStr"/>
       <c r="Y573" s="2" t="inlineStr"/>
       <c r="Z573" s="2" t="inlineStr"/>
-      <c r="AA573" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates what kind of supply that is to be connected to the item.</t>
-        </is>
-      </c>
-      <c r="AB573" s="2" t="inlineStr">
-        <is>
-          <t>1: Single supply only from the supplier or warehouse set for the item. No override accepted.
-2: Multiple supply, the supplier or warehouse set for the item is defaulted. If a valid agreement for the main supplier is not found, the next supplier with a valid agreement will be chosen. The value can be overridden.
-3: Different warehouses according to a percentage set in the distribution relationship table for distribution orders.
-4: Multiple supply, the required quantity supplied according to different supply methods - valid supply methods and percentages are set in (RPS090).</t>
-        </is>
-      </c>
+      <c r="AA573" s="2" t="inlineStr"/>
+      <c r="AB573" s="2" t="inlineStr"/>
       <c r="AC573" s="2" t="inlineStr"/>
       <c r="AD573" s="2" t="inlineStr"/>
       <c r="AE573" s="2" t="inlineStr">
@@ -49395,15 +48332,7 @@
       <c r="X574" s="2" t="inlineStr"/>
       <c r="Y574" s="2" t="inlineStr"/>
       <c r="Z574" s="2" t="inlineStr"/>
-      <c r="AA574" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the lowest level (low level code) at which a material or a semi-finished product may be used in product structures and distribution network.
-The lowest level determines the order for product costing and requirements calculations. It may even be used to describe the relative levels for different documents in a document structure.
-The level is assigned automatically and cannot be changed manually.
-The lower the level in the product structure, the higher value.
-Finished products that are not used in other products are always in the highest level and have level 00.</t>
-        </is>
-      </c>
+      <c r="AA574" s="2" t="inlineStr"/>
       <c r="AB574" s="2" t="inlineStr"/>
       <c r="AC574" s="2" t="inlineStr"/>
       <c r="AD574" s="2" t="inlineStr"/>
@@ -49585,14 +48514,7 @@
       <c r="X576" s="2" t="inlineStr"/>
       <c r="Y576" s="2" t="inlineStr"/>
       <c r="Z576" s="2" t="inlineStr"/>
-      <c r="AA576" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the planning horizon, which is specified for each item/warehouse, and indicates how many days that are covered by the requirements planning from the current system date.
-There may well be requirements beyond the date fixed by the planning horizon, but these are not considered when orders are generated. There is no reason to use a longer horizon in requirements planning than what is required in order to plan the item with the longest lead time.
-To support long-term planning, it is possible to specify a long-term planning horizon per planning policy in (MMS037).
-It is also possible to override the planning horizon for each simulated version of the requirements planning, but the overriding horizon is then used for all items.</t>
-        </is>
-      </c>
+      <c r="AA576" s="2" t="inlineStr"/>
       <c r="AB576" s="2" t="inlineStr"/>
       <c r="AC576" s="2" t="inlineStr"/>
       <c r="AD576" s="2" t="inlineStr"/>
@@ -49683,13 +48605,7 @@
       <c r="X577" s="2" t="inlineStr"/>
       <c r="Y577" s="2" t="inlineStr"/>
       <c r="Z577" s="2" t="inlineStr"/>
-      <c r="AA577" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of days from the point an order is registered to the point the item is shipped. Items with a defined demand time fence are generally included in the master schedule.
-The demand time fence is a point in time in the master production schedule (MPS). The master schedule planning horizon is divided into three regions. In the MPS, the demand time fence is set between the current date and the planning time fence to establish two regions. The first region between the current date and the demand time fence establishes the area where orders are frozen, that is, no unanalyzed and unapproved changes are made to the MPS. The second region, between the demand time fence and the planning fence, is the area where the actual orders may consume the forecast.
-The field also controls the time for automatic allocation. If the field is blank, the value in (CRS701) is used.</t>
-        </is>
-      </c>
+      <c r="AA577" s="2" t="inlineStr"/>
       <c r="AB577" s="2" t="inlineStr"/>
       <c r="AC577" s="2" t="inlineStr"/>
       <c r="AD577" s="2" t="inlineStr"/>
@@ -49800,12 +48716,7 @@
         </is>
       </c>
       <c r="Z578" s="2" t="inlineStr"/>
-      <c r="AA578" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates an order type which is a combined ID for settings that determine how the order is processed during order entry and in the processing flow.
-Order types are defined per order category in the following programs:</t>
-        </is>
-      </c>
+      <c r="AA578" s="2" t="inlineStr"/>
       <c r="AB578" s="2" t="inlineStr"/>
       <c r="AC578" s="2" t="inlineStr">
         <is>
@@ -49900,13 +48811,7 @@
       <c r="X579" s="2" t="inlineStr"/>
       <c r="Y579" s="2" t="inlineStr"/>
       <c r="Z579" s="2" t="inlineStr"/>
-      <c r="AA579" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if M3 should be checking the material planning situation for the item/warehouse immediately. Requirements planning is done in a queue system that is processed in real time.
-If you do not select the check box, then the check of the material planning situation is made in batches, normally at the end of the day.
-This can result in M3 Material Planning generating planned orders (MO, DO, PO or WO) or action messages to propose activities. Action messages are created in (RPS001) as set in the selected planning policy.</t>
-        </is>
-      </c>
+      <c r="AA579" s="2" t="inlineStr"/>
       <c r="AB579" s="2" t="inlineStr"/>
       <c r="AC579" s="2" t="inlineStr"/>
       <c r="AD579" s="2" t="inlineStr"/>
@@ -49997,11 +48902,7 @@
       <c r="X580" s="2" t="inlineStr"/>
       <c r="Y580" s="2" t="inlineStr"/>
       <c r="Z580" s="2" t="inlineStr"/>
-      <c r="AA580" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how many days before the actual need date a planned order should be available in stock. The purpose is to protect the scheduling from any fluctuations in the item's delivery time. This information is only used when planning method 1 or 3 are applied.</t>
-        </is>
-      </c>
+      <c r="AA580" s="2" t="inlineStr"/>
       <c r="AB580" s="2" t="inlineStr"/>
       <c r="AC580" s="2" t="inlineStr"/>
       <c r="AD580" s="2" t="inlineStr"/>
@@ -50092,14 +48993,7 @@
       <c r="X581" s="2" t="inlineStr"/>
       <c r="Y581" s="2" t="inlineStr"/>
       <c r="Z581" s="2" t="inlineStr"/>
-      <c r="AA581" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to make allocation according to defined limits.
-If you do not select the check box, then can allocation only be made in relation to the specified location or location type.
-Quantity controlled allocation is maintained automatically by connecting a quantity controlled allocation table to the item/warehouse. The table is maintained in (MMS057).
-The table enables allocations to be made repeatedly and to be placed in the location type that is consistent with the quantity that remains to be allocated. This means the allocation of a reservation can affect several different location types, for example, whole pallet or picking inventory.</t>
-        </is>
-      </c>
+      <c r="AA581" s="2" t="inlineStr"/>
       <c r="AB581" s="2" t="inlineStr"/>
       <c r="AC581" s="2" t="inlineStr"/>
       <c r="AD581" s="2" t="inlineStr"/>
@@ -50194,21 +49088,8 @@
       <c r="X582" s="2" t="inlineStr"/>
       <c r="Y582" s="2" t="inlineStr"/>
       <c r="Z582" s="2" t="inlineStr"/>
-      <c r="AA582" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the material planning method set for the item/warehouse during acquisition order entry. There are two basic methods (material requirements planning and reorder point planning) used to plan and create acquisition orders.</t>
-        </is>
-      </c>
-      <c r="AB582" s="2" t="inlineStr">
-        <is>
-          <t>0: Manually planned
-1: Material requirements planning (MRP)
-2: Reorder point planning (ROP) per item/warehouse
-3: Order-driven - Acquisition orders are only triggered, created and released by a requiring order
-4: Reorder point planning (ROP) per item and facility
-5: Reorder point planning (ROP) per item and global facility.</t>
-        </is>
-      </c>
+      <c r="AA582" s="2" t="inlineStr"/>
+      <c r="AB582" s="2" t="inlineStr"/>
       <c r="AC582" s="2" t="inlineStr"/>
       <c r="AD582" s="2" t="inlineStr"/>
       <c r="AE582" s="2" t="inlineStr">
@@ -50298,20 +49179,8 @@
       <c r="X583" s="2" t="inlineStr"/>
       <c r="Y583" s="2" t="inlineStr"/>
       <c r="Z583" s="2" t="inlineStr"/>
-      <c r="AA583" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the item is part of the master schedule. The master schedule represents what the company plans to produce expressed in specific configurations, quantities and dates. The master schedule takes into account the forecast, the production plan and other important considerations such as backlog, availability of material and capacity, management policies and goals.</t>
-        </is>
-      </c>
-      <c r="AB583" s="2" t="inlineStr">
-        <is>
-          <t>0: Not a master scheduled item
-1: Master scheduled item - may be used for manufactured, purchased or distributed items. By selecting this option, planned orders will not automatically be scheduled inside the planning time fence. The system will instead apply an A3 action message to the planned order and place it on the planning time fence with an alternative date.
-2: Master scheduled item that always contains a customer order-specific configuration - may be used for scheduling of products that display a relatively low item volume, are very specialized to customer needs, and generate high inventory costs.
-3: Planning entity - used for forecasting on a more aggregated level. For instance, pasta could be an appropriate item to forecast when selling macaroni and spaghetti. If pasta is the planning entity, the forecast on pasta will be consumed when macaroni or spaghetti is sold. The planning entity should have inventory accounting = 2. The connection between the items that you sell and the planning entity is defined in (RPS045).
-4: Process planning item - used for items to be defined as process planned and whose inventory accounting code in (MMS001) must equal 2. For end items connected to a planning process the master schedule code should be 0 or 1.</t>
-        </is>
-      </c>
+      <c r="AA583" s="2" t="inlineStr"/>
+      <c r="AB583" s="2" t="inlineStr"/>
       <c r="AC583" s="2" t="inlineStr"/>
       <c r="AD583" s="2" t="inlineStr"/>
       <c r="AE583" s="2" t="inlineStr">
@@ -50401,19 +49270,8 @@
       <c r="X584" s="2" t="inlineStr"/>
       <c r="Y584" s="2" t="inlineStr"/>
       <c r="Z584" s="2" t="inlineStr"/>
-      <c r="AA584" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates how the distribution and supplier delivery calendars are checked when an order's delivery date is determined.</t>
-        </is>
-      </c>
-      <c r="AB584" s="2" t="inlineStr">
-        <is>
-          <t>0: Calendars are not used.
-1: Back scheduling.
-2: Forward scheduling.
-3: The closest date possible is selected, regardless of whether a previous or later delivery date is selected.</t>
-        </is>
-      </c>
+      <c r="AA584" s="2" t="inlineStr"/>
+      <c r="AB584" s="2" t="inlineStr"/>
       <c r="AC584" s="2" t="inlineStr"/>
       <c r="AD584" s="2" t="inlineStr"/>
       <c r="AE584" s="2" t="inlineStr">
@@ -50503,11 +49361,7 @@
       <c r="X585" s="2" t="inlineStr"/>
       <c r="Y585" s="2" t="inlineStr"/>
       <c r="Z585" s="2" t="inlineStr"/>
-      <c r="AA585" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if the on-hand balance has been zero or negative since the last inventory.</t>
-        </is>
-      </c>
+      <c r="AA585" s="2" t="inlineStr"/>
       <c r="AB585" s="2" t="inlineStr"/>
       <c r="AC585" s="2" t="inlineStr"/>
       <c r="AD585" s="2" t="inlineStr"/>
@@ -50598,12 +49452,7 @@
       <c r="X586" s="2" t="inlineStr"/>
       <c r="Y586" s="2" t="inlineStr"/>
       <c r="Z586" s="2" t="inlineStr"/>
-      <c r="AA586" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the location where goods received are stored while waiting to be quality inspected in the purchase component group.
-If the item is to be inspected, this location is proposed by default in (PPS300). If the location is blank per item/warehouse, the location is proposed by default from the goods receiving method.</t>
-        </is>
-      </c>
+      <c r="AA586" s="2" t="inlineStr"/>
       <c r="AB586" s="2" t="inlineStr"/>
       <c r="AC586" s="2" t="inlineStr"/>
       <c r="AD586" s="2" t="inlineStr"/>
@@ -50682,13 +49531,7 @@
       <c r="X587" s="2" t="inlineStr"/>
       <c r="Y587" s="2" t="inlineStr"/>
       <c r="Z587" s="2" t="inlineStr"/>
-      <c r="AA587" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if a MRP net change calculation is active.
-If you do not select the check box MRP net change calculation is finished.
-M3 automatically updates the field.</t>
-        </is>
-      </c>
+      <c r="AA587" s="2" t="inlineStr"/>
       <c r="AB587" s="2" t="inlineStr"/>
       <c r="AC587" s="2" t="inlineStr"/>
       <c r="AD587" s="2" t="inlineStr"/>
@@ -50799,14 +49642,7 @@
         </is>
       </c>
       <c r="Z588" s="2" t="inlineStr"/>
-      <c r="AA588" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the facility used.
-Facilities are used to set authorization in time reporting component groups and for activities such as sales, production or distribution.
-A facility is a superior organizational level to a department but lower than a division, that is, a facility belongs to a division, which in turn belongs to a company. A facility can contain one or more warehouses. A user is always connected to a pre-selected facility. All product data and production data are stored per facility, and several facilities can exist in the same database. All planning occurs per warehouse, although the highest planning level in M3 can be the facility, when availability can be calculated per facility. However, this assumes that planning method 4 is used.
-Facilities are defined in (CRS008).</t>
-        </is>
-      </c>
+      <c r="AA588" s="2" t="inlineStr"/>
       <c r="AB588" s="2" t="inlineStr"/>
       <c r="AC588" s="2" t="inlineStr">
         <is>
@@ -50893,13 +49729,7 @@
       <c r="X589" s="2" t="inlineStr"/>
       <c r="Y589" s="2" t="inlineStr"/>
       <c r="Z589" s="2" t="inlineStr"/>
-      <c r="AA589" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a division. This is an identity for a legal unit within a company group.
-Division is a key value in the financial system in M3.
-One division may consist of several facilities. Facilities are used in material and production management and for purchasing purposes.</t>
-        </is>
-      </c>
+      <c r="AA589" s="2" t="inlineStr"/>
       <c r="AB589" s="2" t="inlineStr"/>
       <c r="AC589" s="2" t="inlineStr">
         <is>
@@ -50994,11 +49824,7 @@
       <c r="X590" s="2" t="inlineStr"/>
       <c r="Y590" s="2" t="inlineStr"/>
       <c r="Z590" s="2" t="inlineStr"/>
-      <c r="AA590" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if a time-phased safety stock exists in (RPS040).</t>
-        </is>
-      </c>
+      <c r="AA590" s="2" t="inlineStr"/>
       <c r="AB590" s="2" t="inlineStr"/>
       <c r="AC590" s="2" t="inlineStr"/>
       <c r="AD590" s="2" t="inlineStr"/>
@@ -51109,18 +49935,8 @@
         </is>
       </c>
       <c r="Z591" s="2" t="inlineStr"/>
-      <c r="AA591" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if and how stock transactions are stored in the stock transaction history file.</t>
-        </is>
-      </c>
-      <c r="AB591" s="2" t="inlineStr">
-        <is>
-          <t>1: Detailed storage.
-2: Accumulated storage on daily level per order and transaction type.
-3: Accumulated storage on daily level per transaction type.</t>
-        </is>
-      </c>
+      <c r="AA591" s="2" t="inlineStr"/>
+      <c r="AB591" s="2" t="inlineStr"/>
       <c r="AC591" s="2" t="inlineStr"/>
       <c r="AD591" s="2" t="inlineStr"/>
       <c r="AE591" s="2" t="inlineStr">
@@ -51376,11 +50192,7 @@
       <c r="X594" s="2" t="inlineStr"/>
       <c r="Y594" s="2" t="inlineStr"/>
       <c r="Z594" s="2" t="inlineStr"/>
-      <c r="AA594" s="2" t="inlineStr">
-        <is>
-          <t>The fields indicates the date when the item was last included an MRP calculation.</t>
-        </is>
-      </c>
+      <c r="AA594" s="2" t="inlineStr"/>
       <c r="AB594" s="2" t="inlineStr"/>
       <c r="AC594" s="2" t="inlineStr"/>
       <c r="AD594" s="2" t="inlineStr"/>
@@ -51471,11 +50283,7 @@
       <c r="X595" s="2" t="inlineStr"/>
       <c r="Y595" s="2" t="inlineStr"/>
       <c r="Z595" s="2" t="inlineStr"/>
-      <c r="AA595" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates when (along with the calculation date) the item was last included in an MRP calculation.</t>
-        </is>
-      </c>
+      <c r="AA595" s="2" t="inlineStr"/>
       <c r="AB595" s="2" t="inlineStr"/>
       <c r="AC595" s="2" t="inlineStr"/>
       <c r="AD595" s="2" t="inlineStr"/>
@@ -51558,12 +50366,7 @@
       <c r="X596" s="2" t="inlineStr"/>
       <c r="Y596" s="2" t="inlineStr"/>
       <c r="Z596" s="2" t="inlineStr"/>
-      <c r="AA596" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates time phased safety stock.
-This field is not used in this M3 version.</t>
-        </is>
-      </c>
+      <c r="AA596" s="2" t="inlineStr"/>
       <c r="AB596" s="2" t="inlineStr"/>
       <c r="AC596" s="2" t="inlineStr"/>
       <c r="AD596" s="2" t="inlineStr"/>
@@ -51816,11 +50619,7 @@
       <c r="X599" s="2" t="inlineStr"/>
       <c r="Y599" s="2" t="inlineStr"/>
       <c r="Z599" s="2" t="inlineStr"/>
-      <c r="AA599" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the text ID, which identifies comments made. It is updated automatically when entering comments.</t>
-        </is>
-      </c>
+      <c r="AA599" s="2" t="inlineStr"/>
       <c r="AB599" s="2" t="inlineStr"/>
       <c r="AC599" s="2" t="inlineStr"/>
       <c r="AD599" s="2" t="inlineStr"/>
@@ -51903,11 +50702,7 @@
       <c r="X600" s="2" t="inlineStr"/>
       <c r="Y600" s="2" t="inlineStr"/>
       <c r="Z600" s="2" t="inlineStr"/>
-      <c r="AA600" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the unique key used to connect a detailed message with the original record.</t>
-        </is>
-      </c>
+      <c r="AA600" s="2" t="inlineStr"/>
       <c r="AB600" s="2" t="inlineStr"/>
       <c r="AC600" s="2" t="inlineStr"/>
       <c r="AD600" s="2" t="inlineStr"/>
@@ -51998,11 +50793,7 @@
       <c r="X601" s="2" t="inlineStr"/>
       <c r="Y601" s="2" t="inlineStr"/>
       <c r="Z601" s="2" t="inlineStr"/>
-      <c r="AA601" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the location normally used for packing operations.</t>
-        </is>
-      </c>
+      <c r="AA601" s="2" t="inlineStr"/>
       <c r="AB601" s="2" t="inlineStr"/>
       <c r="AC601" s="2" t="inlineStr"/>
       <c r="AD601" s="2" t="inlineStr"/>
@@ -52089,11 +50880,7 @@
       <c r="X602" s="2" t="inlineStr"/>
       <c r="Y602" s="2" t="inlineStr"/>
       <c r="Z602" s="2" t="inlineStr"/>
-      <c r="AA602" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the normal docking location used for packaged goods ready to be shipped.</t>
-        </is>
-      </c>
+      <c r="AA602" s="2" t="inlineStr"/>
       <c r="AB602" s="2" t="inlineStr"/>
       <c r="AC602" s="2" t="inlineStr"/>
       <c r="AD602" s="2" t="inlineStr"/>
@@ -52180,11 +50967,7 @@
       <c r="X603" s="2" t="inlineStr"/>
       <c r="Y603" s="2" t="inlineStr"/>
       <c r="Z603" s="2" t="inlineStr"/>
-      <c r="AA603" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the delivery split rule of the item, which is used to group items when delivery shares are defined.</t>
-        </is>
-      </c>
+      <c r="AA603" s="2" t="inlineStr"/>
       <c r="AB603" s="2" t="inlineStr"/>
       <c r="AC603" s="2" t="inlineStr"/>
       <c r="AD603" s="2" t="inlineStr"/>
@@ -52271,12 +51054,7 @@
       <c r="X604" s="2" t="inlineStr"/>
       <c r="Y604" s="2" t="inlineStr"/>
       <c r="Z604" s="2" t="inlineStr"/>
-      <c r="AA604" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box if automatic allocation is to be possible for non-approved balance IDs, for example balance IDs with status 1.
-Automatic allocation of non-approved balance IDs applies only to order lines connected to a distribution order.</t>
-        </is>
-      </c>
+      <c r="AA604" s="2" t="inlineStr"/>
       <c r="AB604" s="2" t="inlineStr"/>
       <c r="AC604" s="2" t="inlineStr"/>
       <c r="AD604" s="2" t="inlineStr"/>
@@ -52367,22 +51145,8 @@
       <c r="X605" s="2" t="inlineStr"/>
       <c r="Y605" s="2" t="inlineStr"/>
       <c r="Z605" s="2" t="inlineStr"/>
-      <c r="AA605" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of a time table containing planning points specified in days, hours, and minutes. The table type determines how the time table is used.
-A time table of table type 10 is used to calculate the total sum of the requirements when order policy 15 is used in MRP. Order policy 15 does not support planning policy parameter 440 Planning level = '2-Attribute level' on (MMS037/I).
-A time table of table type 20 is used as a supplier calendar when purchase orders are created in MRP.
-A time table of table type 30 is used to group deliveries to allow usage of forecast pacing in delivery windows.
-A time table of table type 40 is used to group orders to enable order monitoring and forecast pacing.
-A time table of table type 50 is used to calculate the expiry date within a period bucket when the expiry date table on (MMS002/I) is filled.
-Time tables are created in (RPS080). When defining a time table, you can use facility, warehouse, and table type to control the extent of its validity. This means that the same time table ID can be used in different situations and have different settings.</t>
-        </is>
-      </c>
-      <c r="AB605" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">: </t>
-        </is>
-      </c>
+      <c r="AA605" s="2" t="inlineStr"/>
+      <c r="AB605" s="2" t="inlineStr"/>
       <c r="AC605" s="2" t="inlineStr">
         <is>
           <t>RPS080</t>
@@ -52492,18 +51256,8 @@
         </is>
       </c>
       <c r="Z606" s="2" t="inlineStr"/>
-      <c r="AA606" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the status of the record. Usually the status is entered as follows:</t>
-        </is>
-      </c>
-      <c r="AB606" s="2" t="inlineStr">
-        <is>
-          <t>10: Preliminary
-20: Definite
-90: Blocked/expired.</t>
-        </is>
-      </c>
+      <c r="AA606" s="2" t="inlineStr"/>
+      <c r="AB606" s="2" t="inlineStr"/>
       <c r="AC606" s="2" t="inlineStr"/>
       <c r="AD606" s="2" t="inlineStr"/>
       <c r="AE606" s="2" t="inlineStr">
@@ -52593,17 +51347,8 @@
       <c r="X607" s="2" t="inlineStr"/>
       <c r="Y607" s="2" t="inlineStr"/>
       <c r="Z607" s="2" t="inlineStr"/>
-      <c r="AA607" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the VAT code to be used for purchased items.</t>
-        </is>
-      </c>
-      <c r="AB607" s="2" t="inlineStr">
-        <is>
-          <t>0: VAT not used
-1-99: User-defined VAT codes</t>
-        </is>
-      </c>
+      <c r="AA607" s="2" t="inlineStr"/>
+      <c r="AB607" s="2" t="inlineStr"/>
       <c r="AC607" s="2" t="inlineStr"/>
       <c r="AD607" s="2" t="inlineStr"/>
       <c r="AE607" s="2" t="inlineStr">
@@ -52693,17 +51438,8 @@
       <c r="X608" s="2" t="inlineStr"/>
       <c r="Y608" s="2" t="inlineStr"/>
       <c r="Z608" s="2" t="inlineStr"/>
-      <c r="AA608" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the VAT code to be used for sold items.</t>
-        </is>
-      </c>
-      <c r="AB608" s="2" t="inlineStr">
-        <is>
-          <t>0: VAT not used
-1-99: User-defined VAT codes</t>
-        </is>
-      </c>
+      <c r="AA608" s="2" t="inlineStr"/>
+      <c r="AB608" s="2" t="inlineStr"/>
       <c r="AC608" s="2" t="inlineStr"/>
       <c r="AD608" s="2" t="inlineStr"/>
       <c r="AE608" s="2" t="inlineStr">
@@ -52868,11 +51604,7 @@
       <c r="X610" s="2" t="inlineStr"/>
       <c r="Y610" s="2" t="inlineStr"/>
       <c r="Z610" s="2" t="inlineStr"/>
-      <c r="AA610" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates grouping of items according to their technical relations.</t>
-        </is>
-      </c>
+      <c r="AA610" s="2" t="inlineStr"/>
       <c r="AB610" s="2" t="inlineStr"/>
       <c r="AC610" s="2" t="inlineStr">
         <is>
@@ -52967,12 +51699,7 @@
       <c r="X611" s="2" t="inlineStr"/>
       <c r="Y611" s="2" t="inlineStr"/>
       <c r="Z611" s="2" t="inlineStr"/>
-      <c r="AA611" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of days shelf life for a lot or serial number measured from the production date to expiration date.
-This is used to calculate the expiration date when a lot or serial number is created, and the expiration date is stored for each lot number or serial number in (MMS235).</t>
-        </is>
-      </c>
+      <c r="AA611" s="2" t="inlineStr"/>
       <c r="AB611" s="2" t="inlineStr"/>
       <c r="AC611" s="2" t="inlineStr"/>
       <c r="AD611" s="2" t="inlineStr"/>
@@ -53063,12 +51790,7 @@
       <c r="X612" s="2" t="inlineStr"/>
       <c r="Y612" s="2" t="inlineStr"/>
       <c r="Z612" s="2" t="inlineStr"/>
-      <c r="AA612" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of days counted from last inspection date when a lot or serial number must be reinspected.
-This is used when a lot number or serial number is approved. The reinspection date is stored in the lot master (MMS235).</t>
-        </is>
-      </c>
+      <c r="AA612" s="2" t="inlineStr"/>
       <c r="AB612" s="2" t="inlineStr"/>
       <c r="AC612" s="2" t="inlineStr"/>
       <c r="AD612" s="2" t="inlineStr"/>
@@ -53159,12 +51881,7 @@
       <c r="X613" s="2" t="inlineStr"/>
       <c r="Y613" s="2" t="inlineStr"/>
       <c r="Z613" s="2" t="inlineStr"/>
-      <c r="AA613" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the standard number of days from the production date to the last sales date.
-This is used to calculate the last sales date when a lot or serial number is created. The last sales date is stored for each lot number or serial number (MMS235).</t>
-        </is>
-      </c>
+      <c r="AA613" s="2" t="inlineStr"/>
       <c r="AB613" s="2" t="inlineStr"/>
       <c r="AC613" s="2" t="inlineStr"/>
       <c r="AD613" s="2" t="inlineStr"/>
@@ -53275,11 +51992,7 @@
         </is>
       </c>
       <c r="Z614" s="2" t="inlineStr"/>
-      <c r="AA614" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the CTP policy to use. The CTP policy determines how the ATP and CTP calculations are done.</t>
-        </is>
-      </c>
+      <c r="AA614" s="2" t="inlineStr"/>
       <c r="AB614" s="2" t="inlineStr"/>
       <c r="AC614" s="2" t="inlineStr"/>
       <c r="AD614" s="2" t="inlineStr"/>
@@ -53536,19 +52249,8 @@
       <c r="X617" s="2" t="inlineStr"/>
       <c r="Y617" s="2" t="inlineStr"/>
       <c r="Z617" s="2" t="inlineStr"/>
-      <c r="AA617" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the secondary allocation method. If quantities remain to be allocated after allocation has been done according to allocation method 2 (see field to the left), the remaining quantities can be allocated according to a secondary allocation method.
-The secondary allocation method does not apply for replenishment orders (stock transaction type 92).</t>
-        </is>
-      </c>
-      <c r="AB617" s="2" t="inlineStr">
-        <is>
-          <t>0: No secondary allocation is done.
-3: Automatic allocation for the location entered per item/warehouse. Overallocation is permitted per location but not per warehouse. This method may not be used if the item is lot controlled.
-6: Soft automatic allocation with a check against allocatable balance on warehouse level. See the Note below.</t>
-        </is>
-      </c>
+      <c r="AA617" s="2" t="inlineStr"/>
+      <c r="AB617" s="2" t="inlineStr"/>
       <c r="AC617" s="2" t="inlineStr"/>
       <c r="AD617" s="2" t="inlineStr"/>
       <c r="AE617" s="2" t="inlineStr">
@@ -53638,13 +52340,7 @@
       <c r="X618" s="2" t="inlineStr"/>
       <c r="Y618" s="2" t="inlineStr"/>
       <c r="Z618" s="2" t="inlineStr"/>
-      <c r="AA618" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the aging days, which are the number of calendar days that the product must age before it can be used. It is typically used in conjunction with the values in the Aging hours field and/or Aging minutes field.
-Aging can only be used for manufactured items. At receipt, the balance ID will get status 1 (Under inspection) in (MMS060). At the same time, a reclassification transaction will be created in the material plan on the date when the product is available. The reclassification is performed as an autojob process.
-You control whether aging should be used on the manufacturing order type.</t>
-        </is>
-      </c>
+      <c r="AA618" s="2" t="inlineStr"/>
       <c r="AB618" s="2" t="inlineStr"/>
       <c r="AC618" s="2" t="inlineStr"/>
       <c r="AD618" s="2" t="inlineStr"/>
@@ -53735,13 +52431,7 @@
       <c r="X619" s="2" t="inlineStr"/>
       <c r="Y619" s="2" t="inlineStr"/>
       <c r="Z619" s="2" t="inlineStr"/>
-      <c r="AA619" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the aging hours, which are the number of hours that a product must age before it can be used. It is typically used in conjunction with the values in the Aging days and/or Aging minutes field. You cannot enter the aging hours to be greater than 23.
-Aging can only be used for manufactured items. At receipt, the balance ID will get status 1 (Under inspection) in (MMS060). At the same time, a reclassification transaction will be created in the material plan on the date when the product is available. The reclassification is performed by an autojob process.
-You can control whether aging should be used on the manufacturing order type.</t>
-        </is>
-      </c>
+      <c r="AA619" s="2" t="inlineStr"/>
       <c r="AB619" s="2" t="inlineStr"/>
       <c r="AC619" s="2" t="inlineStr"/>
       <c r="AD619" s="2" t="inlineStr"/>
@@ -53832,13 +52522,7 @@
       <c r="X620" s="2" t="inlineStr"/>
       <c r="Y620" s="2" t="inlineStr"/>
       <c r="Z620" s="2" t="inlineStr"/>
-      <c r="AA620" s="2" t="inlineStr">
-        <is>
-          <t>The field identifies the supply chain policy.
-The supply chain policy determines whether to include the item in the supply chain link function.
-If you add a supply chain policy to an item, then this item will be included in the supply chain function and get planned orders automatically generated according to the demand from the above level. The demand and the generated planned order will be preallocated and assigned a supply chain number. Thus, it is possible to have full traceability between demand and supply. Note that currently the start of a supply chain can only be done via a customer order or a released distribution order, and the generated planned orders are always lot sized according to lot-for-lot. It is however possible to manually preallocate lot sized planned purchase orders to one or more supply chains afterwards. Thereby you have the possibility to plan the purchase orders separately from the rest of the supply chain, for example via MRP.</t>
-        </is>
-      </c>
+      <c r="AA620" s="2" t="inlineStr"/>
       <c r="AB620" s="2" t="inlineStr"/>
       <c r="AC620" s="2" t="inlineStr">
         <is>
@@ -53933,12 +52617,7 @@
       <c r="X621" s="2" t="inlineStr"/>
       <c r="Y621" s="2" t="inlineStr"/>
       <c r="Z621" s="2" t="inlineStr"/>
-      <c r="AA621" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the on-hand balance in Catch weight U/M.
-Prerequisites for storing catch weight on location level is to set Industry in MNS095 - Company to Food &amp; Beverage.</t>
-        </is>
-      </c>
+      <c r="AA621" s="2" t="inlineStr"/>
       <c r="AB621" s="2" t="inlineStr"/>
       <c r="AC621" s="2" t="inlineStr"/>
       <c r="AD621" s="2" t="inlineStr"/>
@@ -54033,12 +52712,7 @@
       <c r="X622" s="2" t="inlineStr"/>
       <c r="Y622" s="2" t="inlineStr"/>
       <c r="Z622" s="2" t="inlineStr"/>
-      <c r="AA622" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the on-hand balance under inspection in Catch weight U/M.
-Prerequisites for storing catch weight on location level is to set Industry in MNS095 - Company to Food &amp; Beverage.</t>
-        </is>
-      </c>
+      <c r="AA622" s="2" t="inlineStr"/>
       <c r="AB622" s="2" t="inlineStr"/>
       <c r="AC622" s="2" t="inlineStr"/>
       <c r="AD622" s="2" t="inlineStr"/>
@@ -54133,12 +52807,7 @@
       <c r="X623" s="2" t="inlineStr"/>
       <c r="Y623" s="2" t="inlineStr"/>
       <c r="Z623" s="2" t="inlineStr"/>
-      <c r="AA623" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the rejected on-hand balance in Catch weight U/M.
-Prerequisites for storing catch weight on location level is to set Industry in MNS095 - Company to Food &amp; Beverage.</t>
-        </is>
-      </c>
+      <c r="AA623" s="2" t="inlineStr"/>
       <c r="AB623" s="2" t="inlineStr"/>
       <c r="AC623" s="2" t="inlineStr"/>
       <c r="AD623" s="2" t="inlineStr"/>
@@ -54221,20 +52890,8 @@
       <c r="X624" s="2" t="inlineStr"/>
       <c r="Y624" s="2" t="inlineStr"/>
       <c r="Z624" s="2" t="inlineStr"/>
-      <c r="AA624" s="2" t="inlineStr">
-        <is>
-          <t>The field is a value that indicates whether an item is considered returnable.
-This field is mainly used for purchased items. However, since the indicator is also contained in the item master it can influence different acquisition types.</t>
-        </is>
-      </c>
-      <c r="AB624" s="2" t="inlineStr">
-        <is>
-          <t>0: The item is fully returnable.
-1: The item is returnable with restrictions. Only for information; no warnings are issued.
-2: The item is not returnable to the supplier. You can receive warning messages at customer order entry and customer order return when manually adding a material line on a work order, when entering a planned purchase order, and when entering a purchase order line. You can also receive warning message 65 on the planned purchase order to avoid an auto release.
-3: The item is not returnable to us and/or the supplier. Same as alternative 2, except that the customer order return and work order return can be blocked for this item.</t>
-        </is>
-      </c>
+      <c r="AA624" s="2" t="inlineStr"/>
+      <c r="AB624" s="2" t="inlineStr"/>
       <c r="AC624" s="2" t="inlineStr"/>
       <c r="AD624" s="2" t="inlineStr"/>
       <c r="AE624" s="2" t="inlineStr">
@@ -54316,20 +52973,8 @@
       <c r="X625" s="2" t="inlineStr"/>
       <c r="Y625" s="2" t="inlineStr"/>
       <c r="Z625" s="2" t="inlineStr"/>
-      <c r="AA625" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the types of returnable messages that can appear.</t>
-        </is>
-      </c>
-      <c r="AB625" s="2" t="inlineStr">
-        <is>
-          <t>0: No messages.
-1: Warning message in WO/CO entry and warning message in WO/CO return.
-2: Warning message in WO/CO entry and error message in WO/CO return.
-3: No message in WO/CO entry. Warning message in WO/CO return.
-4: No message in WO/CO entry. Error message in WO/CO return.</t>
-        </is>
-      </c>
+      <c r="AA625" s="2" t="inlineStr"/>
+      <c r="AB625" s="2" t="inlineStr"/>
       <c r="AC625" s="2" t="inlineStr"/>
       <c r="AD625" s="2" t="inlineStr"/>
       <c r="AE625" s="2" t="inlineStr">
@@ -54411,19 +53056,8 @@
       <c r="X626" s="2" t="inlineStr"/>
       <c r="Y626" s="2" t="inlineStr"/>
       <c r="Z626" s="2" t="inlineStr"/>
-      <c r="AA626" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if an item should be considered as not stocked or stocked. This parameter can be set manually or automatically (RPS920).</t>
-        </is>
-      </c>
-      <c r="AB626" s="2" t="inlineStr">
-        <is>
-          <t>Blank: Not used.
-10: Not stocked - The item should normally not have stock, and therefore any safety stock, reorder point, forecast, etc. is neglected.
-20: To be stocked - The item has qualified for being stocked but is currently in an aging period. When the aging period is over, the item will be validated once again against the "Add to stock" settings. If qualified, it will be Stocked. If not qualified, it will go back to Not stocked.
-30: Stocked.</t>
-        </is>
-      </c>
+      <c r="AA626" s="2" t="inlineStr"/>
+      <c r="AB626" s="2" t="inlineStr"/>
       <c r="AC626" s="2" t="inlineStr"/>
       <c r="AD626" s="2" t="inlineStr"/>
       <c r="AE626" s="2" t="inlineStr">
@@ -54501,13 +53135,7 @@
       <c r="X627" s="2" t="inlineStr"/>
       <c r="Y627" s="2" t="inlineStr"/>
       <c r="Z627" s="2" t="inlineStr"/>
-      <c r="AA627" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the aging minutes, which are the number of minutes that the product must age before it can be used. It is typically used in conjunction with the Aging days field and/or Aging hours field. You cannot enter the aging minutes to be greater than 59.
-Aging can only be used for manufactured items. At receipt, the balance ID will get status 1 (Under inspection) in (MMS060). At the same time, a reclassification transaction will be created in the material plan on the date when the product is available. The reclassification is performed by an autojob process.
-You control whether aging should be used on the manufacturing order type.</t>
-        </is>
-      </c>
+      <c r="AA627" s="2" t="inlineStr"/>
       <c r="AB627" s="2" t="inlineStr"/>
       <c r="AC627" s="2" t="inlineStr"/>
       <c r="AD627" s="2" t="inlineStr"/>
@@ -54590,12 +53218,7 @@
       <c r="X628" s="2" t="inlineStr"/>
       <c r="Y628" s="2" t="inlineStr"/>
       <c r="Z628" s="2" t="inlineStr"/>
-      <c r="AA628" s="2" t="inlineStr">
-        <is>
-          <t>This is the number of days that the product keeps its properties and quality.
-This is used to calculate the best before date when a lot or serial number is created, and the best before date is stored for each lot number or serial number in (MMS235).</t>
-        </is>
-      </c>
+      <c r="AA628" s="2" t="inlineStr"/>
       <c r="AB628" s="2" t="inlineStr"/>
       <c r="AC628" s="2" t="inlineStr"/>
       <c r="AD628" s="2" t="inlineStr"/>
@@ -54678,20 +53301,8 @@
       <c r="X629" s="2" t="inlineStr"/>
       <c r="Y629" s="2" t="inlineStr"/>
       <c r="Z629" s="2" t="inlineStr"/>
-      <c r="AA629" s="2" t="inlineStr">
-        <is>
-          <t>This field indicates if frozen safety stock is used. Depending on the desired behavior, this setting can be activated in (MMS002/F) or (RPS040/E).</t>
-        </is>
-      </c>
-      <c r="AB629" s="2" t="inlineStr">
-        <is>
-          <t>0: Safety stock is calculated according to 'Safety stock method'. This can be overridden by settings in (RPS040).
-1: Temporary frozen safety stock is used. A fixed value, entered in the field 'Safety stock' will be used until  it is exceeded by the result of the safety stock calculation (for example, running (MMS615)).
-0: Safety stock is calculated according to settings in (MMS002/F).
-1: Date-controlled frozen safety stock is used. A fixed value, entered in the field 'Calculated extra safety stock' will be used as safety stock until the 'To date' has passed. No inventory build-up trasactions (category 020) will be created in the material plan.
-2: A combination of date-controlled and temporary frozen safety stock is used. A fixed value, entered in the field 'Calculated extra safety stock' will be used as safety stock until the 'To date' has passed, or it is exceeded by the result of the safety stock calculation. No inventory build-up trasactions (category 020) will be created in the material plan.</t>
-        </is>
-      </c>
+      <c r="AA629" s="2" t="inlineStr"/>
+      <c r="AB629" s="2" t="inlineStr"/>
       <c r="AC629" s="2" t="inlineStr"/>
       <c r="AD629" s="2" t="inlineStr"/>
       <c r="AE629" s="2" t="inlineStr">
@@ -54773,12 +53384,7 @@
       <c r="X630" s="2" t="inlineStr"/>
       <c r="Y630" s="2" t="inlineStr"/>
       <c r="Z630" s="2" t="inlineStr"/>
-      <c r="AA630" s="2" t="inlineStr">
-        <is>
-          <t>This field indicates a reason code, which describes why the safety stock is frozen.
-Safety stock reason codes are managed in (MMS092).</t>
-        </is>
-      </c>
+      <c r="AA630" s="2" t="inlineStr"/>
       <c r="AB630" s="2" t="inlineStr"/>
       <c r="AC630" s="2" t="inlineStr">
         <is>
@@ -54861,11 +53467,7 @@
       <c r="X631" s="2" t="inlineStr"/>
       <c r="Y631" s="2" t="inlineStr"/>
       <c r="Z631" s="2" t="inlineStr"/>
-      <c r="AA631" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a classification of items in a selected warehouse.</t>
-        </is>
-      </c>
+      <c r="AA631" s="2" t="inlineStr"/>
       <c r="AB631" s="2" t="inlineStr"/>
       <c r="AC631" s="2" t="inlineStr">
         <is>
@@ -54952,12 +53554,7 @@
       <c r="X632" s="2" t="inlineStr"/>
       <c r="Y632" s="2" t="inlineStr"/>
       <c r="Z632" s="2" t="inlineStr"/>
-      <c r="AA632" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the quantity that is typically requested or issued in a single delivery. It is entered manually and not calculated automatically.
-When safety stock is calculated, it will not be set lower than the average issue quantity.</t>
-        </is>
-      </c>
+      <c r="AA632" s="2" t="inlineStr"/>
       <c r="AB632" s="2" t="inlineStr"/>
       <c r="AC632" s="2" t="inlineStr"/>
       <c r="AD632" s="2" t="inlineStr"/>
@@ -55044,11 +53641,7 @@
       <c r="X633" s="2" t="inlineStr"/>
       <c r="Y633" s="2" t="inlineStr"/>
       <c r="Z633" s="2" t="inlineStr"/>
-      <c r="AA633" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the minimum safety stock level. When safety stock is calculated, it will not be set lower than the minimum safety stock.</t>
-        </is>
-      </c>
+      <c r="AA633" s="2" t="inlineStr"/>
       <c r="AB633" s="2" t="inlineStr"/>
       <c r="AC633" s="2" t="inlineStr"/>
       <c r="AD633" s="2" t="inlineStr"/>
@@ -55214,12 +53807,7 @@
       <c r="X635" s="2" t="inlineStr"/>
       <c r="Y635" s="2" t="inlineStr"/>
       <c r="Z635" s="2" t="inlineStr"/>
-      <c r="AA635" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the product line for an item which is used to facilitate purchase planning by grouping similar types of items from a supplier.
-Product lines are defined in (CRS099) and can be entered either for each item record on (MMS001/E) or for each item-warehouse record on (MMS002/F), depending on the value of the product line level on (CRS780/H).</t>
-        </is>
-      </c>
+      <c r="AA635" s="2" t="inlineStr"/>
       <c r="AB635" s="2" t="inlineStr"/>
       <c r="AC635" s="2" t="inlineStr">
         <is>
@@ -55399,12 +53987,7 @@
       <c r="X637" s="2" t="inlineStr"/>
       <c r="Y637" s="2" t="inlineStr"/>
       <c r="Z637" s="2" t="inlineStr"/>
-      <c r="AA637" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates company number, which is the primary identity in all files in the M3 system. The purpose of this is to be able to handle, in the same database, several companies completely or partially separated.
-A maximum of 999 companies may be handled in the same database.</t>
-        </is>
-      </c>
+      <c r="AA637" s="2" t="inlineStr"/>
       <c r="AB637" s="2" t="inlineStr"/>
       <c r="AC637" s="2" t="inlineStr">
         <is>
@@ -55527,14 +54110,7 @@
         </is>
       </c>
       <c r="Z638" s="2" t="inlineStr"/>
-      <c r="AA638" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the facility used.
-Facilities are used to set authorization in time reporting component groups and for activities such as sales, production or distribution.
-A facility is a superior organizational level to a department but lower than a division, that is, a facility belongs to a division, which in turn belongs to a company. A facility can contain one or more warehouses. A user is always connected to a pre-selected facility. All product data and production data are stored per facility, and several facilities can exist in the same database. All planning occurs per warehouse, although the highest planning level in M3 can be the facility, when availability can be calculated per facility. However, this assumes that planning method 4 is used.
-Facilities are defined in (CRS008).</t>
-        </is>
-      </c>
+      <c r="AA638" s="2" t="inlineStr"/>
       <c r="AB638" s="2" t="inlineStr"/>
       <c r="AC638" s="2" t="inlineStr">
         <is>
@@ -55653,12 +54229,7 @@
       </c>
       <c r="Y639" s="2" t="inlineStr"/>
       <c r="Z639" s="2" t="inlineStr"/>
-      <c r="AA639" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the item number (for Maintenance, the item number or equipment number), which is a unique ID for an individual item.
-Items are entered and maintained in (MMS001). Item number can consist up to 15 alphanumeric characters.</t>
-        </is>
-      </c>
+      <c r="AA639" s="2" t="inlineStr"/>
       <c r="AB639" s="2" t="inlineStr"/>
       <c r="AC639" s="2" t="inlineStr">
         <is>
@@ -55749,12 +54320,7 @@
       <c r="X640" s="2" t="inlineStr"/>
       <c r="Y640" s="2" t="inlineStr"/>
       <c r="Z640" s="2" t="inlineStr"/>
-      <c r="AA640" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the administrative lead time, which is entered for each item and facility. The administrative lead time is added to the total lead time for each item and warehouse. The administrative lead time is only applicable for acquisition methods 1, 2 and 3.
-In principle the administrative lead time can be considered as the time allotted to perform activities that are required before a planned order can be released. For example, a quotation inquiry.</t>
-        </is>
-      </c>
+      <c r="AA640" s="2" t="inlineStr"/>
       <c r="AB640" s="2" t="inlineStr"/>
       <c r="AC640" s="2" t="inlineStr"/>
       <c r="AD640" s="2" t="inlineStr"/>
@@ -55861,11 +54427,7 @@
       </c>
       <c r="Y641" s="2" t="inlineStr"/>
       <c r="Z641" s="2" t="inlineStr"/>
-      <c r="AA641" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the customs statistics number, which is specified for each item/facility. It is used in printouts of various shipping documents, such as the unit document. It is also used for regulating and calculating data for transactions to INTRASTAT, the trade statistics of the EU.</t>
-        </is>
-      </c>
+      <c r="AA641" s="2" t="inlineStr"/>
       <c r="AB641" s="2" t="inlineStr"/>
       <c r="AC641" s="2" t="inlineStr">
         <is>
@@ -55952,13 +54514,7 @@
       <c r="X642" s="2" t="inlineStr"/>
       <c r="Y642" s="2" t="inlineStr"/>
       <c r="Z642" s="2" t="inlineStr"/>
-      <c r="AA642" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a recalculation factor supplement U/M. It is used when a delivered or received quantity is to be recalculated to the supplement U/M, which is valid for a EU customs number.
-Recalculation is based on the net weight for items.
-Delivered or received quantity in supplement U/M is sometimes used when transactions for INTRASTAT are created by the system.</t>
-        </is>
-      </c>
+      <c r="AA642" s="2" t="inlineStr"/>
       <c r="AB642" s="2" t="inlineStr"/>
       <c r="AC642" s="2" t="inlineStr"/>
       <c r="AD642" s="2" t="inlineStr"/>
@@ -56049,13 +54605,7 @@
       <c r="X643" s="2" t="inlineStr"/>
       <c r="Y643" s="2" t="inlineStr"/>
       <c r="Z643" s="2" t="inlineStr"/>
-      <c r="AA643" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the itemâs country of origin. It is retrieved from (MMS003).
-For Intrastat transactions split per country of origin of the lot number, as set in (CRS726), the field is instead updated from (MMS235).
-The information can be used for trade statistics reported to the authorities.</t>
-        </is>
-      </c>
+      <c r="AA643" s="2" t="inlineStr"/>
       <c r="AB643" s="2" t="inlineStr"/>
       <c r="AC643" s="2" t="inlineStr"/>
       <c r="AD643" s="2" t="inlineStr"/>
@@ -56142,16 +54692,7 @@
       <c r="X644" s="2" t="inlineStr"/>
       <c r="Y644" s="2" t="inlineStr"/>
       <c r="Z644" s="2" t="inlineStr"/>
-      <c r="AA644" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the average cost saved per item/facility in the local currency.
-The average cost is the cost of items issued from stock. The current average cost is used as the transaction price for all negative inventory transactions.
-This cost is calculated using the moving weighted average cost method. It is updated using the acquisition cost for each positive inventory transaction in M3.
-The formula for automatic calculation of the average cost is:
-((Current on-hand balance*Current average cost)+(Trans. quantity*Acquisition cost))/New on-hand balance.
-However, you can manually set an average cost for an item/facility in (CAS370) or in (CAS371). You can do this to set an initial average cost for an item or to change an incorrect average cost.</t>
-        </is>
-      </c>
+      <c r="AA644" s="2" t="inlineStr"/>
       <c r="AB644" s="2" t="inlineStr"/>
       <c r="AC644" s="2" t="inlineStr"/>
       <c r="AD644" s="2" t="inlineStr"/>
@@ -56246,11 +54787,7 @@
       <c r="X645" s="2" t="inlineStr"/>
       <c r="Y645" s="2" t="inlineStr"/>
       <c r="Z645" s="2" t="inlineStr"/>
-      <c r="AA645" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the standard cost for the item, calculated per item/facility.</t>
-        </is>
-      </c>
+      <c r="AA645" s="2" t="inlineStr"/>
       <c r="AB645" s="2" t="inlineStr"/>
       <c r="AC645" s="2" t="inlineStr"/>
       <c r="AD645" s="2" t="inlineStr"/>
@@ -56345,13 +54882,7 @@
       <c r="X646" s="2" t="inlineStr"/>
       <c r="Y646" s="2" t="inlineStr"/>
       <c r="Z646" s="2" t="inlineStr"/>
-      <c r="AA646" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ordering costs per item, expressed in domestic currency. This is for the fixed costs arising each time the corresponding item is purchased or manufactured.
-The ordering cost is used for calculating the economic order quantity according to the Wilson formula, and when lot sizes are calculated for requirements planning.
-If the ordering cost per item is missing, use the one entered as parameter in (CRS730).</t>
-        </is>
-      </c>
+      <c r="AA646" s="2" t="inlineStr"/>
       <c r="AB646" s="2" t="inlineStr"/>
       <c r="AC646" s="2" t="inlineStr"/>
       <c r="AD646" s="2" t="inlineStr"/>
@@ -56438,12 +54969,7 @@
       <c r="X647" s="2" t="inlineStr"/>
       <c r="Y647" s="2" t="inlineStr"/>
       <c r="Z647" s="2" t="inlineStr"/>
-      <c r="AA647" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the product's theoretical yield, expressed as a percentage to two decimal places. You can specify either the yield percentage or the yield quantity manually. If you leave this value blank, it will be calculated automatically.
-The yield is calculated as the quotient between the yield quantity and the batch quantity.</t>
-        </is>
-      </c>
+      <c r="AA647" s="2" t="inlineStr"/>
       <c r="AB647" s="2" t="inlineStr"/>
       <c r="AC647" s="2" t="inlineStr"/>
       <c r="AD647" s="2" t="inlineStr"/>
@@ -56787,14 +55313,7 @@
       <c r="X651" s="2" t="inlineStr"/>
       <c r="Y651" s="2" t="inlineStr"/>
       <c r="Z651" s="2" t="inlineStr"/>
-      <c r="AA651" s="2" t="inlineStr">
-        <is>
-          <t>This field indicates the lead time method for manufactured items. (Note that the field also applies for work orders.)
-Select the check box if the operation time should be automatically calculated depending on the setup time and run time for each operation. The product lead time is calculated by adding the operation time from the operations included in the product structure. This method does consider order quantity, queue time, transportation time, etc.
-Do not select the check box if the operation times should be managed manually. Then a lead time offset is entered for each operation to set the number of days before the product's finish date that an operation must start. The product lead time equals the longest lead time offset. This method ignores quantity when calculating the total lead time for the manufacturing order. However, the order quantity affects the operation time on the manufacturing order.
-This field is normally activated.</t>
-        </is>
-      </c>
+      <c r="AA651" s="2" t="inlineStr"/>
       <c r="AB651" s="2" t="inlineStr"/>
       <c r="AC651" s="2" t="inlineStr"/>
       <c r="AD651" s="2" t="inlineStr"/>
@@ -56885,11 +55404,7 @@
       <c r="X652" s="2" t="inlineStr"/>
       <c r="Y652" s="2" t="inlineStr"/>
       <c r="Z652" s="2" t="inlineStr"/>
-      <c r="AA652" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the time fence (in days) for when dynamic lead time is calculated. A manufacturing order is within the time fence when its planned finish date is.</t>
-        </is>
-      </c>
+      <c r="AA652" s="2" t="inlineStr"/>
       <c r="AB652" s="2" t="inlineStr"/>
       <c r="AC652" s="2" t="inlineStr"/>
       <c r="AD652" s="2" t="inlineStr"/>
@@ -56980,18 +55495,8 @@
       <c r="X653" s="2" t="inlineStr"/>
       <c r="Y653" s="2" t="inlineStr"/>
       <c r="Z653" s="2" t="inlineStr"/>
-      <c r="AA653" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if the item should be flow order planned within the specified flow order fence.</t>
-        </is>
-      </c>
-      <c r="AB653" s="2" t="inlineStr">
-        <is>
-          <t>0: No
-1: Yes, within the flow order fence
-2: Yes, within the flow order fence and for all released manufacturing orders.</t>
-        </is>
-      </c>
+      <c r="AA653" s="2" t="inlineStr"/>
+      <c r="AB653" s="2" t="inlineStr"/>
       <c r="AC653" s="2" t="inlineStr"/>
       <c r="AD653" s="2" t="inlineStr"/>
       <c r="AE653" s="2" t="inlineStr">
@@ -57081,11 +55586,7 @@
       <c r="X654" s="2" t="inlineStr"/>
       <c r="Y654" s="2" t="inlineStr"/>
       <c r="Z654" s="2" t="inlineStr"/>
-      <c r="AA654" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of days within which manufacturing orders are to be classified as flow orders.</t>
-        </is>
-      </c>
+      <c r="AA654" s="2" t="inlineStr"/>
       <c r="AB654" s="2" t="inlineStr"/>
       <c r="AC654" s="2" t="inlineStr"/>
       <c r="AD654" s="2" t="inlineStr"/>
@@ -57176,13 +55677,7 @@
       <c r="X655" s="2" t="inlineStr"/>
       <c r="Y655" s="2" t="inlineStr"/>
       <c r="Z655" s="2" t="inlineStr"/>
-      <c r="AA655" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if a production rate is activated for the current item.
-Production rate is set in (RPS030) and makes it possible to control the production based on date. The requirements calculation then distributes the order quantity into one order per bucket. If you instead enter a fixed order quantity in (MMS002/F), then this quantity is considered as one order in the requirements calculation.
-The item/warehouse for which you want to use a production rate must have order policy 23 or 24.</t>
-        </is>
-      </c>
+      <c r="AA655" s="2" t="inlineStr"/>
       <c r="AB655" s="2" t="inlineStr"/>
       <c r="AC655" s="2" t="inlineStr"/>
       <c r="AD655" s="2" t="inlineStr"/>
@@ -57360,14 +55855,7 @@
       <c r="X657" s="2" t="inlineStr"/>
       <c r="Y657" s="2" t="inlineStr"/>
       <c r="Z657" s="2" t="inlineStr"/>
-      <c r="AA657" s="2" t="inlineStr">
-        <is>
-          <t>This field indicates if the item should be reserved for a manufacturing order.
-Select the check box if the item should be reserved for a manufacturing order.
-The selection is specified for each item/facility.
-In those cases the item is controlled by a reorder point and is used frequently, this parameter helps minimize the load on the system. However, if reservations are not made, the item cannot be picked using a picking list. Instead it must issued using one of the automatic functions (refer to MO issue type).</t>
-        </is>
-      </c>
+      <c r="AA657" s="2" t="inlineStr"/>
       <c r="AB657" s="2" t="inlineStr"/>
       <c r="AC657" s="2" t="inlineStr"/>
       <c r="AD657" s="2" t="inlineStr"/>
@@ -57458,12 +55946,7 @@
       <c r="X658" s="2" t="inlineStr"/>
       <c r="Y658" s="2" t="inlineStr"/>
       <c r="Z658" s="2" t="inlineStr"/>
-      <c r="AA658" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if the item is manufactured and delivered with or without a manufacturing order.
-Select the check box if the item is manufactured and delivered without a manufacturing order.</t>
-        </is>
-      </c>
+      <c r="AA658" s="2" t="inlineStr"/>
       <c r="AB658" s="2" t="inlineStr"/>
       <c r="AC658" s="2" t="inlineStr"/>
       <c r="AD658" s="2" t="inlineStr"/>
@@ -57570,12 +56053,7 @@
         </is>
       </c>
       <c r="Z659" s="2" t="inlineStr"/>
-      <c r="AA659" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the main warehouse for the current item per facility. The item's cost is retrieved from the main warehouse. For situations where the item is connected to several warehouses and acquired in different ways, then the acquisition code set for the main warehouse is retrieved to calculate the cost.
-When the item is scheduled with optimal on-hand balance per facility, acquisition is pressumed to be from the main warehouse. - Manufactured items have necessay connections from the facility to the item/warehouse, which are made according to settings in the main warehouse.</t>
-        </is>
-      </c>
+      <c r="AA659" s="2" t="inlineStr"/>
       <c r="AB659" s="2" t="inlineStr"/>
       <c r="AC659" s="2" t="inlineStr"/>
       <c r="AD659" s="2" t="inlineStr"/>
@@ -57670,13 +56148,7 @@
       <c r="X660" s="2" t="inlineStr"/>
       <c r="Y660" s="2" t="inlineStr"/>
       <c r="Z660" s="2" t="inlineStr"/>
-      <c r="AA660" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the optimal on-hand balance for each facility.
-If this point is not reached, the order control method specified for the facility's main warehouse is checked.
-If the current warehouse has method 4 and existing orders (planned or released) do not cover the quantity needed, a planned order will be created.</t>
-        </is>
-      </c>
+      <c r="AA660" s="2" t="inlineStr"/>
       <c r="AB660" s="2" t="inlineStr"/>
       <c r="AC660" s="2" t="inlineStr"/>
       <c r="AD660" s="2" t="inlineStr"/>
@@ -57771,11 +56243,7 @@
       <c r="X661" s="2" t="inlineStr"/>
       <c r="Y661" s="2" t="inlineStr"/>
       <c r="Z661" s="2" t="inlineStr"/>
-      <c r="AA661" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the facility's on-hand balance, which is maintained according to the on-hand balance method.</t>
-        </is>
-      </c>
+      <c r="AA661" s="2" t="inlineStr"/>
       <c r="AB661" s="2" t="inlineStr"/>
       <c r="AC661" s="2" t="inlineStr"/>
       <c r="AD661" s="2" t="inlineStr"/>
@@ -57870,11 +56338,7 @@
       <c r="X662" s="2" t="inlineStr"/>
       <c r="Y662" s="2" t="inlineStr"/>
       <c r="Z662" s="2" t="inlineStr"/>
-      <c r="AA662" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the inspected facility's on-hand balance, which is maintained according to the on-hand balance method.</t>
-        </is>
-      </c>
+      <c r="AA662" s="2" t="inlineStr"/>
       <c r="AB662" s="2" t="inlineStr"/>
       <c r="AC662" s="2" t="inlineStr"/>
       <c r="AD662" s="2" t="inlineStr"/>
@@ -57969,11 +56433,7 @@
       <c r="X663" s="2" t="inlineStr"/>
       <c r="Y663" s="2" t="inlineStr"/>
       <c r="Z663" s="2" t="inlineStr"/>
-      <c r="AA663" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the rejected facility's on-hand balance, which is maintained according to the on-hand balance method.</t>
-        </is>
-      </c>
+      <c r="AA663" s="2" t="inlineStr"/>
       <c r="AB663" s="2" t="inlineStr"/>
       <c r="AC663" s="2" t="inlineStr"/>
       <c r="AD663" s="2" t="inlineStr"/>
@@ -58064,18 +56524,8 @@
       <c r="X664" s="2" t="inlineStr"/>
       <c r="Y664" s="2" t="inlineStr"/>
       <c r="Z664" s="2" t="inlineStr"/>
-      <c r="AA664" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates which method is to be used when calculating the on-hand balance for the facility.</t>
-        </is>
-      </c>
-      <c r="AB664" s="2" t="inlineStr">
-        <is>
-          <t>0: Do not accumulate on-hand balance
-1: Accumulate changes in balance regarding statuses 2 and 3
-2: Accumulate changes according to transaction types: - Purchasing, order category 1 - Physical inventory differences - Manufacturing - Sales - Scrap. This method is intended for use within maintenance-oriented activities.</t>
-        </is>
-      </c>
+      <c r="AA664" s="2" t="inlineStr"/>
+      <c r="AB664" s="2" t="inlineStr"/>
       <c r="AC664" s="2" t="inlineStr"/>
       <c r="AD664" s="2" t="inlineStr"/>
       <c r="AE664" s="2" t="inlineStr">
@@ -58335,13 +56785,7 @@
       <c r="X667" s="2" t="inlineStr"/>
       <c r="Y667" s="2" t="inlineStr"/>
       <c r="Z667" s="2" t="inlineStr"/>
-      <c r="AA667" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if a prompt to create a manufacturing order (MO) for dynamically configured manufactured items is made immediately after customer order (CO) line entry.
-Select the check box to prompt to create a manufacturing order (MO) for dynamically configured manufactured items is made immediately after customer order (CO) line entry.
-Dynamically configured manufactured items have configuration code 1.</t>
-        </is>
-      </c>
+      <c r="AA667" s="2" t="inlineStr"/>
       <c r="AB667" s="2" t="inlineStr"/>
       <c r="AC667" s="2" t="inlineStr"/>
       <c r="AD667" s="2" t="inlineStr"/>
@@ -58432,11 +56876,7 @@
       <c r="X668" s="2" t="inlineStr"/>
       <c r="Y668" s="2" t="inlineStr"/>
       <c r="Z668" s="2" t="inlineStr"/>
-      <c r="AA668" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the consumption code, which is defined for each item used for trade statistics.</t>
-        </is>
-      </c>
+      <c r="AA668" s="2" t="inlineStr"/>
       <c r="AB668" s="2" t="inlineStr"/>
       <c r="AC668" s="2" t="inlineStr">
         <is>
@@ -58531,12 +56971,7 @@
       <c r="X669" s="2" t="inlineStr"/>
       <c r="Y669" s="2" t="inlineStr"/>
       <c r="Z669" s="2" t="inlineStr"/>
-      <c r="AA669" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates an area, province or state within a country. The information is used for addresses, U.S. sales tax and for trade statistics.
-When editing addresses, the information is validated when state is used as an address element according to the address formatting rule (CRS117), used for the country to which the address applies. Address formatting rules are stated for each country (CRS045/E).</t>
-        </is>
-      </c>
+      <c r="AA669" s="2" t="inlineStr"/>
       <c r="AB669" s="2" t="inlineStr"/>
       <c r="AC669" s="2" t="inlineStr">
         <is>
@@ -58627,12 +57062,7 @@
       <c r="X670" s="2" t="inlineStr"/>
       <c r="Y670" s="2" t="inlineStr"/>
       <c r="Z670" s="2" t="inlineStr"/>
-      <c r="AA670" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the customs procedure used for the import of goods.
-The information is used to update the trade statistics.</t>
-        </is>
-      </c>
+      <c r="AA670" s="2" t="inlineStr"/>
       <c r="AB670" s="2" t="inlineStr"/>
       <c r="AC670" s="2" t="inlineStr">
         <is>
@@ -58723,11 +57153,7 @@
       <c r="X671" s="2" t="inlineStr"/>
       <c r="Y671" s="2" t="inlineStr"/>
       <c r="Z671" s="2" t="inlineStr"/>
-      <c r="AA671" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the customs procedure used for the export of goods.</t>
-        </is>
-      </c>
+      <c r="AA671" s="2" t="inlineStr"/>
       <c r="AB671" s="2" t="inlineStr"/>
       <c r="AC671" s="2" t="inlineStr">
         <is>
@@ -58818,12 +57244,7 @@
       <c r="X672" s="2" t="inlineStr"/>
       <c r="Y672" s="2" t="inlineStr"/>
       <c r="Z672" s="2" t="inlineStr"/>
-      <c r="AA672" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of the costing model used for each item.
-Costing models are defined in (PPS285).</t>
-        </is>
-      </c>
+      <c r="AA672" s="2" t="inlineStr"/>
       <c r="AB672" s="2" t="inlineStr"/>
       <c r="AC672" s="2" t="inlineStr">
         <is>
@@ -58914,14 +57335,7 @@
       <c r="X673" s="2" t="inlineStr"/>
       <c r="Y673" s="2" t="inlineStr"/>
       <c r="Z673" s="2" t="inlineStr"/>
-      <c r="AA673" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of the product costing model.
-The costing model is defined in (PCS025).
-For manufacturing the costing model is generally applied in (PCS001), or in (MMS003) for item per facility.
-For maintenance the costing model is generally applied in (CRS788), parameter 21, or in (MOS301/F) for service per facility.</t>
-        </is>
-      </c>
+      <c r="AA673" s="2" t="inlineStr"/>
       <c r="AB673" s="2" t="inlineStr"/>
       <c r="AC673" s="2" t="inlineStr"/>
       <c r="AD673" s="2" t="inlineStr"/>
@@ -59008,13 +57422,7 @@
       <c r="X674" s="2" t="inlineStr"/>
       <c r="Y674" s="2" t="inlineStr"/>
       <c r="Z674" s="2" t="inlineStr"/>
-      <c r="AA674" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of a process planning item.
-By entering a process planning item, you define an item as an end product. The end product is an item that is the result of a planning process.
-A process planning item must be set to inventory accounting code 2 in (MMS001) and master scheduling code 4 in (MMS002).</t>
-        </is>
-      </c>
+      <c r="AA674" s="2" t="inlineStr"/>
       <c r="AB674" s="2" t="inlineStr"/>
       <c r="AC674" s="2" t="inlineStr"/>
       <c r="AD674" s="2" t="inlineStr"/>
@@ -59101,12 +57509,7 @@
       <c r="X675" s="2" t="inlineStr"/>
       <c r="Y675" s="2" t="inlineStr"/>
       <c r="Z675" s="2" t="inlineStr"/>
-      <c r="AA675" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the process planning item for a push process.
-This functin is not activated in the current release of M3.</t>
-        </is>
-      </c>
+      <c r="AA675" s="2" t="inlineStr"/>
       <c r="AB675" s="2" t="inlineStr"/>
       <c r="AC675" s="2" t="inlineStr"/>
       <c r="AD675" s="2" t="inlineStr"/>
@@ -59193,12 +57596,7 @@
       <c r="X676" s="2" t="inlineStr"/>
       <c r="Y676" s="2" t="inlineStr"/>
       <c r="Z676" s="2" t="inlineStr"/>
-      <c r="AA676" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the ID of a costing model for sales prices.
-Costing models can be connected to different price lists and are used to calculate both basic prices and order-costed prices. It is also used for price origin C (price is calculated online at CO line entry).</t>
-        </is>
-      </c>
+      <c r="AA676" s="2" t="inlineStr"/>
       <c r="AB676" s="2" t="inlineStr"/>
       <c r="AC676" s="2" t="inlineStr">
         <is>
@@ -59289,12 +57687,7 @@
       <c r="X677" s="2" t="inlineStr"/>
       <c r="Y677" s="2" t="inlineStr"/>
       <c r="Z677" s="2" t="inlineStr"/>
-      <c r="AA677" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the sales price on a customer order line with line type 0 is calculated (dynamically) during customer order entry.
-Select the check box if line type 0 should be calculated (dynamically) during customer order entry.</t>
-        </is>
-      </c>
+      <c r="AA677" s="2" t="inlineStr"/>
       <c r="AB677" s="2" t="inlineStr"/>
       <c r="AC677" s="2" t="inlineStr"/>
       <c r="AD677" s="2" t="inlineStr"/>
@@ -59385,12 +57778,7 @@
       <c r="X678" s="2" t="inlineStr"/>
       <c r="Y678" s="2" t="inlineStr"/>
       <c r="Z678" s="2" t="inlineStr"/>
-      <c r="AA678" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the sales price on a customer order line with line type 1 is calculated (dynamically) during customer order entry.
-Select the check box if customer order line with line type 1 should be calculated (dynamically) during customer order entry.</t>
-        </is>
-      </c>
+      <c r="AA678" s="2" t="inlineStr"/>
       <c r="AB678" s="2" t="inlineStr"/>
       <c r="AC678" s="2" t="inlineStr"/>
       <c r="AD678" s="2" t="inlineStr"/>
@@ -59481,12 +57869,7 @@
       <c r="X679" s="2" t="inlineStr"/>
       <c r="Y679" s="2" t="inlineStr"/>
       <c r="Z679" s="2" t="inlineStr"/>
-      <c r="AA679" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates whether the sales price on a customer order line with line type 2 is dynamically calculated during customer order entry.
-Select the check box if sales price on a customer order line with line type 2 should be dynamically calculated during customer order entry.</t>
-        </is>
-      </c>
+      <c r="AA679" s="2" t="inlineStr"/>
       <c r="AB679" s="2" t="inlineStr"/>
       <c r="AC679" s="2" t="inlineStr"/>
       <c r="AD679" s="2" t="inlineStr"/>
@@ -59577,19 +57960,8 @@
       <c r="X680" s="2" t="inlineStr"/>
       <c r="Y680" s="2" t="inlineStr"/>
       <c r="Z680" s="2" t="inlineStr"/>
-      <c r="AA680" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the default value for the preliminary price code field on customer order line (line type 0). The preliminary price code on a CO line determines whether the sales price on a customer order line is preliminary. Customer order lines flagged as preliminary priced are not invoiced until the flag is removed.</t>
-        </is>
-      </c>
-      <c r="AB680" s="2" t="inlineStr">
-        <is>
-          <t>0: Sales price is final (not preliminary).
-1: Preliniary sales price.
-2: Preliniary sales price.
-3: Preliminary sales price.</t>
-        </is>
-      </c>
+      <c r="AA680" s="2" t="inlineStr"/>
+      <c r="AB680" s="2" t="inlineStr"/>
       <c r="AC680" s="2" t="inlineStr"/>
       <c r="AD680" s="2" t="inlineStr"/>
       <c r="AE680" s="2" t="inlineStr">
@@ -59679,19 +58051,8 @@
       <c r="X681" s="2" t="inlineStr"/>
       <c r="Y681" s="2" t="inlineStr"/>
       <c r="Z681" s="2" t="inlineStr"/>
-      <c r="AA681" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the default value for the preliminary price code on the CO (customer order) line for line type 1. Preliminary price code on CO line controls whether the sales price on a customer order line is preliminary or not. Customer order lines with preliminary price marking will not be invoiced until the marking has been removed.</t>
-        </is>
-      </c>
-      <c r="AB681" s="2" t="inlineStr">
-        <is>
-          <t>0: The sales price is not preliminary.
-1: The sales price is preliminary. The preliminary price marking will automatically be set to 0 (final price) if sales price calculation is performed from: - Purchase proposal (PPS170) - Purchase order line (PPS201) - Purchase confirmation (PPS250) - Check supplier invoice (PPS405) - Re-calculate sales price (OIS156).
-2: The sales price is preliminary. The preliminary price marking will automatically be set to 0 (final price) if sales price calculation is performed from: - Check supplier invoice (PPS405) - Re-calculate sales price (OIS156).
-3: The sales price is preliminary. The only way to remove the preliminary price marking is to change the order line.</t>
-        </is>
-      </c>
+      <c r="AA681" s="2" t="inlineStr"/>
+      <c r="AB681" s="2" t="inlineStr"/>
       <c r="AC681" s="2" t="inlineStr"/>
       <c r="AD681" s="2" t="inlineStr"/>
       <c r="AE681" s="2" t="inlineStr">
@@ -59781,19 +58142,8 @@
       <c r="X682" s="2" t="inlineStr"/>
       <c r="Y682" s="2" t="inlineStr"/>
       <c r="Z682" s="2" t="inlineStr"/>
-      <c r="AA682" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the default value for the preliminary price code on the CO (customer order) line for line type 2. Preliminary price code on CO line controls whether the sales price on a customer order line is preliminary or not. Customer order lines with preliminary price marking will not be invoiced until the marking has been removed.</t>
-        </is>
-      </c>
-      <c r="AB682" s="2" t="inlineStr">
-        <is>
-          <t>0: The sales price is not preliminary.
-1: The sales price is preliminary. The preliminary price marking will automatically be set to 0 (final price) if sales price calculation is performed from: - Purchase proposal (PPS170) - Purchase order line (PPS201) - Purchase confirmation (PPS250) - Check supplier invoice (PPS405) - Re-calculate sales price (OIS156).
-2: The sales price is preliminary. The preliminary price marking will automatically be set to 0 (final price) if sales price calculation is performed from: - Check supplier invoice (PPS405) - Re-calculate sales price (OIS156).
-3: The sales price is preliminary. The only way to remove the preliminary price marking is to change the order line.</t>
-        </is>
-      </c>
+      <c r="AA682" s="2" t="inlineStr"/>
+      <c r="AB682" s="2" t="inlineStr"/>
       <c r="AC682" s="2" t="inlineStr"/>
       <c r="AD682" s="2" t="inlineStr"/>
       <c r="AE682" s="2" t="inlineStr">
@@ -59875,11 +58225,7 @@
       <c r="X683" s="2" t="inlineStr"/>
       <c r="Y683" s="2" t="inlineStr"/>
       <c r="Z683" s="2" t="inlineStr"/>
-      <c r="AA683" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the text ID, which identifies comments made. It is updated automatically when entering comments.</t>
-        </is>
-      </c>
+      <c r="AA683" s="2" t="inlineStr"/>
       <c r="AB683" s="2" t="inlineStr"/>
       <c r="AC683" s="2" t="inlineStr"/>
       <c r="AD683" s="2" t="inlineStr"/>
@@ -59962,11 +58308,7 @@
       <c r="X684" s="2" t="inlineStr"/>
       <c r="Y684" s="2" t="inlineStr"/>
       <c r="Z684" s="2" t="inlineStr"/>
-      <c r="AA684" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the unique key used to connect a detailed message with the original record.</t>
-        </is>
-      </c>
+      <c r="AA684" s="2" t="inlineStr"/>
       <c r="AB684" s="2" t="inlineStr"/>
       <c r="AC684" s="2" t="inlineStr"/>
       <c r="AD684" s="2" t="inlineStr"/>
@@ -60057,11 +58399,7 @@
       <c r="X685" s="2" t="inlineStr"/>
       <c r="Y685" s="2" t="inlineStr"/>
       <c r="Z685" s="2" t="inlineStr"/>
-      <c r="AA685" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the number of decimal places (up to four) that will be shown for the item cost.</t>
-        </is>
-      </c>
+      <c r="AA685" s="2" t="inlineStr"/>
       <c r="AB685" s="2" t="inlineStr"/>
       <c r="AC685" s="2" t="inlineStr"/>
       <c r="AD685" s="2" t="inlineStr"/>
@@ -60152,13 +58490,7 @@
       <c r="X686" s="2" t="inlineStr"/>
       <c r="Y686" s="2" t="inlineStr"/>
       <c r="Z686" s="2" t="inlineStr"/>
-      <c r="AA686" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the default item cost quantity per item/facility (or equipment, in the case of maintenance).
-However, if the field is used in an order line, it indicates a specific relationship between the value and that order line only. The order line value will then replace the default item cost quantity entered in (MMS003/E).
-The item cost quantity is always entered in the basic unit of measure of the item.</t>
-        </is>
-      </c>
+      <c r="AA686" s="2" t="inlineStr"/>
       <c r="AB686" s="2" t="inlineStr"/>
       <c r="AC686" s="2" t="inlineStr"/>
       <c r="AD686" s="2" t="inlineStr"/>
@@ -60241,11 +58573,7 @@
       <c r="X687" s="2" t="inlineStr"/>
       <c r="Y687" s="2" t="inlineStr"/>
       <c r="Z687" s="2" t="inlineStr"/>
-      <c r="AA687" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the environment group. Each item can be connected to a group that is defined in (CRS038).</t>
-        </is>
-      </c>
+      <c r="AA687" s="2" t="inlineStr"/>
       <c r="AB687" s="2" t="inlineStr"/>
       <c r="AC687" s="2" t="inlineStr">
         <is>
@@ -60340,22 +58668,8 @@
       <c r="X688" s="2" t="inlineStr"/>
       <c r="Y688" s="2" t="inlineStr"/>
       <c r="Z688" s="2" t="inlineStr"/>
-      <c r="AA688" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the inventory accounting method that defines how the cost of an item is determined per item/facility.</t>
-        </is>
-      </c>
-      <c r="AB688" s="2" t="inlineStr">
-        <is>
-          <t>0: Zero cost
-1: Standard cost
-2: Average cost
-3: Dynamic product cost
-4: Actual cost
-5: Simplified purchasing
-6: FIFO cost</t>
-        </is>
-      </c>
+      <c r="AA688" s="2" t="inlineStr"/>
+      <c r="AB688" s="2" t="inlineStr"/>
       <c r="AC688" s="2" t="inlineStr"/>
       <c r="AD688" s="2" t="inlineStr"/>
       <c r="AE688" s="2" t="inlineStr">
@@ -60449,12 +58763,7 @@
       <c r="X689" s="2" t="inlineStr"/>
       <c r="Y689" s="2" t="inlineStr"/>
       <c r="Z689" s="2" t="inlineStr"/>
-      <c r="AA689" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the minimum contribution margin ratio for an item.
-The information is used to check the contribution margin ratio when customer order lines are entered. The value is stated as a percent with a maximum of two decimal places. If no value is entered (zero or blank), the check will not be made.</t>
-        </is>
-      </c>
+      <c r="AA689" s="2" t="inlineStr"/>
       <c r="AB689" s="2" t="inlineStr"/>
       <c r="AC689" s="2" t="inlineStr"/>
       <c r="AD689" s="2" t="inlineStr"/>
@@ -60537,11 +58846,7 @@
       <c r="X690" s="2" t="inlineStr"/>
       <c r="Y690" s="2" t="inlineStr"/>
       <c r="Z690" s="2" t="inlineStr"/>
-      <c r="AA690" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a technical relationship used to group items. The value entered must therefore follow the classification rules defined in (MMS042).</t>
-        </is>
-      </c>
+      <c r="AA690" s="2" t="inlineStr"/>
       <c r="AB690" s="2" t="inlineStr"/>
       <c r="AC690" s="2" t="inlineStr">
         <is>
@@ -60636,13 +58941,7 @@
       <c r="X691" s="2" t="inlineStr"/>
       <c r="Y691" s="2" t="inlineStr"/>
       <c r="Z691" s="2" t="inlineStr"/>
-      <c r="AA691" s="2" t="inlineStr">
-        <is>
-          <t>The fields indicates the fraction of a day for which lead time is rounded up.
-Lead time that is less than the specified value will be considered 0 days.
-This is normally used when the product structure contains very short operation times and lead time should not be set at the minimum of 1 day.</t>
-        </is>
-      </c>
+      <c r="AA691" s="2" t="inlineStr"/>
       <c r="AB691" s="2" t="inlineStr"/>
       <c r="AC691" s="2" t="inlineStr"/>
       <c r="AD691" s="2" t="inlineStr"/>
@@ -60733,13 +59032,7 @@
       <c r="X692" s="2" t="inlineStr"/>
       <c r="Y692" s="2" t="inlineStr"/>
       <c r="Z692" s="2" t="inlineStr"/>
-      <c r="AA692" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to include the item in an available-to-promise (ATP) check in the Global CTP and in some of M3 APS planning tools.
-If you select the check box, the item is treated as a critical material. This enables you to monitor for example its ATP extra carefully during planning and confirmation of delivery dates to customer in order to avoid shortages. Examples of material that can be defined as critical, are materials with a long lead time or material that is difficult to supply.
-The supply model in (MMS059) determines whether or not an ATP check on material used is carried out when a customer order is entered.</t>
-        </is>
-      </c>
+      <c r="AA692" s="2" t="inlineStr"/>
       <c r="AB692" s="2" t="inlineStr"/>
       <c r="AC692" s="2" t="inlineStr"/>
       <c r="AD692" s="2" t="inlineStr"/>
@@ -60830,12 +59123,7 @@
       <c r="X693" s="2" t="inlineStr"/>
       <c r="Y693" s="2" t="inlineStr"/>
       <c r="Z693" s="2" t="inlineStr"/>
-      <c r="AA693" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the general costing model to apply during distribution costing if there is no costing model selected for each combination of item and facility in (MMS003/F).
-The costing model can be overruled when calculating the cost in (PCS280).</t>
-        </is>
-      </c>
+      <c r="AA693" s="2" t="inlineStr"/>
       <c r="AB693" s="2" t="inlineStr"/>
       <c r="AC693" s="2" t="inlineStr"/>
       <c r="AD693" s="2" t="inlineStr"/>
@@ -60922,11 +59210,7 @@
       <c r="X694" s="2" t="inlineStr"/>
       <c r="Y694" s="2" t="inlineStr"/>
       <c r="Z694" s="2" t="inlineStr"/>
-      <c r="AA694" s="2" t="inlineStr">
-        <is>
-          <t>The field is user-defined, but is most often used to control account entries. It is therefore an accounting object that can be verified and changed in (CRS335).</t>
-        </is>
-      </c>
+      <c r="AA694" s="2" t="inlineStr"/>
       <c r="AB694" s="2" t="inlineStr"/>
       <c r="AC694" s="2" t="inlineStr">
         <is>
@@ -61017,13 +59301,7 @@
       <c r="X695" s="2" t="inlineStr"/>
       <c r="Y695" s="2" t="inlineStr"/>
       <c r="Z695" s="2" t="inlineStr"/>
-      <c r="AA695" s="2" t="inlineStr">
-        <is>
-          <t>Select the check box to calculate the average cost per item, facility and costing attribute in the attribute model in (ATS051). The average cost is stored by costing attribute in the FCAAVC table and displayed in (CAS380) when you select option 12 for an average-costed item in (MMS003/B). The advantage of calculating an average cost per costing attribute is that the average cost then reflects the impact of attributes such as Status and Size on the item cost.
-If you do not select the check box, the average cost is calculated per item and facility only and no attributes are included in the calculation. The cost is displayed in (MMS003) and (CAS370).
-Prerequisites for average costing based on attributes are:</t>
-        </is>
-      </c>
+      <c r="AA695" s="2" t="inlineStr"/>
       <c r="AB695" s="2" t="inlineStr"/>
       <c r="AC695" s="2" t="inlineStr"/>
       <c r="AD695" s="2" t="inlineStr"/>
@@ -61118,12 +59396,7 @@
       <c r="X696" s="2" t="inlineStr"/>
       <c r="Y696" s="2" t="inlineStr"/>
       <c r="Z696" s="2" t="inlineStr"/>
-      <c r="AA696" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the on-hand balance in Catch weight U/M.
-Prerequisites for storing catch weight on location level is to set Industry in MNS095 - Company to Food &amp; Beverage.</t>
-        </is>
-      </c>
+      <c r="AA696" s="2" t="inlineStr"/>
       <c r="AB696" s="2" t="inlineStr"/>
       <c r="AC696" s="2" t="inlineStr"/>
       <c r="AD696" s="2" t="inlineStr"/>
@@ -61218,12 +59491,7 @@
       <c r="X697" s="2" t="inlineStr"/>
       <c r="Y697" s="2" t="inlineStr"/>
       <c r="Z697" s="2" t="inlineStr"/>
-      <c r="AA697" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the on-hand balance under inspection in Catch weight U/M.
-Prerequisites for storing catch weight on location level is to set Industry in MNS095 - Company to Food &amp; Beverage.</t>
-        </is>
-      </c>
+      <c r="AA697" s="2" t="inlineStr"/>
       <c r="AB697" s="2" t="inlineStr"/>
       <c r="AC697" s="2" t="inlineStr"/>
       <c r="AD697" s="2" t="inlineStr"/>
@@ -61318,12 +59586,7 @@
       <c r="X698" s="2" t="inlineStr"/>
       <c r="Y698" s="2" t="inlineStr"/>
       <c r="Z698" s="2" t="inlineStr"/>
-      <c r="AA698" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the rejected on-hand balance in Catch weight U/M.
-Prerequisites for storing catch weight on location level is to set Industry in MNS095 - Company to Food &amp; Beverage.</t>
-        </is>
-      </c>
+      <c r="AA698" s="2" t="inlineStr"/>
       <c r="AB698" s="2" t="inlineStr"/>
       <c r="AC698" s="2" t="inlineStr"/>
       <c r="AD698" s="2" t="inlineStr"/>
@@ -61414,18 +59677,8 @@
       <c r="X699" s="2" t="inlineStr"/>
       <c r="Y699" s="2" t="inlineStr"/>
       <c r="Z699" s="2" t="inlineStr"/>
-      <c r="AA699" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates if the value for a specific transaction should be calculated based on the actual weight multiplied by the cost per weight. All stock transactions and internal accounting transactions will be created based on the actual weight and a cost expressed per weight unit. Internal accounting and General Ledger transactions will continue to hold a quantity but this will be the actual weight-based quantity and not the quantity in the basic unit of measure.</t>
-        </is>
-      </c>
-      <c r="AB699" s="2" t="inlineStr">
-        <is>
-          <t>0: No catch weight cost
-1: Catch weight cost
-2: Catch weight cost by facility</t>
-        </is>
-      </c>
+      <c r="AA699" s="2" t="inlineStr"/>
+      <c r="AB699" s="2" t="inlineStr"/>
       <c r="AC699" s="2" t="inlineStr"/>
       <c r="AD699" s="2" t="inlineStr"/>
       <c r="AE699" s="2" t="inlineStr">
@@ -61511,11 +59764,7 @@
       <c r="X700" s="2" t="inlineStr"/>
       <c r="Y700" s="2" t="inlineStr"/>
       <c r="Z700" s="2" t="inlineStr"/>
-      <c r="AA700" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates a factor that is used to convert an alternate U/M to a basic U/M. You can enter a factor with up to 9 decimal places.</t>
-        </is>
-      </c>
+      <c r="AA700" s="2" t="inlineStr"/>
       <c r="AB700" s="2" t="inlineStr"/>
       <c r="AC700" s="2" t="inlineStr"/>
       <c r="AD700" s="2" t="inlineStr"/>
@@ -61598,12 +59847,7 @@
       <c r="X701" s="2" t="inlineStr"/>
       <c r="Y701" s="2" t="inlineStr"/>
       <c r="Z701" s="2" t="inlineStr"/>
-      <c r="AA701" s="2" t="inlineStr">
-        <is>
-          <t>Select this check box to activate the use of alternate product structures (i.e. alternate manufacturing processes) for this item-facility setup.
-If this setting is enabled, you may create alternate structures for the item in (PDS023).</t>
-        </is>
-      </c>
+      <c r="AA701" s="2" t="inlineStr"/>
       <c r="AB701" s="2" t="inlineStr"/>
       <c r="AC701" s="2" t="inlineStr"/>
       <c r="AD701" s="2" t="inlineStr"/>
@@ -61686,12 +59930,7 @@
       <c r="X702" s="2" t="inlineStr"/>
       <c r="Y702" s="2" t="inlineStr"/>
       <c r="Z702" s="2" t="inlineStr"/>
-      <c r="AA702" s="2" t="inlineStr">
-        <is>
-          <t>The field indicates the sequencing code, which is specified per item/facility and used as a reference for sequencing the work center schedules. The sequencing code cannot be changed if planned manufacturing orders exist for the product.
-Sequencing codes are defined in (CRS745).</t>
-        </is>
-      </c>
+      <c r="AA702" s="2" t="inlineStr"/>
       <c r="AB702" s="2" t="inlineStr"/>
       <c r="AC702" s="2" t="inlineStr">
         <is>
